--- a/submission.xlsx
+++ b/submission.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15.17</v>
+        <v>10.049</v>
       </c>
       <c r="C2" t="n">
-        <v>109.598</v>
+        <v>113.142</v>
       </c>
       <c r="D2" t="n">
-        <v>28.157</v>
+        <v>20.077</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.159</v>
+        <v>9.901999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>108.332</v>
+        <v>120.136</v>
       </c>
       <c r="D3" t="n">
-        <v>27.48</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="4">
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.01</v>
+        <v>9.909000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>110.711</v>
+        <v>126.386</v>
       </c>
       <c r="D4" t="n">
-        <v>27.91</v>
+        <v>21.811</v>
       </c>
     </row>
     <row r="5">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.902</v>
+        <v>10.441</v>
       </c>
       <c r="C5" t="n">
-        <v>127.736</v>
+        <v>130.989</v>
       </c>
       <c r="D5" t="n">
-        <v>31.221</v>
+        <v>23.079</v>
       </c>
     </row>
     <row r="6">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.476</v>
+        <v>10.138</v>
       </c>
       <c r="C6" t="n">
-        <v>122.621</v>
+        <v>139.007</v>
       </c>
       <c r="D6" t="n">
-        <v>31.032</v>
+        <v>23.651</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.288</v>
+        <v>10.696</v>
       </c>
       <c r="C7" t="n">
-        <v>123.828</v>
+        <v>131.865</v>
       </c>
       <c r="D7" t="n">
-        <v>30.846</v>
+        <v>23.147</v>
       </c>
     </row>
     <row r="8">
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.069</v>
+        <v>12.322</v>
       </c>
       <c r="C8" t="n">
-        <v>134.867</v>
+        <v>121.08</v>
       </c>
       <c r="D8" t="n">
-        <v>30.983</v>
+        <v>24.642</v>
       </c>
     </row>
     <row r="9">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13.841</v>
+        <v>11.801</v>
       </c>
       <c r="C9" t="n">
-        <v>124.205</v>
+        <v>118.037</v>
       </c>
       <c r="D9" t="n">
-        <v>29.348</v>
+        <v>23.462</v>
       </c>
     </row>
     <row r="10">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.003</v>
+        <v>9.397</v>
       </c>
       <c r="C10" t="n">
-        <v>97.16500000000001</v>
+        <v>129.734</v>
       </c>
       <c r="D10" t="n">
-        <v>25.728</v>
+        <v>21.441</v>
       </c>
     </row>
     <row r="11">
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16.64</v>
+        <v>9.529</v>
       </c>
       <c r="C11" t="n">
-        <v>90.705</v>
+        <v>125.465</v>
       </c>
       <c r="D11" t="n">
-        <v>25.345</v>
+        <v>20.149</v>
       </c>
     </row>
     <row r="12">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.098</v>
+        <v>10.003</v>
       </c>
       <c r="C12" t="n">
-        <v>113.004</v>
+        <v>130.955</v>
       </c>
       <c r="D12" t="n">
-        <v>29.203</v>
+        <v>21.042</v>
       </c>
     </row>
     <row r="13">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14.619</v>
+        <v>9.949</v>
       </c>
       <c r="C13" t="n">
-        <v>116.137</v>
+        <v>122.456</v>
       </c>
       <c r="D13" t="n">
-        <v>29.061</v>
+        <v>20.592</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.636</v>
+        <v>8.736000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>108.541</v>
+        <v>116.768</v>
       </c>
       <c r="D14" t="n">
-        <v>25.691</v>
+        <v>18.357</v>
       </c>
     </row>
     <row r="15">
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.072</v>
+        <v>9.372999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>98.95999999999999</v>
+        <v>106.85</v>
       </c>
       <c r="D15" t="n">
-        <v>23.118</v>
+        <v>19.079</v>
       </c>
     </row>
     <row r="16">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14.384</v>
+        <v>9.813000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>113.024</v>
+        <v>117.093</v>
       </c>
       <c r="D16" t="n">
-        <v>26.437</v>
+        <v>21.382</v>
       </c>
     </row>
     <row r="17">
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14.144</v>
+        <v>11.692</v>
       </c>
       <c r="C17" t="n">
-        <v>119.894</v>
+        <v>121.201</v>
       </c>
       <c r="D17" t="n">
-        <v>28.696</v>
+        <v>23.423</v>
       </c>
     </row>
     <row r="18">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13.942</v>
+        <v>11.623</v>
       </c>
       <c r="C18" t="n">
-        <v>128.227</v>
+        <v>120.82</v>
       </c>
       <c r="D18" t="n">
-        <v>31.535</v>
+        <v>22.054</v>
       </c>
     </row>
     <row r="19">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15.38</v>
+        <v>10.179</v>
       </c>
       <c r="C19" t="n">
-        <v>107.939</v>
+        <v>123.245</v>
       </c>
       <c r="D19" t="n">
-        <v>28.245</v>
+        <v>20.731</v>
       </c>
     </row>
     <row r="20">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.584</v>
+        <v>9.045</v>
       </c>
       <c r="C20" t="n">
-        <v>105.323</v>
+        <v>125.411</v>
       </c>
       <c r="D20" t="n">
-        <v>27.817</v>
+        <v>19.744</v>
       </c>
     </row>
     <row r="21">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.747</v>
+        <v>9.993</v>
       </c>
       <c r="C21" t="n">
-        <v>115.802</v>
+        <v>128.514</v>
       </c>
       <c r="D21" t="n">
-        <v>29.217</v>
+        <v>19.654</v>
       </c>
     </row>
     <row r="22">
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15.087</v>
+        <v>10.622</v>
       </c>
       <c r="C22" t="n">
-        <v>113.801</v>
+        <v>120.618</v>
       </c>
       <c r="D22" t="n">
-        <v>29.541</v>
+        <v>19.55</v>
       </c>
     </row>
     <row r="23">
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.946</v>
+        <v>10.194</v>
       </c>
       <c r="C23" t="n">
-        <v>87.002</v>
+        <v>117.358</v>
       </c>
       <c r="D23" t="n">
-        <v>24.762</v>
+        <v>20.105</v>
       </c>
     </row>
     <row r="24">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.206</v>
+        <v>10.057</v>
       </c>
       <c r="C24" t="n">
-        <v>94.613</v>
+        <v>121.429</v>
       </c>
       <c r="D24" t="n">
-        <v>25.172</v>
+        <v>22.067</v>
       </c>
     </row>
     <row r="25">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15.111</v>
+        <v>10.594</v>
       </c>
       <c r="C25" t="n">
-        <v>107.238</v>
+        <v>122.003</v>
       </c>
       <c r="D25" t="n">
-        <v>26.787</v>
+        <v>23.105</v>
       </c>
     </row>
     <row r="26">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13.896</v>
+        <v>11.524</v>
       </c>
       <c r="C26" t="n">
-        <v>121.391</v>
+        <v>116.435</v>
       </c>
       <c r="D26" t="n">
-        <v>28.429</v>
+        <v>23.667</v>
       </c>
     </row>
     <row r="27">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.928</v>
+        <v>12.02</v>
       </c>
       <c r="C27" t="n">
-        <v>122.857</v>
+        <v>109.886</v>
       </c>
       <c r="D27" t="n">
-        <v>29.147</v>
+        <v>23.551</v>
       </c>
     </row>
     <row r="28">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14.169</v>
+        <v>12.417</v>
       </c>
       <c r="C28" t="n">
-        <v>117.944</v>
+        <v>116.022</v>
       </c>
       <c r="D28" t="n">
-        <v>28.16</v>
+        <v>24.024</v>
       </c>
     </row>
     <row r="29">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>14.713</v>
+        <v>12.375</v>
       </c>
       <c r="C29" t="n">
-        <v>110.854</v>
+        <v>124.285</v>
       </c>
       <c r="D29" t="n">
-        <v>27.343</v>
+        <v>23.672</v>
       </c>
     </row>
     <row r="30">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15.622</v>
+        <v>10.926</v>
       </c>
       <c r="C30" t="n">
-        <v>101.322</v>
+        <v>132.606</v>
       </c>
       <c r="D30" t="n">
-        <v>26.293</v>
+        <v>22.593</v>
       </c>
     </row>
     <row r="31">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16.9</v>
+        <v>9.141</v>
       </c>
       <c r="C31" t="n">
-        <v>89.93899999999999</v>
+        <v>136.367</v>
       </c>
       <c r="D31" t="n">
-        <v>25.618</v>
+        <v>21.087</v>
       </c>
     </row>
     <row r="32">
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.722</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>89.297</v>
+        <v>126.741</v>
       </c>
       <c r="D32" t="n">
-        <v>24.699</v>
+        <v>21.274</v>
       </c>
     </row>
     <row r="33">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.31</v>
+        <v>12.317</v>
       </c>
       <c r="C33" t="n">
-        <v>118.883</v>
+        <v>106.257</v>
       </c>
       <c r="D33" t="n">
-        <v>28.666</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="34">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12.927</v>
+        <v>12.174</v>
       </c>
       <c r="C34" t="n">
-        <v>135.541</v>
+        <v>107.657</v>
       </c>
       <c r="D34" t="n">
-        <v>30.874</v>
+        <v>21.885</v>
       </c>
     </row>
     <row r="35">
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>14.184</v>
+        <v>11.314</v>
       </c>
       <c r="C35" t="n">
-        <v>124.271</v>
+        <v>121.091</v>
       </c>
       <c r="D35" t="n">
-        <v>30.87</v>
+        <v>21.464</v>
       </c>
     </row>
     <row r="36">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>13.655</v>
+        <v>10.419</v>
       </c>
       <c r="C36" t="n">
-        <v>127.279</v>
+        <v>123.535</v>
       </c>
       <c r="D36" t="n">
-        <v>29.644</v>
+        <v>19.408</v>
       </c>
     </row>
     <row r="37">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>14.251</v>
+        <v>10.689</v>
       </c>
       <c r="C37" t="n">
-        <v>116.21</v>
+        <v>106.037</v>
       </c>
       <c r="D37" t="n">
-        <v>26.986</v>
+        <v>16.566</v>
       </c>
     </row>
     <row r="38">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>13.536</v>
+        <v>10.187</v>
       </c>
       <c r="C38" t="n">
-        <v>119.208</v>
+        <v>104.723</v>
       </c>
       <c r="D38" t="n">
-        <v>25.241</v>
+        <v>17.445</v>
       </c>
     </row>
     <row r="39">
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>14.505</v>
+        <v>10.626</v>
       </c>
       <c r="C39" t="n">
-        <v>110.497</v>
+        <v>112.957</v>
       </c>
       <c r="D39" t="n">
-        <v>25.409</v>
+        <v>21.184</v>
       </c>
     </row>
     <row r="40">
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>14.391</v>
+        <v>11.292</v>
       </c>
       <c r="C40" t="n">
-        <v>108.823</v>
+        <v>109.426</v>
       </c>
       <c r="D40" t="n">
-        <v>24.589</v>
+        <v>21.724</v>
       </c>
     </row>
     <row r="41">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.542</v>
+        <v>11.746</v>
       </c>
       <c r="C41" t="n">
-        <v>93.354</v>
+        <v>93.15300000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>22.988</v>
+        <v>18.825</v>
       </c>
     </row>
     <row r="42">
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>14.938</v>
+        <v>10.542</v>
       </c>
       <c r="C42" t="n">
-        <v>97.29600000000001</v>
+        <v>98.85299999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>22.534</v>
+        <v>17.775</v>
       </c>
     </row>
     <row r="43">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>14.836</v>
+        <v>8.316000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>98.517</v>
+        <v>107.188</v>
       </c>
       <c r="D43" t="n">
-        <v>22.66</v>
+        <v>15.787</v>
       </c>
     </row>
     <row r="44">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>14.662</v>
+        <v>7.319</v>
       </c>
       <c r="C44" t="n">
-        <v>99.767</v>
+        <v>113.899</v>
       </c>
       <c r="D44" t="n">
-        <v>22.602</v>
+        <v>15.516</v>
       </c>
     </row>
     <row r="45">
@@ -1133,13 +1133,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>14.837</v>
+        <v>7.474</v>
       </c>
       <c r="C45" t="n">
-        <v>98.378</v>
+        <v>118.207</v>
       </c>
       <c r="D45" t="n">
-        <v>22.627</v>
+        <v>16.549</v>
       </c>
     </row>
     <row r="46">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>14.949</v>
+        <v>6.908</v>
       </c>
       <c r="C46" t="n">
-        <v>96.348</v>
+        <v>125.857</v>
       </c>
       <c r="D46" t="n">
-        <v>22.318</v>
+        <v>16.794</v>
       </c>
     </row>
     <row r="47">
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>14.078</v>
+        <v>8.412000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>108.824</v>
+        <v>119.74</v>
       </c>
       <c r="D47" t="n">
-        <v>23.777</v>
+        <v>17.696</v>
       </c>
     </row>
     <row r="48">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>13.747</v>
+        <v>8.698</v>
       </c>
       <c r="C48" t="n">
-        <v>112.834</v>
+        <v>114.403</v>
       </c>
       <c r="D48" t="n">
-        <v>24.099</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="49">
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>14.435</v>
+        <v>8.273</v>
       </c>
       <c r="C49" t="n">
-        <v>107.08</v>
+        <v>119.179</v>
       </c>
       <c r="D49" t="n">
-        <v>24.227</v>
+        <v>16.318</v>
       </c>
     </row>
     <row r="50">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>14.822</v>
+        <v>8.238</v>
       </c>
       <c r="C50" t="n">
-        <v>103.284</v>
+        <v>121.494</v>
       </c>
       <c r="D50" t="n">
-        <v>24.153</v>
+        <v>17.433</v>
       </c>
     </row>
     <row r="51">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>13.653</v>
+        <v>9.239000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>119.563</v>
+        <v>128.045</v>
       </c>
       <c r="D51" t="n">
-        <v>25.898</v>
+        <v>19.424</v>
       </c>
     </row>
     <row r="52">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12.507</v>
+        <v>9.291</v>
       </c>
       <c r="C52" t="n">
-        <v>131.434</v>
+        <v>120.935</v>
       </c>
       <c r="D52" t="n">
-        <v>26.328</v>
+        <v>19.282</v>
       </c>
     </row>
     <row r="53">
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>12.113</v>
+        <v>9.493</v>
       </c>
       <c r="C53" t="n">
-        <v>135.51</v>
+        <v>111.333</v>
       </c>
       <c r="D53" t="n">
-        <v>26.505</v>
+        <v>18.119</v>
       </c>
     </row>
     <row r="54">
@@ -1277,13 +1277,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>13.994</v>
+        <v>10.812</v>
       </c>
       <c r="C54" t="n">
-        <v>116.55</v>
+        <v>107.033</v>
       </c>
       <c r="D54" t="n">
-        <v>25.67</v>
+        <v>20.934</v>
       </c>
     </row>
     <row r="55">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>15.883</v>
+        <v>10.766</v>
       </c>
       <c r="C55" t="n">
-        <v>97.001</v>
+        <v>109.56</v>
       </c>
       <c r="D55" t="n">
-        <v>24.812</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="56">
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>16.1</v>
+        <v>10.501</v>
       </c>
       <c r="C56" t="n">
-        <v>92.29600000000001</v>
+        <v>109.307</v>
       </c>
       <c r="D56" t="n">
-        <v>24.083</v>
+        <v>20.101</v>
       </c>
     </row>
     <row r="57">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>14.333</v>
+        <v>10.611</v>
       </c>
       <c r="C57" t="n">
-        <v>107.302</v>
+        <v>109.628</v>
       </c>
       <c r="D57" t="n">
-        <v>24.1</v>
+        <v>20.415</v>
       </c>
     </row>
     <row r="58">
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>13.913</v>
+        <v>10.847</v>
       </c>
       <c r="C58" t="n">
-        <v>110.296</v>
+        <v>110.909</v>
       </c>
       <c r="D58" t="n">
-        <v>23.852</v>
+        <v>21.308</v>
       </c>
     </row>
     <row r="59">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>14.054</v>
+        <v>10.786</v>
       </c>
       <c r="C59" t="n">
-        <v>109.237</v>
+        <v>110.944</v>
       </c>
       <c r="D59" t="n">
-        <v>23.905</v>
+        <v>21.126</v>
       </c>
     </row>
     <row r="60">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>14.054</v>
+        <v>10.512</v>
       </c>
       <c r="C60" t="n">
-        <v>109.237</v>
+        <v>112.507</v>
       </c>
       <c r="D60" t="n">
-        <v>23.905</v>
+        <v>21.083</v>
       </c>
     </row>
     <row r="61">
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>14.054</v>
+        <v>11.239</v>
       </c>
       <c r="C61" t="n">
-        <v>109.237</v>
+        <v>107.694</v>
       </c>
       <c r="D61" t="n">
-        <v>23.905</v>
+        <v>21.112</v>
       </c>
     </row>
     <row r="62">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>14.054</v>
+        <v>12.687</v>
       </c>
       <c r="C62" t="n">
-        <v>109.237</v>
+        <v>98.651</v>
       </c>
       <c r="D62" t="n">
-        <v>23.905</v>
+        <v>20.732</v>
       </c>
     </row>
     <row r="63">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>14.054</v>
+        <v>13.601</v>
       </c>
       <c r="C63" t="n">
-        <v>109.237</v>
+        <v>92.977</v>
       </c>
       <c r="D63" t="n">
-        <v>23.905</v>
+        <v>20.655</v>
       </c>
     </row>
     <row r="64">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>14.054</v>
+        <v>13.536</v>
       </c>
       <c r="C64" t="n">
-        <v>109.237</v>
+        <v>93.571</v>
       </c>
       <c r="D64" t="n">
-        <v>23.905</v>
+        <v>20.469</v>
       </c>
     </row>
     <row r="65">
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>14.113</v>
+        <v>13.91</v>
       </c>
       <c r="C65" t="n">
-        <v>108.269</v>
+        <v>91.858</v>
       </c>
       <c r="D65" t="n">
-        <v>23.773</v>
+        <v>20.635</v>
       </c>
     </row>
     <row r="66">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>13.876</v>
+        <v>12.847</v>
       </c>
       <c r="C66" t="n">
-        <v>112.142</v>
+        <v>95.946</v>
       </c>
       <c r="D66" t="n">
-        <v>24.302</v>
+        <v>19.322</v>
       </c>
     </row>
     <row r="67">
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>13.539</v>
+        <v>11.147</v>
       </c>
       <c r="C67" t="n">
-        <v>117.63</v>
+        <v>105.174</v>
       </c>
       <c r="D67" t="n">
-        <v>25.053</v>
+        <v>18.686</v>
       </c>
     </row>
     <row r="68">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>13.302</v>
+        <v>10.157</v>
       </c>
       <c r="C68" t="n">
-        <v>121.504</v>
+        <v>111.933</v>
       </c>
       <c r="D68" t="n">
-        <v>25.583</v>
+        <v>18.496</v>
       </c>
     </row>
     <row r="69">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>13.361</v>
+        <v>10.725</v>
       </c>
       <c r="C69" t="n">
-        <v>120.536</v>
+        <v>111.034</v>
       </c>
       <c r="D69" t="n">
-        <v>25.451</v>
+        <v>19.12</v>
       </c>
     </row>
     <row r="70">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>13.31</v>
+        <v>10.749</v>
       </c>
       <c r="C70" t="n">
-        <v>121.098</v>
+        <v>112.184</v>
       </c>
       <c r="D70" t="n">
-        <v>25.479</v>
+        <v>19.142</v>
       </c>
     </row>
     <row r="71">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>13.515</v>
+        <v>10.224</v>
       </c>
       <c r="C71" t="n">
-        <v>118.848</v>
+        <v>107.597</v>
       </c>
       <c r="D71" t="n">
-        <v>25.364</v>
+        <v>18.062</v>
       </c>
     </row>
     <row r="72">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>13.805</v>
+        <v>9.548</v>
       </c>
       <c r="C72" t="n">
-        <v>115.66</v>
+        <v>102.173</v>
       </c>
       <c r="D72" t="n">
-        <v>25.2</v>
+        <v>16.609</v>
       </c>
     </row>
     <row r="73">
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>14.009</v>
+        <v>9.114000000000001</v>
       </c>
       <c r="C73" t="n">
-        <v>113.41</v>
+        <v>98.86799999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>25.085</v>
+        <v>15.637</v>
       </c>
     </row>
     <row r="74">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>13.958</v>
+        <v>9.221</v>
       </c>
       <c r="C74" t="n">
-        <v>113.973</v>
+        <v>100.952</v>
       </c>
       <c r="D74" t="n">
-        <v>25.114</v>
+        <v>15.907</v>
       </c>
     </row>
     <row r="75">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>14.009</v>
+        <v>9.27</v>
       </c>
       <c r="C75" t="n">
-        <v>113.41</v>
+        <v>99.669</v>
       </c>
       <c r="D75" t="n">
-        <v>25.085</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="76">
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>13.805</v>
+        <v>9.103</v>
       </c>
       <c r="C76" t="n">
-        <v>115.66</v>
+        <v>104.757</v>
       </c>
       <c r="D76" t="n">
-        <v>25.2</v>
+        <v>16.066</v>
       </c>
     </row>
     <row r="77">
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>13.515</v>
+        <v>8.847</v>
       </c>
       <c r="C77" t="n">
-        <v>118.848</v>
+        <v>111.71</v>
       </c>
       <c r="D77" t="n">
-        <v>25.364</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="78">
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>13.31</v>
+        <v>8.65</v>
       </c>
       <c r="C78" t="n">
-        <v>121.098</v>
+        <v>116.676</v>
       </c>
       <c r="D78" t="n">
-        <v>25.479</v>
+        <v>16.442</v>
       </c>
     </row>
     <row r="79">
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>13.361</v>
+        <v>8.666</v>
       </c>
       <c r="C79" t="n">
-        <v>120.536</v>
+        <v>115.657</v>
       </c>
       <c r="D79" t="n">
-        <v>25.451</v>
+        <v>16.315</v>
       </c>
     </row>
     <row r="80">
@@ -1693,13 +1693,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>13.361</v>
+        <v>8.759</v>
       </c>
       <c r="C80" t="n">
-        <v>120.536</v>
+        <v>113.921</v>
       </c>
       <c r="D80" t="n">
-        <v>25.451</v>
+        <v>16.031</v>
       </c>
     </row>
     <row r="81">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>13.361</v>
+        <v>8.253</v>
       </c>
       <c r="C81" t="n">
-        <v>120.536</v>
+        <v>121.288</v>
       </c>
       <c r="D81" t="n">
-        <v>25.451</v>
+        <v>16.935</v>
       </c>
     </row>
     <row r="82">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>13.361</v>
+        <v>7.555</v>
       </c>
       <c r="C82" t="n">
-        <v>120.536</v>
+        <v>132.317</v>
       </c>
       <c r="D82" t="n">
-        <v>25.451</v>
+        <v>18.132</v>
       </c>
     </row>
     <row r="83">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>13.361</v>
+        <v>7.153</v>
       </c>
       <c r="C83" t="n">
-        <v>120.536</v>
+        <v>139.709</v>
       </c>
       <c r="D83" t="n">
-        <v>25.451</v>
+        <v>18.962</v>
       </c>
     </row>
     <row r="84">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>13.361</v>
+        <v>7.298</v>
       </c>
       <c r="C84" t="n">
-        <v>120.536</v>
+        <v>138.594</v>
       </c>
       <c r="D84" t="n">
-        <v>25.451</v>
+        <v>18.713</v>
       </c>
     </row>
     <row r="85">
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>13.33</v>
+        <v>6.9</v>
       </c>
       <c r="C85" t="n">
-        <v>120.877</v>
+        <v>142.807</v>
       </c>
       <c r="D85" t="n">
-        <v>25.468</v>
+        <v>18.588</v>
       </c>
     </row>
     <row r="86">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>13.454</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="C86" t="n">
-        <v>119.513</v>
+        <v>128.84</v>
       </c>
       <c r="D86" t="n">
-        <v>25.398</v>
+        <v>18.999</v>
       </c>
     </row>
     <row r="87">
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>13.629</v>
+        <v>10.331</v>
       </c>
       <c r="C87" t="n">
-        <v>117.58</v>
+        <v>106.947</v>
       </c>
       <c r="D87" t="n">
-        <v>25.3</v>
+        <v>19.402</v>
       </c>
     </row>
     <row r="88">
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>13.752</v>
+        <v>11.759</v>
       </c>
       <c r="C88" t="n">
-        <v>116.215</v>
+        <v>92.53</v>
       </c>
       <c r="D88" t="n">
-        <v>25.23</v>
+        <v>19.857</v>
       </c>
     </row>
     <row r="89">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>13.722</v>
+        <v>11.399</v>
       </c>
       <c r="C89" t="n">
-        <v>116.547</v>
+        <v>96.352</v>
       </c>
       <c r="D89" t="n">
-        <v>25.247</v>
+        <v>19.779</v>
       </c>
     </row>
     <row r="90">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>13.748</v>
+        <v>11.574</v>
       </c>
       <c r="C90" t="n">
-        <v>116.264</v>
+        <v>95.82599999999999</v>
       </c>
       <c r="D90" t="n">
-        <v>25.232</v>
+        <v>19.996</v>
       </c>
     </row>
     <row r="91">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>13.627</v>
+        <v>10.845</v>
       </c>
       <c r="C91" t="n">
-        <v>117.605</v>
+        <v>97.996</v>
       </c>
       <c r="D91" t="n">
-        <v>25.301</v>
+        <v>19.047</v>
       </c>
     </row>
     <row r="92">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>13.458</v>
+        <v>9.805999999999999</v>
       </c>
       <c r="C92" t="n">
-        <v>119.466</v>
+        <v>102.085</v>
       </c>
       <c r="D92" t="n">
-        <v>25.396</v>
+        <v>17.973</v>
       </c>
     </row>
     <row r="93">
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>13.343</v>
+        <v>9.071999999999999</v>
       </c>
       <c r="C93" t="n">
-        <v>120.743</v>
+        <v>104.917</v>
       </c>
       <c r="D93" t="n">
-        <v>25.461</v>
+        <v>17.265</v>
       </c>
     </row>
     <row r="94">
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13.372</v>
+        <v>9.273999999999999</v>
       </c>
       <c r="C94" t="n">
-        <v>120.421</v>
+        <v>103.653</v>
       </c>
       <c r="D94" t="n">
-        <v>25.445</v>
+        <v>17.333</v>
       </c>
     </row>
     <row r="95">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>13.342</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C95" t="n">
-        <v>120.753</v>
+        <v>104.698</v>
       </c>
       <c r="D95" t="n">
-        <v>25.462</v>
+        <v>17.012</v>
       </c>
     </row>
     <row r="96">
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>13.462</v>
+        <v>10.923</v>
       </c>
       <c r="C96" t="n">
-        <v>119.428</v>
+        <v>98.59</v>
       </c>
       <c r="D96" t="n">
-        <v>25.394</v>
+        <v>18.061</v>
       </c>
     </row>
     <row r="97">
@@ -1965,13 +1965,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13.632</v>
+        <v>13.931</v>
       </c>
       <c r="C97" t="n">
-        <v>117.55</v>
+        <v>90.02500000000001</v>
       </c>
       <c r="D97" t="n">
-        <v>25.298</v>
+        <v>19.588</v>
       </c>
     </row>
     <row r="98">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>13.751</v>
+        <v>16.099</v>
       </c>
       <c r="C98" t="n">
-        <v>116.225</v>
+        <v>83.58</v>
       </c>
       <c r="D98" t="n">
-        <v>25.23</v>
+        <v>20.539</v>
       </c>
     </row>
     <row r="99">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>13.721</v>
+        <v>15.651</v>
       </c>
       <c r="C99" t="n">
-        <v>116.556</v>
+        <v>84.57599999999999</v>
       </c>
       <c r="D99" t="n">
-        <v>25.247</v>
+        <v>20.235</v>
       </c>
     </row>
     <row r="100">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>13.721</v>
+        <v>15.897</v>
       </c>
       <c r="C100" t="n">
-        <v>116.556</v>
+        <v>83.033</v>
       </c>
       <c r="D100" t="n">
-        <v>25.247</v>
+        <v>20.073</v>
       </c>
     </row>
     <row r="101">
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>13.721</v>
+        <v>14.947</v>
       </c>
       <c r="C101" t="n">
-        <v>116.556</v>
+        <v>88.494</v>
       </c>
       <c r="D101" t="n">
-        <v>25.247</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="102">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>13.721</v>
+        <v>13.62</v>
       </c>
       <c r="C102" t="n">
-        <v>116.556</v>
+        <v>96.634</v>
       </c>
       <c r="D102" t="n">
-        <v>25.247</v>
+        <v>22.041</v>
       </c>
     </row>
     <row r="103">
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>13.721</v>
+        <v>12.7</v>
       </c>
       <c r="C103" t="n">
-        <v>116.556</v>
+        <v>102.544</v>
       </c>
       <c r="D103" t="n">
-        <v>25.247</v>
+        <v>22.883</v>
       </c>
     </row>
     <row r="104">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>13.721</v>
+        <v>12.933</v>
       </c>
       <c r="C104" t="n">
-        <v>116.556</v>
+        <v>101.532</v>
       </c>
       <c r="D104" t="n">
-        <v>25.247</v>
+        <v>22.762</v>
       </c>
     </row>
     <row r="105">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>13.683</v>
+        <v>13.152</v>
       </c>
       <c r="C105" t="n">
-        <v>117.288</v>
+        <v>100.26</v>
       </c>
       <c r="D105" t="n">
-        <v>25.368</v>
+        <v>22.951</v>
       </c>
     </row>
     <row r="106">
@@ -2109,13 +2109,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>13.836</v>
+        <v>12.258</v>
       </c>
       <c r="C106" t="n">
-        <v>114.363</v>
+        <v>105.654</v>
       </c>
       <c r="D106" t="n">
-        <v>24.886</v>
+        <v>22.249</v>
       </c>
     </row>
     <row r="107">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>14.052</v>
+        <v>11</v>
       </c>
       <c r="C107" t="n">
-        <v>110.219</v>
+        <v>113.376</v>
       </c>
       <c r="D107" t="n">
-        <v>24.203</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="108">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>14.205</v>
+        <v>10.121</v>
       </c>
       <c r="C108" t="n">
-        <v>107.294</v>
+        <v>118.797</v>
       </c>
       <c r="D108" t="n">
-        <v>23.721</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="109">
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>14.167</v>
+        <v>10.356</v>
       </c>
       <c r="C109" t="n">
-        <v>108.025</v>
+        <v>117.299</v>
       </c>
       <c r="D109" t="n">
-        <v>23.841</v>
+        <v>20.751</v>
       </c>
     </row>
     <row r="110">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>14.163</v>
+        <v>10.199</v>
       </c>
       <c r="C110" t="n">
-        <v>108.072</v>
+        <v>119.305</v>
       </c>
       <c r="D110" t="n">
-        <v>23.844</v>
+        <v>20.908</v>
       </c>
     </row>
     <row r="111">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>14.179</v>
+        <v>10.81</v>
       </c>
       <c r="C111" t="n">
-        <v>107.893</v>
+        <v>111.372</v>
       </c>
       <c r="D111" t="n">
-        <v>23.834</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="112">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>14.209</v>
+        <v>11.686</v>
       </c>
       <c r="C112" t="n">
-        <v>107.58</v>
+        <v>100.116</v>
       </c>
       <c r="D112" t="n">
-        <v>23.818</v>
+        <v>19.532</v>
       </c>
     </row>
     <row r="113">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>14.228</v>
+        <v>12.317</v>
       </c>
       <c r="C113" t="n">
-        <v>107.376</v>
+        <v>91.84</v>
       </c>
       <c r="D113" t="n">
-        <v>23.807</v>
+        <v>18.931</v>
       </c>
     </row>
     <row r="114">
@@ -2237,13 +2237,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>14.222</v>
+        <v>12.215</v>
       </c>
       <c r="C114" t="n">
-        <v>107.438</v>
+        <v>93.705</v>
       </c>
       <c r="D114" t="n">
-        <v>23.81</v>
+        <v>19.063</v>
       </c>
     </row>
     <row r="115">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>14.241</v>
+        <v>12.405</v>
       </c>
       <c r="C115" t="n">
-        <v>107.24</v>
+        <v>92.416</v>
       </c>
       <c r="D115" t="n">
-        <v>23.8</v>
+        <v>19.058</v>
       </c>
     </row>
     <row r="116">
@@ -2269,13 +2269,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>14.15</v>
+        <v>11.879</v>
       </c>
       <c r="C116" t="n">
-        <v>108.213</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="D116" t="n">
-        <v>23.851</v>
+        <v>18.929</v>
       </c>
     </row>
     <row r="117">
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>14.02</v>
+        <v>11.112</v>
       </c>
       <c r="C117" t="n">
-        <v>109.606</v>
+        <v>100.065</v>
       </c>
       <c r="D117" t="n">
-        <v>23.924</v>
+        <v>18.774</v>
       </c>
     </row>
     <row r="118">
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>13.928</v>
+        <v>10.374</v>
       </c>
       <c r="C118" t="n">
-        <v>110.589</v>
+        <v>103.742</v>
       </c>
       <c r="D118" t="n">
-        <v>23.976</v>
+        <v>18.366</v>
       </c>
     </row>
     <row r="119">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>13.951</v>
+        <v>10.383</v>
       </c>
       <c r="C119" t="n">
-        <v>110.343</v>
+        <v>103.098</v>
       </c>
       <c r="D119" t="n">
-        <v>23.963</v>
+        <v>18.234</v>
       </c>
     </row>
     <row r="120">
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>13.894</v>
+        <v>10.625</v>
       </c>
       <c r="C120" t="n">
-        <v>111.129</v>
+        <v>102.726</v>
       </c>
       <c r="D120" t="n">
-        <v>24.052</v>
+        <v>18.745</v>
       </c>
     </row>
     <row r="121">
@@ -2349,13 +2349,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>14.122</v>
+        <v>10.611</v>
       </c>
       <c r="C121" t="n">
-        <v>107.986</v>
+        <v>103.614</v>
       </c>
       <c r="D121" t="n">
-        <v>23.696</v>
+        <v>18.936</v>
       </c>
     </row>
     <row r="122">
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>14.445</v>
+        <v>10.238</v>
       </c>
       <c r="C122" t="n">
-        <v>103.535</v>
+        <v>105.178</v>
       </c>
       <c r="D122" t="n">
-        <v>23.192</v>
+        <v>18.518</v>
       </c>
     </row>
     <row r="123">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>14.672</v>
+        <v>9.845000000000001</v>
       </c>
       <c r="C123" t="n">
-        <v>100.401</v>
+        <v>106.587</v>
       </c>
       <c r="D123" t="n">
-        <v>22.836</v>
+        <v>18.012</v>
       </c>
     </row>
     <row r="124">
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>14.618</v>
+        <v>9.927</v>
       </c>
       <c r="C124" t="n">
-        <v>101.15</v>
+        <v>106.373</v>
       </c>
       <c r="D124" t="n">
-        <v>22.923</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="125">
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>14.666</v>
+        <v>9.888999999999999</v>
       </c>
       <c r="C125" t="n">
-        <v>100.464</v>
+        <v>105.268</v>
       </c>
       <c r="D125" t="n">
-        <v>22.84</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="126">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>14.498</v>
+        <v>10.369</v>
       </c>
       <c r="C126" t="n">
-        <v>102.962</v>
+        <v>109.174</v>
       </c>
       <c r="D126" t="n">
-        <v>23.162</v>
+        <v>18.817</v>
       </c>
     </row>
     <row r="127">
@@ -2445,13 +2445,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>14.254</v>
+        <v>10.946</v>
       </c>
       <c r="C127" t="n">
-        <v>106.564</v>
+        <v>114.896</v>
       </c>
       <c r="D127" t="n">
-        <v>23.621</v>
+        <v>19.863</v>
       </c>
     </row>
     <row r="128">
@@ -2461,13 +2461,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>14.083</v>
+        <v>11.255</v>
       </c>
       <c r="C128" t="n">
-        <v>109.099</v>
+        <v>119.112</v>
       </c>
       <c r="D128" t="n">
-        <v>23.945</v>
+        <v>20.523</v>
       </c>
     </row>
     <row r="129">
@@ -2477,13 +2477,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>14.126</v>
+        <v>11.134</v>
       </c>
       <c r="C129" t="n">
-        <v>108.465</v>
+        <v>117.974</v>
       </c>
       <c r="D129" t="n">
-        <v>23.864</v>
+        <v>20.307</v>
       </c>
     </row>
     <row r="130">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>14.132</v>
+        <v>11.05</v>
       </c>
       <c r="C130" t="n">
-        <v>108.399</v>
+        <v>119.569</v>
       </c>
       <c r="D130" t="n">
-        <v>23.861</v>
+        <v>20.319</v>
       </c>
     </row>
     <row r="131">
@@ -2509,13 +2509,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>14.107</v>
+        <v>11.521</v>
       </c>
       <c r="C131" t="n">
-        <v>108.664</v>
+        <v>112.694</v>
       </c>
       <c r="D131" t="n">
-        <v>23.875</v>
+        <v>20.457</v>
       </c>
     </row>
     <row r="132">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>14.072</v>
+        <v>12.155</v>
       </c>
       <c r="C132" t="n">
-        <v>109.039</v>
+        <v>103.097</v>
       </c>
       <c r="D132" t="n">
-        <v>23.895</v>
+        <v>20.605</v>
       </c>
     </row>
     <row r="133">
@@ -2541,13 +2541,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>14.048</v>
+        <v>12.537</v>
       </c>
       <c r="C133" t="n">
-        <v>109.303</v>
+        <v>96.169</v>
       </c>
       <c r="D133" t="n">
-        <v>23.909</v>
+        <v>20.696</v>
       </c>
     </row>
     <row r="134">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>14.054</v>
+        <v>12.436</v>
       </c>
       <c r="C134" t="n">
-        <v>109.237</v>
+        <v>97.687</v>
       </c>
       <c r="D134" t="n">
-        <v>23.905</v>
+        <v>20.652</v>
       </c>
     </row>
     <row r="135">
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>14.037</v>
+        <v>12.429</v>
       </c>
       <c r="C135" t="n">
-        <v>109.416</v>
+        <v>97.291</v>
       </c>
       <c r="D135" t="n">
-        <v>23.915</v>
+        <v>20.626</v>
       </c>
     </row>
     <row r="136">
@@ -2589,13 +2589,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>14.104</v>
+        <v>12.548</v>
       </c>
       <c r="C136" t="n">
-        <v>108.7</v>
+        <v>98.67</v>
       </c>
       <c r="D136" t="n">
-        <v>23.877</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="137">
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>14.199</v>
+        <v>12.621</v>
       </c>
       <c r="C137" t="n">
-        <v>107.684</v>
+        <v>100.541</v>
       </c>
       <c r="D137" t="n">
-        <v>23.823</v>
+        <v>21.641</v>
       </c>
     </row>
     <row r="138">
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>14.266</v>
+        <v>12.649</v>
       </c>
       <c r="C138" t="n">
-        <v>106.968</v>
+        <v>102.582</v>
       </c>
       <c r="D138" t="n">
-        <v>23.785</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="139">
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>14.249</v>
+        <v>12.906</v>
       </c>
       <c r="C139" t="n">
-        <v>107.147</v>
+        <v>99.623</v>
       </c>
       <c r="D139" t="n">
-        <v>23.795</v>
+        <v>21.119</v>
       </c>
     </row>
     <row r="140">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>14.283</v>
+        <v>13.465</v>
       </c>
       <c r="C140" t="n">
-        <v>106.787</v>
+        <v>94.849</v>
       </c>
       <c r="D140" t="n">
-        <v>23.776</v>
+        <v>20.298</v>
       </c>
     </row>
     <row r="141">
@@ -2669,13 +2669,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>14.149</v>
+        <v>13.009</v>
       </c>
       <c r="C141" t="n">
-        <v>108.226</v>
+        <v>97.07599999999999</v>
       </c>
       <c r="D141" t="n">
-        <v>23.851</v>
+        <v>20.346</v>
       </c>
     </row>
     <row r="142">
@@ -2685,13 +2685,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>13.939</v>
+        <v>11.866</v>
       </c>
       <c r="C142" t="n">
-        <v>110.482</v>
+        <v>105.171</v>
       </c>
       <c r="D142" t="n">
-        <v>23.97</v>
+        <v>21.051</v>
       </c>
     </row>
     <row r="143">
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>13.887</v>
+        <v>11.081</v>
       </c>
       <c r="C143" t="n">
-        <v>111.038</v>
+        <v>110.299</v>
       </c>
       <c r="D143" t="n">
-        <v>23.999</v>
+        <v>21.426</v>
       </c>
     </row>
     <row r="144">
@@ -2717,13 +2717,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>14.032</v>
+        <v>11.299</v>
       </c>
       <c r="C144" t="n">
-        <v>109.479</v>
+        <v>108.869</v>
       </c>
       <c r="D144" t="n">
-        <v>23.918</v>
+        <v>21.341</v>
       </c>
     </row>
     <row r="145">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>14.181</v>
+        <v>11.668</v>
       </c>
       <c r="C145" t="n">
-        <v>107.535</v>
+        <v>106.97</v>
       </c>
       <c r="D145" t="n">
-        <v>23.734</v>
+        <v>21.631</v>
       </c>
     </row>
     <row r="146">
@@ -2749,13 +2749,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>13.863</v>
+        <v>10.612</v>
       </c>
       <c r="C146" t="n">
-        <v>112.29</v>
+        <v>112.106</v>
       </c>
       <c r="D146" t="n">
-        <v>24.309</v>
+        <v>20.571</v>
       </c>
     </row>
     <row r="147">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>13.448</v>
+        <v>9.074</v>
       </c>
       <c r="C147" t="n">
-        <v>118.655</v>
+        <v>116.21</v>
       </c>
       <c r="D147" t="n">
-        <v>25.105</v>
+        <v>18.831</v>
       </c>
     </row>
     <row r="148">
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>13.154</v>
+        <v>8.007</v>
       </c>
       <c r="C148" t="n">
-        <v>123.154</v>
+        <v>121.737</v>
       </c>
       <c r="D148" t="n">
-        <v>25.667</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="149">
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>13.228</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="C149" t="n">
-        <v>122.029</v>
+        <v>122.577</v>
       </c>
       <c r="D149" t="n">
-        <v>25.526</v>
+        <v>18.021</v>
       </c>
     </row>
     <row r="150">
@@ -2813,13 +2813,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>13.158</v>
+        <v>8.367000000000001</v>
       </c>
       <c r="C150" t="n">
-        <v>122.797</v>
+        <v>124.541</v>
       </c>
       <c r="D150" t="n">
-        <v>25.565</v>
+        <v>18.139</v>
       </c>
     </row>
     <row r="151">
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>13.437</v>
+        <v>8.455</v>
       </c>
       <c r="C151" t="n">
-        <v>119.728</v>
+        <v>120.66</v>
       </c>
       <c r="D151" t="n">
-        <v>25.408</v>
+        <v>17.974</v>
       </c>
     </row>
     <row r="152">
@@ -2845,13 +2845,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>13.831</v>
+        <v>8.507999999999999</v>
       </c>
       <c r="C152" t="n">
-        <v>115.381</v>
+        <v>119.097</v>
       </c>
       <c r="D152" t="n">
-        <v>25.185</v>
+        <v>17.976</v>
       </c>
     </row>
     <row r="153">
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>14.11</v>
+        <v>8.532999999999999</v>
       </c>
       <c r="C153" t="n">
-        <v>112.312</v>
+        <v>119.087</v>
       </c>
       <c r="D153" t="n">
-        <v>25.028</v>
+        <v>18.196</v>
       </c>
     </row>
     <row r="154">
@@ -2877,13 +2877,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>14.04</v>
+        <v>8.510999999999999</v>
       </c>
       <c r="C154" t="n">
-        <v>113.079</v>
+        <v>120.322</v>
       </c>
       <c r="D154" t="n">
-        <v>25.067</v>
+        <v>18.438</v>
       </c>
     </row>
     <row r="155">
@@ -2893,13 +2893,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>13.886</v>
+        <v>8.535</v>
       </c>
       <c r="C155" t="n">
-        <v>114.669</v>
+        <v>120.069</v>
       </c>
       <c r="D155" t="n">
-        <v>25.146</v>
+        <v>18.351</v>
       </c>
     </row>
     <row r="156">
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>14.503</v>
+        <v>8.429</v>
       </c>
       <c r="C156" t="n">
-        <v>108.311</v>
+        <v>119.74</v>
       </c>
       <c r="D156" t="n">
-        <v>24.832</v>
+        <v>18.054</v>
       </c>
     </row>
     <row r="157">
@@ -2925,13 +2925,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>15.375</v>
+        <v>8.359</v>
       </c>
       <c r="C157" t="n">
-        <v>99.303</v>
+        <v>118.786</v>
       </c>
       <c r="D157" t="n">
-        <v>24.387</v>
+        <v>17.705</v>
       </c>
     </row>
     <row r="158">
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>15.991</v>
+        <v>8.435</v>
       </c>
       <c r="C158" t="n">
-        <v>92.94499999999999</v>
+        <v>117.531</v>
       </c>
       <c r="D158" t="n">
-        <v>24.073</v>
+        <v>17.589</v>
       </c>
     </row>
     <row r="159">
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>15.837</v>
+        <v>8.500999999999999</v>
       </c>
       <c r="C159" t="n">
-        <v>94.53400000000001</v>
+        <v>118.93</v>
       </c>
       <c r="D159" t="n">
-        <v>24.152</v>
+        <v>17.723</v>
       </c>
     </row>
     <row r="160">
@@ -2973,13 +2973,13 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>15.99</v>
+        <v>8.429</v>
       </c>
       <c r="C160" t="n">
-        <v>92.964</v>
+        <v>119.86</v>
       </c>
       <c r="D160" t="n">
-        <v>24.074</v>
+        <v>17.734</v>
       </c>
     </row>
     <row r="161">
@@ -2989,13 +2989,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>15.381</v>
+        <v>8.263999999999999</v>
       </c>
       <c r="C161" t="n">
-        <v>99.246</v>
+        <v>121.956</v>
       </c>
       <c r="D161" t="n">
-        <v>24.384</v>
+        <v>17.727</v>
       </c>
     </row>
     <row r="162">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>14.518</v>
+        <v>8.157</v>
       </c>
       <c r="C162" t="n">
-        <v>108.145</v>
+        <v>122.103</v>
       </c>
       <c r="D162" t="n">
-        <v>24.823</v>
+        <v>17.394</v>
       </c>
     </row>
     <row r="163">
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>13.909</v>
+        <v>8.238</v>
       </c>
       <c r="C163" t="n">
-        <v>114.427</v>
+        <v>127.398</v>
       </c>
       <c r="D163" t="n">
-        <v>25.133</v>
+        <v>18.812</v>
       </c>
     </row>
     <row r="164">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>14.061</v>
+        <v>8.281000000000001</v>
       </c>
       <c r="C164" t="n">
-        <v>112.856</v>
+        <v>127.333</v>
       </c>
       <c r="D164" t="n">
-        <v>25.056</v>
+        <v>18.976</v>
       </c>
     </row>
     <row r="165">
@@ -3053,13 +3053,13 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>14.064</v>
+        <v>8.009</v>
       </c>
       <c r="C165" t="n">
-        <v>112.828</v>
+        <v>133.042</v>
       </c>
       <c r="D165" t="n">
-        <v>25.054</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="166">
@@ -3069,13 +3069,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>14.053</v>
+        <v>9.307</v>
       </c>
       <c r="C166" t="n">
-        <v>112.942</v>
+        <v>117.264</v>
       </c>
       <c r="D166" t="n">
-        <v>25.06</v>
+        <v>18.726</v>
       </c>
     </row>
     <row r="167">
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>14.04</v>
+        <v>10.872</v>
       </c>
       <c r="C167" t="n">
-        <v>113.086</v>
+        <v>99.46899999999999</v>
       </c>
       <c r="D167" t="n">
-        <v>25.068</v>
+        <v>18.277</v>
       </c>
     </row>
     <row r="168">
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>14.022</v>
+        <v>11.638</v>
       </c>
       <c r="C168" t="n">
-        <v>113.277</v>
+        <v>85.10899999999999</v>
       </c>
       <c r="D168" t="n">
-        <v>25.078</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="169">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>14.015</v>
+        <v>11.016</v>
       </c>
       <c r="C169" t="n">
-        <v>113.357</v>
+        <v>90.649</v>
       </c>
       <c r="D169" t="n">
-        <v>25.082</v>
+        <v>17.282</v>
       </c>
     </row>
     <row r="170">
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>14.023</v>
+        <v>10.943</v>
       </c>
       <c r="C170" t="n">
-        <v>113.27</v>
+        <v>88.881</v>
       </c>
       <c r="D170" t="n">
-        <v>25.077</v>
+        <v>16.643</v>
       </c>
     </row>
     <row r="171">
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>13.965</v>
+        <v>11.641</v>
       </c>
       <c r="C171" t="n">
-        <v>113.903</v>
+        <v>92.661</v>
       </c>
       <c r="D171" t="n">
-        <v>25.11</v>
+        <v>18.825</v>
       </c>
     </row>
     <row r="172">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>13.88</v>
+        <v>12.614</v>
       </c>
       <c r="C172" t="n">
-        <v>114.828</v>
+        <v>98.419</v>
       </c>
       <c r="D172" t="n">
-        <v>25.158</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="173">
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>13.82</v>
+        <v>13.285</v>
       </c>
       <c r="C173" t="n">
-        <v>115.481</v>
+        <v>102.622</v>
       </c>
       <c r="D173" t="n">
-        <v>25.192</v>
+        <v>24.171</v>
       </c>
     </row>
     <row r="174">
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>13.835</v>
+        <v>13.113</v>
       </c>
       <c r="C174" t="n">
-        <v>115.318</v>
+        <v>101.563</v>
       </c>
       <c r="D174" t="n">
-        <v>25.183</v>
+        <v>23.605</v>
       </c>
     </row>
     <row r="175">
@@ -3213,13 +3213,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>13.833</v>
+        <v>13.061</v>
       </c>
       <c r="C175" t="n">
-        <v>115.337</v>
+        <v>103.031</v>
       </c>
       <c r="D175" t="n">
-        <v>25.184</v>
+        <v>24.001</v>
       </c>
     </row>
     <row r="176">
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>13.84</v>
+        <v>13.316</v>
       </c>
       <c r="C176" t="n">
-        <v>115.26</v>
+        <v>97.89100000000001</v>
       </c>
       <c r="D176" t="n">
-        <v>25.18</v>
+        <v>22.494</v>
       </c>
     </row>
     <row r="177">
@@ -3245,13 +3245,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>13.85</v>
+        <v>13.645</v>
       </c>
       <c r="C177" t="n">
-        <v>115.151</v>
+        <v>90.52500000000001</v>
       </c>
       <c r="D177" t="n">
-        <v>25.175</v>
+        <v>20.289</v>
       </c>
     </row>
     <row r="178">
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>13.857</v>
+        <v>13.873</v>
       </c>
       <c r="C178" t="n">
-        <v>115.074</v>
+        <v>85.218</v>
       </c>
       <c r="D178" t="n">
-        <v>25.171</v>
+        <v>18.686</v>
       </c>
     </row>
     <row r="179">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>13.855</v>
+        <v>13.798</v>
       </c>
       <c r="C179" t="n">
-        <v>115.093</v>
+        <v>86.636</v>
       </c>
       <c r="D179" t="n">
-        <v>25.172</v>
+        <v>19.005</v>
       </c>
     </row>
     <row r="180">
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>13.858</v>
+        <v>13.91</v>
       </c>
       <c r="C180" t="n">
-        <v>115.064</v>
+        <v>85.28100000000001</v>
       </c>
       <c r="D180" t="n">
-        <v>25.17</v>
+        <v>18.722</v>
       </c>
     </row>
     <row r="181">
@@ -3309,13 +3309,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>13.847</v>
+        <v>13.446</v>
       </c>
       <c r="C181" t="n">
-        <v>115.18</v>
+        <v>90.145</v>
       </c>
       <c r="D181" t="n">
-        <v>25.176</v>
+        <v>19.706</v>
       </c>
     </row>
     <row r="182">
@@ -3325,13 +3325,13 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>13.832</v>
+        <v>12.805</v>
       </c>
       <c r="C182" t="n">
-        <v>115.343</v>
+        <v>97.148</v>
       </c>
       <c r="D182" t="n">
-        <v>25.185</v>
+        <v>21.109</v>
       </c>
     </row>
     <row r="183">
@@ -3341,13 +3341,13 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>13.822</v>
+        <v>12.362</v>
       </c>
       <c r="C183" t="n">
-        <v>115.459</v>
+        <v>102.077</v>
       </c>
       <c r="D183" t="n">
-        <v>25.191</v>
+        <v>22.116</v>
       </c>
     </row>
     <row r="184">
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>13.824</v>
+        <v>12.474</v>
       </c>
       <c r="C184" t="n">
-        <v>115.43</v>
+        <v>100.934</v>
       </c>
       <c r="D184" t="n">
-        <v>25.189</v>
+        <v>21.916</v>
       </c>
     </row>
     <row r="185">
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>13.723</v>
+        <v>12.829</v>
       </c>
       <c r="C185" t="n">
-        <v>116.516</v>
+        <v>99.65300000000001</v>
       </c>
       <c r="D185" t="n">
-        <v>25.246</v>
+        <v>22.387</v>
       </c>
     </row>
     <row r="186">
@@ -3389,13 +3389,13 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>14.13</v>
+        <v>11.609</v>
       </c>
       <c r="C186" t="n">
-        <v>112.173</v>
+        <v>105.548</v>
       </c>
       <c r="D186" t="n">
-        <v>25.019</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="187">
@@ -3405,13 +3405,13 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>14.706</v>
+        <v>9.826000000000001</v>
       </c>
       <c r="C187" t="n">
-        <v>106.021</v>
+        <v>113.855</v>
       </c>
       <c r="D187" t="n">
-        <v>24.697</v>
+        <v>18.917</v>
       </c>
     </row>
     <row r="188">
@@ -3421,13 +3421,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>15.113</v>
+        <v>8.516999999999999</v>
       </c>
       <c r="C188" t="n">
-        <v>101.679</v>
+        <v>120.061</v>
       </c>
       <c r="D188" t="n">
-        <v>24.47</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="189">
@@ -3437,13 +3437,13 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>15.011</v>
+        <v>8.785</v>
       </c>
       <c r="C189" t="n">
-        <v>102.765</v>
+        <v>118.939</v>
       </c>
       <c r="D189" t="n">
-        <v>24.527</v>
+        <v>17.783</v>
       </c>
     </row>
     <row r="190">
@@ -3453,13 +3453,13 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>15.025</v>
+        <v>8.879</v>
       </c>
       <c r="C190" t="n">
-        <v>102.616</v>
+        <v>117.582</v>
       </c>
       <c r="D190" t="n">
-        <v>24.519</v>
+        <v>17.706</v>
       </c>
     </row>
     <row r="191">
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>14.969</v>
+        <v>8.483000000000001</v>
       </c>
       <c r="C191" t="n">
-        <v>103.209</v>
+        <v>123.511</v>
       </c>
       <c r="D191" t="n">
-        <v>24.551</v>
+        <v>18.162</v>
       </c>
     </row>
     <row r="192">
@@ -3485,13 +3485,13 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>14.889</v>
+        <v>7.941</v>
       </c>
       <c r="C192" t="n">
-        <v>104.049</v>
+        <v>131.821</v>
       </c>
       <c r="D192" t="n">
-        <v>24.596</v>
+        <v>18.765</v>
       </c>
     </row>
     <row r="193">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>14.833</v>
+        <v>7.539</v>
       </c>
       <c r="C193" t="n">
-        <v>104.642</v>
+        <v>137.512</v>
       </c>
       <c r="D193" t="n">
-        <v>24.628</v>
+        <v>19.163</v>
       </c>
     </row>
     <row r="194">
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>14.847</v>
+        <v>7.648</v>
       </c>
       <c r="C194" t="n">
-        <v>104.494</v>
+        <v>135.834</v>
       </c>
       <c r="D194" t="n">
-        <v>24.62</v>
+        <v>19.067</v>
       </c>
     </row>
     <row r="195">
@@ -3533,13 +3533,13 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>14.865</v>
+        <v>7.251</v>
       </c>
       <c r="C195" t="n">
-        <v>103.393</v>
+        <v>137.019</v>
       </c>
       <c r="D195" t="n">
-        <v>24.191</v>
+        <v>18.827</v>
       </c>
     </row>
     <row r="196">
@@ -3549,13 +3549,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>14.524</v>
+        <v>9.085000000000001</v>
       </c>
       <c r="C196" t="n">
-        <v>111.194</v>
+        <v>131.412</v>
       </c>
       <c r="D196" t="n">
-        <v>26.432</v>
+        <v>20.088</v>
       </c>
     </row>
     <row r="197">
@@ -3565,13 +3565,13 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>15.799</v>
+        <v>10.32</v>
       </c>
       <c r="C197" t="n">
-        <v>100.833</v>
+        <v>127.01</v>
       </c>
       <c r="D197" t="n">
-        <v>26.619</v>
+        <v>20.336</v>
       </c>
     </row>
     <row r="198">
@@ -3581,13 +3581,13 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>15.738</v>
+        <v>10.85</v>
       </c>
       <c r="C198" t="n">
-        <v>100.486</v>
+        <v>119.947</v>
       </c>
       <c r="D198" t="n">
-        <v>26.045</v>
+        <v>20.982</v>
       </c>
     </row>
     <row r="199">
@@ -3597,13 +3597,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>16.003</v>
+        <v>10.021</v>
       </c>
       <c r="C199" t="n">
-        <v>92.904</v>
+        <v>122.506</v>
       </c>
       <c r="D199" t="n">
-        <v>23.658</v>
+        <v>20.818</v>
       </c>
     </row>
     <row r="200">
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>15.716</v>
+        <v>11.577</v>
       </c>
       <c r="C200" t="n">
-        <v>94.95399999999999</v>
+        <v>119.468</v>
       </c>
       <c r="D200" t="n">
-        <v>23.749</v>
+        <v>22.086</v>
       </c>
     </row>
     <row r="201">
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>16.476</v>
+        <v>11.661</v>
       </c>
       <c r="C201" t="n">
-        <v>85.892</v>
+        <v>121.656</v>
       </c>
       <c r="D201" t="n">
-        <v>22.919</v>
+        <v>21.263</v>
       </c>
     </row>
     <row r="202">
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>15.935</v>
+        <v>10.463</v>
       </c>
       <c r="C202" t="n">
-        <v>91.078</v>
+        <v>124.964</v>
       </c>
       <c r="D202" t="n">
-        <v>23.189</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="203">
@@ -3661,13 +3661,13 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>15.461</v>
+        <v>9.106</v>
       </c>
       <c r="C203" t="n">
-        <v>95.133</v>
+        <v>134.51</v>
       </c>
       <c r="D203" t="n">
-        <v>23.28</v>
+        <v>19.349</v>
       </c>
     </row>
     <row r="204">
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>15.895</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="C204" t="n">
-        <v>90.142</v>
+        <v>130.784</v>
       </c>
       <c r="D204" t="n">
-        <v>22.66</v>
+        <v>20.502</v>
       </c>
     </row>
     <row r="205">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>15.313</v>
+        <v>10.335</v>
       </c>
       <c r="C205" t="n">
-        <v>101.177</v>
+        <v>125.044</v>
       </c>
       <c r="D205" t="n">
-        <v>25.282</v>
+        <v>20.807</v>
       </c>
     </row>
     <row r="206">
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>16.243</v>
+        <v>9.688000000000001</v>
       </c>
       <c r="C206" t="n">
-        <v>96.76600000000001</v>
+        <v>127.968</v>
       </c>
       <c r="D206" t="n">
-        <v>26.442</v>
+        <v>20.227</v>
       </c>
     </row>
     <row r="207">
@@ -3725,13 +3725,13 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>16.315</v>
+        <v>9.525</v>
       </c>
       <c r="C207" t="n">
-        <v>93.916</v>
+        <v>132.654</v>
       </c>
       <c r="D207" t="n">
-        <v>25.51</v>
+        <v>19.499</v>
       </c>
     </row>
     <row r="208">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>17.159</v>
+        <v>9.327999999999999</v>
       </c>
       <c r="C208" t="n">
-        <v>80.586</v>
+        <v>132.306</v>
       </c>
       <c r="D208" t="n">
-        <v>22.823</v>
+        <v>19.517</v>
       </c>
     </row>
     <row r="209">
@@ -3757,13 +3757,13 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>16.364</v>
+        <v>10.173</v>
       </c>
       <c r="C209" t="n">
-        <v>87.57599999999999</v>
+        <v>122.555</v>
       </c>
       <c r="D209" t="n">
-        <v>23.16</v>
+        <v>19.817</v>
       </c>
     </row>
     <row r="210">
@@ -3773,13 +3773,13 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>17.055</v>
+        <v>9.077</v>
       </c>
       <c r="C210" t="n">
-        <v>82.524</v>
+        <v>128.855</v>
       </c>
       <c r="D210" t="n">
-        <v>23.29</v>
+        <v>20.046</v>
       </c>
     </row>
     <row r="211">
@@ -3789,13 +3789,13 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>17.069</v>
+        <v>9.148</v>
       </c>
       <c r="C211" t="n">
-        <v>82.383</v>
+        <v>131.578</v>
       </c>
       <c r="D211" t="n">
-        <v>23.275</v>
+        <v>19.878</v>
       </c>
     </row>
     <row r="212">
@@ -3805,13 +3805,13 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>17.03</v>
+        <v>9.771000000000001</v>
       </c>
       <c r="C212" t="n">
-        <v>83.04900000000001</v>
+        <v>125.08</v>
       </c>
       <c r="D212" t="n">
-        <v>23.41</v>
+        <v>18.755</v>
       </c>
     </row>
     <row r="213">
@@ -3821,13 +3821,13 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>16.818</v>
+        <v>10.605</v>
       </c>
       <c r="C213" t="n">
-        <v>83.119</v>
+        <v>114.568</v>
       </c>
       <c r="D213" t="n">
-        <v>22.781</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="214">
@@ -3837,13 +3837,13 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>16.035</v>
+        <v>10.216</v>
       </c>
       <c r="C214" t="n">
-        <v>97.292</v>
+        <v>124.355</v>
       </c>
       <c r="D214" t="n">
-        <v>25.997</v>
+        <v>19.848</v>
       </c>
     </row>
     <row r="215">
@@ -3853,13 +3853,13 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>16.302</v>
+        <v>9.682</v>
       </c>
       <c r="C215" t="n">
-        <v>96.928</v>
+        <v>134.03</v>
       </c>
       <c r="D215" t="n">
-        <v>26.682</v>
+        <v>20.512</v>
       </c>
     </row>
     <row r="216">
@@ -3869,13 +3869,13 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>15.745</v>
+        <v>10.792</v>
       </c>
       <c r="C216" t="n">
-        <v>105.101</v>
+        <v>118.175</v>
       </c>
       <c r="D216" t="n">
-        <v>28.154</v>
+        <v>20.508</v>
       </c>
     </row>
     <row r="217">
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>15.166</v>
+        <v>11.44</v>
       </c>
       <c r="C217" t="n">
-        <v>111.958</v>
+        <v>109.453</v>
       </c>
       <c r="D217" t="n">
-        <v>29.028</v>
+        <v>19.709</v>
       </c>
     </row>
     <row r="218">
@@ -3901,13 +3901,13 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>15.184</v>
+        <v>10.566</v>
       </c>
       <c r="C218" t="n">
-        <v>111.33</v>
+        <v>116.096</v>
       </c>
       <c r="D218" t="n">
-        <v>28.878</v>
+        <v>19.756</v>
       </c>
     </row>
     <row r="219">
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>15.776</v>
+        <v>10.136</v>
       </c>
       <c r="C219" t="n">
-        <v>102.377</v>
+        <v>126.101</v>
       </c>
       <c r="D219" t="n">
-        <v>27.121</v>
+        <v>20.236</v>
       </c>
     </row>
     <row r="220">
@@ -3933,13 +3933,13 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>14.98</v>
+        <v>10.708</v>
       </c>
       <c r="C220" t="n">
-        <v>112.957</v>
+        <v>123.513</v>
       </c>
       <c r="D220" t="n">
-        <v>28.73</v>
+        <v>21.235</v>
       </c>
     </row>
     <row r="221">
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>14.682</v>
+        <v>10.078</v>
       </c>
       <c r="C221" t="n">
-        <v>115.145</v>
+        <v>127.559</v>
       </c>
       <c r="D221" t="n">
-        <v>28.692</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="222">
@@ -3965,13 +3965,13 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>15.1</v>
+        <v>9.856</v>
       </c>
       <c r="C222" t="n">
-        <v>109.084</v>
+        <v>124.266</v>
       </c>
       <c r="D222" t="n">
-        <v>27.662</v>
+        <v>20.164</v>
       </c>
     </row>
     <row r="223">
@@ -3981,13 +3981,13 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>16.046</v>
+        <v>9.901</v>
       </c>
       <c r="C223" t="n">
-        <v>98.057</v>
+        <v>127.868</v>
       </c>
       <c r="D223" t="n">
-        <v>26.265</v>
+        <v>20.385</v>
       </c>
     </row>
     <row r="224">
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>16.662</v>
+        <v>10.802</v>
       </c>
       <c r="C224" t="n">
-        <v>90.976</v>
+        <v>123.366</v>
       </c>
       <c r="D224" t="n">
-        <v>25.366</v>
+        <v>20.427</v>
       </c>
     </row>
     <row r="225">
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>16.646</v>
+        <v>10.447</v>
       </c>
       <c r="C225" t="n">
-        <v>90.05800000000001</v>
+        <v>123.729</v>
       </c>
       <c r="D225" t="n">
-        <v>25.014</v>
+        <v>20.335</v>
       </c>
     </row>
     <row r="226">
@@ -4029,13 +4029,13 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>15.936</v>
+        <v>10.053</v>
       </c>
       <c r="C226" t="n">
-        <v>97.79000000000001</v>
+        <v>122.712</v>
       </c>
       <c r="D226" t="n">
-        <v>25.899</v>
+        <v>20.464</v>
       </c>
     </row>
     <row r="227">
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>15.138</v>
+        <v>10.498</v>
       </c>
       <c r="C227" t="n">
-        <v>107.536</v>
+        <v>120.363</v>
       </c>
       <c r="D227" t="n">
-        <v>27.172</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="228">
@@ -4061,13 +4061,13 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>14.694</v>
+        <v>11.206</v>
       </c>
       <c r="C228" t="n">
-        <v>114.972</v>
+        <v>113.777</v>
       </c>
       <c r="D228" t="n">
-        <v>28.676</v>
+        <v>21.223</v>
       </c>
     </row>
     <row r="229">
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>15.06</v>
+        <v>11.937</v>
       </c>
       <c r="C229" t="n">
-        <v>112.808</v>
+        <v>109.5</v>
       </c>
       <c r="D229" t="n">
-        <v>28.962</v>
+        <v>21.817</v>
       </c>
     </row>
     <row r="230">
@@ -4093,13 +4093,13 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>16.034</v>
+        <v>10.447</v>
       </c>
       <c r="C230" t="n">
-        <v>101.667</v>
+        <v>118.323</v>
       </c>
       <c r="D230" t="n">
-        <v>27.721</v>
+        <v>19.803</v>
       </c>
     </row>
     <row r="231">
@@ -4109,13 +4109,13 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>15.386</v>
+        <v>11.216</v>
       </c>
       <c r="C231" t="n">
-        <v>109.295</v>
+        <v>120.719</v>
       </c>
       <c r="D231" t="n">
-        <v>28.634</v>
+        <v>19.654</v>
       </c>
     </row>
     <row r="232">
@@ -4125,13 +4125,13 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>14.052</v>
+        <v>11.814</v>
       </c>
       <c r="C232" t="n">
-        <v>128.108</v>
+        <v>121.981</v>
       </c>
       <c r="D232" t="n">
-        <v>31.962</v>
+        <v>19.922</v>
       </c>
     </row>
     <row r="233">
@@ -4141,13 +4141,13 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>14.936</v>
+        <v>11.435</v>
       </c>
       <c r="C233" t="n">
-        <v>112.315</v>
+        <v>121.318</v>
       </c>
       <c r="D233" t="n">
-        <v>28.484</v>
+        <v>19.869</v>
       </c>
     </row>
     <row r="234">
@@ -4157,13 +4157,13 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>16.132</v>
+        <v>10.369</v>
       </c>
       <c r="C234" t="n">
-        <v>91.967</v>
+        <v>108.919</v>
       </c>
       <c r="D234" t="n">
-        <v>24.243</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="235">
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>15.744</v>
+        <v>10.814</v>
       </c>
       <c r="C235" t="n">
-        <v>95.209</v>
+        <v>107.884</v>
       </c>
       <c r="D235" t="n">
-        <v>24.267</v>
+        <v>18.783</v>
       </c>
     </row>
     <row r="236">
@@ -4189,13 +4189,13 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>15.702</v>
+        <v>10.901</v>
       </c>
       <c r="C236" t="n">
-        <v>98.97199999999999</v>
+        <v>118.528</v>
       </c>
       <c r="D236" t="n">
-        <v>25.638</v>
+        <v>19.578</v>
       </c>
     </row>
     <row r="237">
@@ -4205,13 +4205,13 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>16.083</v>
+        <v>11.375</v>
       </c>
       <c r="C237" t="n">
-        <v>96.336</v>
+        <v>124.24</v>
       </c>
       <c r="D237" t="n">
-        <v>25.69</v>
+        <v>22.574</v>
       </c>
     </row>
     <row r="238">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>15.956</v>
+        <v>11.087</v>
       </c>
       <c r="C238" t="n">
-        <v>97.075</v>
+        <v>125.877</v>
       </c>
       <c r="D238" t="n">
-        <v>25.573</v>
+        <v>23.517</v>
       </c>
     </row>
     <row r="239">
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>15.565</v>
+        <v>10.177</v>
       </c>
       <c r="C239" t="n">
-        <v>100.331</v>
+        <v>130.432</v>
       </c>
       <c r="D239" t="n">
-        <v>25.684</v>
+        <v>23.031</v>
       </c>
     </row>
     <row r="240">
@@ -4253,13 +4253,13 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>15.284</v>
+        <v>10.176</v>
       </c>
       <c r="C240" t="n">
-        <v>103.606</v>
+        <v>126.529</v>
       </c>
       <c r="D240" t="n">
-        <v>26.217</v>
+        <v>21.317</v>
       </c>
     </row>
     <row r="241">
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>16.27</v>
+        <v>9.971</v>
       </c>
       <c r="C241" t="n">
-        <v>93.693</v>
+        <v>120.549</v>
       </c>
       <c r="D241" t="n">
-        <v>25.389</v>
+        <v>20.093</v>
       </c>
     </row>
     <row r="242">
@@ -4285,13 +4285,13 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>15.491</v>
+        <v>11.015</v>
       </c>
       <c r="C242" t="n">
-        <v>101.786</v>
+        <v>109.802</v>
       </c>
       <c r="D242" t="n">
-        <v>25.807</v>
+        <v>19.077</v>
       </c>
     </row>
     <row r="243">
@@ -4301,13 +4301,13 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>15.944</v>
+        <v>11.951</v>
       </c>
       <c r="C243" t="n">
-        <v>92.47499999999999</v>
+        <v>101.714</v>
       </c>
       <c r="D243" t="n">
-        <v>23.413</v>
+        <v>19.259</v>
       </c>
     </row>
     <row r="244">
@@ -4317,13 +4317,13 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>14.763</v>
+        <v>12.657</v>
       </c>
       <c r="C244" t="n">
-        <v>107.202</v>
+        <v>97.146</v>
       </c>
       <c r="D244" t="n">
-        <v>25.686</v>
+        <v>20.484</v>
       </c>
     </row>
     <row r="245">
@@ -4333,13 +4333,13 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>15.554</v>
+        <v>9.731999999999999</v>
       </c>
       <c r="C245" t="n">
-        <v>99.607</v>
+        <v>114.187</v>
       </c>
       <c r="D245" t="n">
-        <v>25.442</v>
+        <v>19.504</v>
       </c>
     </row>
     <row r="246">
@@ -4349,13 +4349,13 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>15.475</v>
+        <v>9.532999999999999</v>
       </c>
       <c r="C246" t="n">
-        <v>101.483</v>
+        <v>115.523</v>
       </c>
       <c r="D246" t="n">
-        <v>25.935</v>
+        <v>18.798</v>
       </c>
     </row>
     <row r="247">
@@ -4365,13 +4365,13 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>15.618</v>
+        <v>11.521</v>
       </c>
       <c r="C247" t="n">
-        <v>95.956</v>
+        <v>113.308</v>
       </c>
       <c r="D247" t="n">
-        <v>24.189</v>
+        <v>20.172</v>
       </c>
     </row>
     <row r="248">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>15.555</v>
+        <v>11.656</v>
       </c>
       <c r="C248" t="n">
-        <v>96.687</v>
+        <v>116.145</v>
       </c>
       <c r="D248" t="n">
-        <v>24.235</v>
+        <v>21.37</v>
       </c>
     </row>
     <row r="249">
@@ -4397,13 +4397,13 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>16.254</v>
+        <v>11.105</v>
       </c>
       <c r="C249" t="n">
-        <v>87.86799999999999</v>
+        <v>116.778</v>
       </c>
       <c r="D249" t="n">
-        <v>22.878</v>
+        <v>21.041</v>
       </c>
     </row>
     <row r="250">
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>17.25</v>
+        <v>10.879</v>
       </c>
       <c r="C250" t="n">
-        <v>80.56699999999999</v>
+        <v>120.681</v>
       </c>
       <c r="D250" t="n">
-        <v>23.194</v>
+        <v>20.395</v>
       </c>
     </row>
     <row r="251">
@@ -4429,13 +4429,13 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>16.357</v>
+        <v>10.84</v>
       </c>
       <c r="C251" t="n">
-        <v>88.61499999999999</v>
+        <v>115.959</v>
       </c>
       <c r="D251" t="n">
-        <v>23.295</v>
+        <v>19.287</v>
       </c>
     </row>
     <row r="252">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>15.181</v>
+        <v>10.235</v>
       </c>
       <c r="C252" t="n">
-        <v>106.658</v>
+        <v>107.837</v>
       </c>
       <c r="D252" t="n">
-        <v>26.741</v>
+        <v>18.859</v>
       </c>
     </row>
     <row r="253">
@@ -4461,13 +4461,13 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>15.382</v>
+        <v>10.789</v>
       </c>
       <c r="C253" t="n">
-        <v>107.199</v>
+        <v>92.646</v>
       </c>
       <c r="D253" t="n">
-        <v>27.681</v>
+        <v>18.405</v>
       </c>
     </row>
     <row r="254">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>16.632</v>
+        <v>11.227</v>
       </c>
       <c r="C254" t="n">
-        <v>91.572</v>
+        <v>90.852</v>
       </c>
       <c r="D254" t="n">
-        <v>25.668</v>
+        <v>18.43</v>
       </c>
     </row>
     <row r="255">
@@ -4493,13 +4493,13 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>15.931</v>
+        <v>12.356</v>
       </c>
       <c r="C255" t="n">
-        <v>94.15000000000001</v>
+        <v>87.996</v>
       </c>
       <c r="D255" t="n">
-        <v>24.213</v>
+        <v>19.652</v>
       </c>
     </row>
     <row r="256">
@@ -4509,13 +4509,13 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>15.137</v>
+        <v>13.453</v>
       </c>
       <c r="C256" t="n">
-        <v>101.577</v>
+        <v>80.977</v>
       </c>
       <c r="D256" t="n">
-        <v>24.668</v>
+        <v>18.679</v>
       </c>
     </row>
     <row r="257">
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>14.804</v>
+        <v>13.71</v>
       </c>
       <c r="C257" t="n">
-        <v>110.075</v>
+        <v>76.977</v>
       </c>
       <c r="D257" t="n">
-        <v>26.996</v>
+        <v>18.006</v>
       </c>
     </row>
     <row r="258">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>15.378</v>
+        <v>14.871</v>
       </c>
       <c r="C258" t="n">
-        <v>104.286</v>
+        <v>79.499</v>
       </c>
       <c r="D258" t="n">
-        <v>26.526</v>
+        <v>19.729</v>
       </c>
     </row>
     <row r="259">
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>16.235</v>
+        <v>14.747</v>
       </c>
       <c r="C259" t="n">
-        <v>94.79300000000001</v>
+        <v>86.48699999999999</v>
       </c>
       <c r="D259" t="n">
-        <v>25.404</v>
+        <v>21.933</v>
       </c>
     </row>
     <row r="260">
@@ -4573,13 +4573,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>16.153</v>
+        <v>14.734</v>
       </c>
       <c r="C260" t="n">
-        <v>96.27500000000001</v>
+        <v>83.565</v>
       </c>
       <c r="D260" t="n">
-        <v>25.723</v>
+        <v>20.177</v>
       </c>
     </row>
     <row r="261">
@@ -4589,13 +4589,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>15.77</v>
+        <v>12.8</v>
       </c>
       <c r="C261" t="n">
-        <v>103.717</v>
+        <v>90.70099999999999</v>
       </c>
       <c r="D261" t="n">
-        <v>27.527</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="262">
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>15.988</v>
+        <v>13.154</v>
       </c>
       <c r="C262" t="n">
-        <v>95.398</v>
+        <v>94.129</v>
       </c>
       <c r="D262" t="n">
-        <v>24.969</v>
+        <v>20.967</v>
       </c>
     </row>
     <row r="263">
@@ -4621,13 +4621,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>17.543</v>
+        <v>12.109</v>
       </c>
       <c r="C263" t="n">
-        <v>71.238</v>
+        <v>90.536</v>
       </c>
       <c r="D263" t="n">
-        <v>20.434</v>
+        <v>20.041</v>
       </c>
     </row>
     <row r="264">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>15.956</v>
+        <v>13.09</v>
       </c>
       <c r="C264" t="n">
-        <v>92.089</v>
+        <v>81.863</v>
       </c>
       <c r="D264" t="n">
-        <v>23.612</v>
+        <v>19.258</v>
       </c>
     </row>
     <row r="265">
@@ -4653,13 +4653,13 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>14.103</v>
+        <v>12.781</v>
       </c>
       <c r="C265" t="n">
-        <v>120.997</v>
+        <v>86.10299999999999</v>
       </c>
       <c r="D265" t="n">
-        <v>28.997</v>
+        <v>19.726</v>
       </c>
     </row>
     <row r="266">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>14.346</v>
+        <v>15.001</v>
       </c>
       <c r="C266" t="n">
-        <v>117.24</v>
+        <v>81.438</v>
       </c>
       <c r="D266" t="n">
-        <v>28.314</v>
+        <v>20.534</v>
       </c>
     </row>
     <row r="267">
@@ -4685,13 +4685,13 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>14.947</v>
+        <v>15.604</v>
       </c>
       <c r="C267" t="n">
-        <v>110.274</v>
+        <v>90.26300000000001</v>
       </c>
       <c r="D267" t="n">
-        <v>27.491</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="268">
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>15.048</v>
+        <v>14.495</v>
       </c>
       <c r="C268" t="n">
-        <v>108.19</v>
+        <v>106.486</v>
       </c>
       <c r="D268" t="n">
-        <v>27.139</v>
+        <v>23.404</v>
       </c>
     </row>
     <row r="269">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>14.745</v>
+        <v>11.762</v>
       </c>
       <c r="C269" t="n">
-        <v>109.291</v>
+        <v>117.651</v>
       </c>
       <c r="D269" t="n">
-        <v>26.628</v>
+        <v>23.172</v>
       </c>
     </row>
     <row r="270">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>15.528</v>
+        <v>11.898</v>
       </c>
       <c r="C270" t="n">
-        <v>94.624</v>
+        <v>102.193</v>
       </c>
       <c r="D270" t="n">
-        <v>23.411</v>
+        <v>21.101</v>
       </c>
     </row>
     <row r="271">
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>14.652</v>
+        <v>14.282</v>
       </c>
       <c r="C271" t="n">
-        <v>109.663</v>
+        <v>86.26900000000001</v>
       </c>
       <c r="D271" t="n">
-        <v>26.49</v>
+        <v>20.324</v>
       </c>
     </row>
     <row r="272">
@@ -4765,13 +4765,13 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>15.357</v>
+        <v>14.784</v>
       </c>
       <c r="C272" t="n">
-        <v>106.117</v>
+        <v>79.383</v>
       </c>
       <c r="D272" t="n">
-        <v>27.253</v>
+        <v>18.372</v>
       </c>
     </row>
     <row r="273">
@@ -4781,13 +4781,13 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>15.671</v>
+        <v>14.033</v>
       </c>
       <c r="C273" t="n">
-        <v>106.998</v>
+        <v>81.24299999999999</v>
       </c>
       <c r="D273" t="n">
-        <v>28.593</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="274">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>16.311</v>
+        <v>13.606</v>
       </c>
       <c r="C274" t="n">
-        <v>94.464</v>
+        <v>84.095</v>
       </c>
       <c r="D274" t="n">
-        <v>25.83</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="275">
@@ -4813,13 +4813,13 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>14.435</v>
+        <v>15.69</v>
       </c>
       <c r="C275" t="n">
-        <v>114.157</v>
+        <v>76.402</v>
       </c>
       <c r="D275" t="n">
-        <v>27.222</v>
+        <v>19.392</v>
       </c>
     </row>
     <row r="276">
@@ -4829,13 +4829,13 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>13.593</v>
+        <v>15.382</v>
       </c>
       <c r="C276" t="n">
-        <v>122.959</v>
+        <v>75.994</v>
       </c>
       <c r="D276" t="n">
-        <v>27.621</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="277">
@@ -4845,13 +4845,13 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>13.006</v>
+        <v>12.7</v>
       </c>
       <c r="C277" t="n">
-        <v>132.762</v>
+        <v>83.51900000000001</v>
       </c>
       <c r="D277" t="n">
-        <v>29.793</v>
+        <v>18.432</v>
       </c>
     </row>
     <row r="278">
@@ -4861,13 +4861,13 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>14.124</v>
+        <v>12.839</v>
       </c>
       <c r="C278" t="n">
-        <v>120.182</v>
+        <v>84.33799999999999</v>
       </c>
       <c r="D278" t="n">
-        <v>28.913</v>
+        <v>18.753</v>
       </c>
     </row>
     <row r="279">
@@ -4877,13 +4877,13 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>14.151</v>
+        <v>13.691</v>
       </c>
       <c r="C279" t="n">
-        <v>121.537</v>
+        <v>79.21899999999999</v>
       </c>
       <c r="D279" t="n">
-        <v>29.656</v>
+        <v>18.477</v>
       </c>
     </row>
     <row r="280">
@@ -4893,13 +4893,13 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>15.072</v>
+        <v>13.652</v>
       </c>
       <c r="C280" t="n">
-        <v>111.053</v>
+        <v>79.657</v>
       </c>
       <c r="D280" t="n">
-        <v>28.369</v>
+        <v>18.236</v>
       </c>
     </row>
     <row r="281">
@@ -4909,13 +4909,13 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>16.237</v>
+        <v>14.217</v>
       </c>
       <c r="C281" t="n">
-        <v>94.44499999999999</v>
+        <v>79.408</v>
       </c>
       <c r="D281" t="n">
-        <v>25.442</v>
+        <v>17.943</v>
       </c>
     </row>
     <row r="282">
@@ -4925,13 +4925,13 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>16.901</v>
+        <v>16.149</v>
       </c>
       <c r="C282" t="n">
-        <v>76.892</v>
+        <v>84.41800000000001</v>
       </c>
       <c r="D282" t="n">
-        <v>20.834</v>
+        <v>20.006</v>
       </c>
     </row>
     <row r="283">
@@ -4941,13 +4941,13 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>16.598</v>
+        <v>13.739</v>
       </c>
       <c r="C283" t="n">
-        <v>77.48099999999999</v>
+        <v>101.016</v>
       </c>
       <c r="D283" t="n">
-        <v>20.39</v>
+        <v>20.475</v>
       </c>
     </row>
     <row r="284">
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>14.904</v>
+        <v>12.576</v>
       </c>
       <c r="C284" t="n">
-        <v>102.331</v>
+        <v>102.058</v>
       </c>
       <c r="D284" t="n">
-        <v>24.244</v>
+        <v>19.943</v>
       </c>
     </row>
     <row r="285">
@@ -4973,13 +4973,13 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>13.536</v>
+        <v>14.415</v>
       </c>
       <c r="C285" t="n">
-        <v>124.369</v>
+        <v>83.88</v>
       </c>
       <c r="D285" t="n">
-        <v>28.168</v>
+        <v>18.821</v>
       </c>
     </row>
     <row r="286">
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>14.161</v>
+        <v>14.472</v>
       </c>
       <c r="C286" t="n">
-        <v>115.813</v>
+        <v>79.703</v>
       </c>
       <c r="D286" t="n">
-        <v>26.93</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="287">
@@ -5005,13 +5005,13 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>16.49</v>
+        <v>13.386</v>
       </c>
       <c r="C287" t="n">
-        <v>91.376</v>
+        <v>80.813</v>
       </c>
       <c r="D287" t="n">
-        <v>24.919</v>
+        <v>17.759</v>
       </c>
     </row>
     <row r="288">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>18.021</v>
+        <v>14.481</v>
       </c>
       <c r="C288" t="n">
-        <v>60.423</v>
+        <v>81.642</v>
       </c>
       <c r="D288" t="n">
-        <v>18.327</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="289">
@@ -5037,13 +5037,13 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>16.945</v>
+        <v>16.181</v>
       </c>
       <c r="C289" t="n">
-        <v>70.035</v>
+        <v>80.312</v>
       </c>
       <c r="D289" t="n">
-        <v>19.037</v>
+        <v>21.358</v>
       </c>
     </row>
     <row r="290">
@@ -5053,13 +5053,13 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>15.477</v>
+        <v>16.896</v>
       </c>
       <c r="C290" t="n">
-        <v>88.764</v>
+        <v>81.214</v>
       </c>
       <c r="D290" t="n">
-        <v>21.417</v>
+        <v>21.897</v>
       </c>
     </row>
     <row r="291">
@@ -5069,13 +5069,13 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>14.365</v>
+        <v>14.73</v>
       </c>
       <c r="C291" t="n">
-        <v>119.869</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="D291" t="n">
-        <v>29.391</v>
+        <v>19.734</v>
       </c>
     </row>
     <row r="292">
@@ -5085,13 +5085,13 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>14.993</v>
+        <v>14.629</v>
       </c>
       <c r="C292" t="n">
-        <v>107.221</v>
+        <v>84.75</v>
       </c>
       <c r="D292" t="n">
-        <v>26.572</v>
+        <v>19.235</v>
       </c>
     </row>
     <row r="293">
@@ -5101,13 +5101,13 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>14.313</v>
+        <v>14.658</v>
       </c>
       <c r="C293" t="n">
-        <v>114.164</v>
+        <v>80.764</v>
       </c>
       <c r="D293" t="n">
-        <v>26.943</v>
+        <v>18.988</v>
       </c>
     </row>
     <row r="294">
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>15.013</v>
+        <v>15.668</v>
       </c>
       <c r="C294" t="n">
-        <v>99.736</v>
+        <v>73.806</v>
       </c>
       <c r="D294" t="n">
-        <v>23.346</v>
+        <v>19.517</v>
       </c>
     </row>
     <row r="295">
@@ -5133,13 +5133,13 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>14.947</v>
+        <v>14.999</v>
       </c>
       <c r="C295" t="n">
-        <v>106.89</v>
+        <v>76.995</v>
       </c>
       <c r="D295" t="n">
-        <v>26.138</v>
+        <v>18.736</v>
       </c>
     </row>
     <row r="296">
@@ -5149,13 +5149,13 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>14.668</v>
+        <v>15.924</v>
       </c>
       <c r="C296" t="n">
-        <v>110.442</v>
+        <v>74.883</v>
       </c>
       <c r="D296" t="n">
-        <v>26.631</v>
+        <v>18.951</v>
       </c>
     </row>
     <row r="297">
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>14.655</v>
+        <v>15.086</v>
       </c>
       <c r="C297" t="n">
-        <v>107.433</v>
+        <v>77.646</v>
       </c>
       <c r="D297" t="n">
-        <v>25.335</v>
+        <v>18.329</v>
       </c>
     </row>
     <row r="298">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>15.145</v>
+        <v>12.337</v>
       </c>
       <c r="C298" t="n">
-        <v>103.66</v>
+        <v>94.194</v>
       </c>
       <c r="D298" t="n">
-        <v>25.527</v>
+        <v>20.508</v>
       </c>
     </row>
     <row r="299">
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>15.041</v>
+        <v>14.152</v>
       </c>
       <c r="C299" t="n">
-        <v>107.324</v>
+        <v>87.273</v>
       </c>
       <c r="D299" t="n">
-        <v>26.801</v>
+        <v>20.966</v>
       </c>
     </row>
     <row r="300">
@@ -5213,13 +5213,13 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>15.553</v>
+        <v>13.786</v>
       </c>
       <c r="C300" t="n">
-        <v>99.262</v>
+        <v>85.61</v>
       </c>
       <c r="D300" t="n">
-        <v>25.247</v>
+        <v>19.675</v>
       </c>
     </row>
     <row r="301">
@@ -5229,13 +5229,13 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>15.235</v>
+        <v>15.408</v>
       </c>
       <c r="C301" t="n">
-        <v>100.727</v>
+        <v>77.553</v>
       </c>
       <c r="D301" t="n">
-        <v>24.601</v>
+        <v>19.301</v>
       </c>
     </row>
     <row r="302">
@@ -5245,13 +5245,13 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>14.534</v>
+        <v>13.412</v>
       </c>
       <c r="C302" t="n">
-        <v>110.415</v>
+        <v>94.89</v>
       </c>
       <c r="D302" t="n">
-        <v>26.138</v>
+        <v>21.458</v>
       </c>
     </row>
     <row r="303">
@@ -5261,13 +5261,13 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>15.024</v>
+        <v>13.399</v>
       </c>
       <c r="C303" t="n">
-        <v>102.733</v>
+        <v>97.401</v>
       </c>
       <c r="D303" t="n">
-        <v>24.725</v>
+        <v>21.031</v>
       </c>
     </row>
     <row r="304">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>15.644</v>
+        <v>12.503</v>
       </c>
       <c r="C304" t="n">
-        <v>98.703</v>
+        <v>97.661</v>
       </c>
       <c r="D304" t="n">
-        <v>25.293</v>
+        <v>19.565</v>
       </c>
     </row>
     <row r="305">
@@ -5293,13 +5293,13 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>15.576</v>
+        <v>14.894</v>
       </c>
       <c r="C305" t="n">
-        <v>101.605</v>
+        <v>83.434</v>
       </c>
       <c r="D305" t="n">
-        <v>26.175</v>
+        <v>19.157</v>
       </c>
     </row>
     <row r="306">
@@ -5309,13 +5309,13 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>15.014</v>
+        <v>15.202</v>
       </c>
       <c r="C306" t="n">
-        <v>109.811</v>
+        <v>77.616</v>
       </c>
       <c r="D306" t="n">
-        <v>27.645</v>
+        <v>19.215</v>
       </c>
     </row>
     <row r="307">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>14.909</v>
+        <v>13.197</v>
       </c>
       <c r="C307" t="n">
-        <v>112.445</v>
+        <v>78.392</v>
       </c>
       <c r="D307" t="n">
-        <v>28.327</v>
+        <v>17.771</v>
       </c>
     </row>
     <row r="308">
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>13.847</v>
+        <v>12.758</v>
       </c>
       <c r="C308" t="n">
-        <v>130.768</v>
+        <v>83.104</v>
       </c>
       <c r="D308" t="n">
-        <v>32.204</v>
+        <v>19.856</v>
       </c>
     </row>
     <row r="309">
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>14.482</v>
+        <v>13.722</v>
       </c>
       <c r="C309" t="n">
-        <v>119.914</v>
+        <v>79.998</v>
       </c>
       <c r="D309" t="n">
-        <v>29.947</v>
+        <v>19.854</v>
       </c>
     </row>
     <row r="310">
@@ -5373,13 +5373,13 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>16.368</v>
+        <v>16.003</v>
       </c>
       <c r="C310" t="n">
-        <v>87.66</v>
+        <v>72.53700000000001</v>
       </c>
       <c r="D310" t="n">
-        <v>23.231</v>
+        <v>19.064</v>
       </c>
     </row>
   </sheetData>

--- a/submission.xlsx
+++ b/submission.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.049</v>
+        <v>10.092</v>
       </c>
       <c r="C2" t="n">
-        <v>113.142</v>
+        <v>137.921</v>
       </c>
       <c r="D2" t="n">
-        <v>20.077</v>
+        <v>22.663</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.901999999999999</v>
+        <v>9.912000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>120.136</v>
+        <v>146.554</v>
       </c>
       <c r="D3" t="n">
-        <v>20.97</v>
+        <v>23.792</v>
       </c>
     </row>
     <row r="4">
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.909000000000001</v>
+        <v>9.917</v>
       </c>
       <c r="C4" t="n">
-        <v>126.386</v>
+        <v>148.977</v>
       </c>
       <c r="D4" t="n">
-        <v>21.811</v>
+        <v>24.627</v>
       </c>
     </row>
     <row r="5">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.441</v>
+        <v>10.494</v>
       </c>
       <c r="C5" t="n">
-        <v>130.989</v>
+        <v>149.976</v>
       </c>
       <c r="D5" t="n">
-        <v>23.079</v>
+        <v>26.414</v>
       </c>
     </row>
     <row r="6">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.138</v>
+        <v>10.219</v>
       </c>
       <c r="C6" t="n">
-        <v>139.007</v>
+        <v>136.847</v>
       </c>
       <c r="D6" t="n">
-        <v>23.651</v>
+        <v>25.633</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.696</v>
+        <v>10.8</v>
       </c>
       <c r="C7" t="n">
-        <v>131.865</v>
+        <v>127.452</v>
       </c>
       <c r="D7" t="n">
-        <v>23.147</v>
+        <v>25.477</v>
       </c>
     </row>
     <row r="8">
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.322</v>
+        <v>12.437</v>
       </c>
       <c r="C8" t="n">
-        <v>121.08</v>
+        <v>133.1</v>
       </c>
       <c r="D8" t="n">
-        <v>24.642</v>
+        <v>29.187</v>
       </c>
     </row>
     <row r="9">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.801</v>
+        <v>11.861</v>
       </c>
       <c r="C9" t="n">
-        <v>118.037</v>
+        <v>134.245</v>
       </c>
       <c r="D9" t="n">
-        <v>23.462</v>
+        <v>27.338</v>
       </c>
     </row>
     <row r="10">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.397</v>
+        <v>9.364000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>129.734</v>
+        <v>136.366</v>
       </c>
       <c r="D10" t="n">
-        <v>21.441</v>
+        <v>22.608</v>
       </c>
     </row>
     <row r="11">
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.529</v>
+        <v>9.456</v>
       </c>
       <c r="C11" t="n">
-        <v>125.465</v>
+        <v>131.087</v>
       </c>
       <c r="D11" t="n">
-        <v>20.149</v>
+        <v>20.629</v>
       </c>
     </row>
     <row r="12">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10.003</v>
+        <v>9.961</v>
       </c>
       <c r="C12" t="n">
-        <v>130.955</v>
+        <v>134.879</v>
       </c>
       <c r="D12" t="n">
-        <v>21.042</v>
+        <v>22.025</v>
       </c>
     </row>
     <row r="13">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9.949</v>
+        <v>9.933</v>
       </c>
       <c r="C13" t="n">
-        <v>122.456</v>
+        <v>117.115</v>
       </c>
       <c r="D13" t="n">
-        <v>20.592</v>
+        <v>21.118</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.736000000000001</v>
+        <v>8.709</v>
       </c>
       <c r="C14" t="n">
-        <v>116.768</v>
+        <v>103.651</v>
       </c>
       <c r="D14" t="n">
-        <v>18.357</v>
+        <v>18.364</v>
       </c>
     </row>
     <row r="15">
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.372999999999999</v>
+        <v>9.295999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>106.85</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>19.079</v>
+        <v>17.798</v>
       </c>
     </row>
     <row r="16">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9.813000000000001</v>
+        <v>9.771000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>117.093</v>
+        <v>114.233</v>
       </c>
       <c r="D16" t="n">
-        <v>21.382</v>
+        <v>21.483</v>
       </c>
     </row>
     <row r="17">
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11.692</v>
+        <v>11.709</v>
       </c>
       <c r="C17" t="n">
-        <v>121.201</v>
+        <v>119.858</v>
       </c>
       <c r="D17" t="n">
-        <v>23.423</v>
+        <v>25.026</v>
       </c>
     </row>
     <row r="18">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11.623</v>
+        <v>11.717</v>
       </c>
       <c r="C18" t="n">
-        <v>120.82</v>
+        <v>116.18</v>
       </c>
       <c r="D18" t="n">
-        <v>22.054</v>
+        <v>25.203</v>
       </c>
     </row>
     <row r="19">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.179</v>
+        <v>10.278</v>
       </c>
       <c r="C19" t="n">
-        <v>123.245</v>
+        <v>110.463</v>
       </c>
       <c r="D19" t="n">
-        <v>20.731</v>
+        <v>21.349</v>
       </c>
     </row>
     <row r="20">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.045</v>
+        <v>9.089</v>
       </c>
       <c r="C20" t="n">
-        <v>125.411</v>
+        <v>112.545</v>
       </c>
       <c r="D20" t="n">
-        <v>19.744</v>
+        <v>19.457</v>
       </c>
     </row>
     <row r="21">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.993</v>
+        <v>9.932</v>
       </c>
       <c r="C21" t="n">
-        <v>128.514</v>
+        <v>123.68</v>
       </c>
       <c r="D21" t="n">
-        <v>19.654</v>
+        <v>20.089</v>
       </c>
     </row>
     <row r="22">
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10.622</v>
+        <v>10.577</v>
       </c>
       <c r="C22" t="n">
-        <v>120.618</v>
+        <v>120.736</v>
       </c>
       <c r="D22" t="n">
-        <v>19.55</v>
+        <v>21.331</v>
       </c>
     </row>
     <row r="23">
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10.194</v>
+        <v>10.236</v>
       </c>
       <c r="C23" t="n">
-        <v>117.358</v>
+        <v>117.017</v>
       </c>
       <c r="D23" t="n">
-        <v>20.105</v>
+        <v>22.004</v>
       </c>
     </row>
     <row r="24">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10.057</v>
+        <v>10.093</v>
       </c>
       <c r="C24" t="n">
-        <v>121.429</v>
+        <v>119.764</v>
       </c>
       <c r="D24" t="n">
-        <v>22.067</v>
+        <v>23.934</v>
       </c>
     </row>
     <row r="25">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10.594</v>
+        <v>10.62</v>
       </c>
       <c r="C25" t="n">
-        <v>122.003</v>
+        <v>125.128</v>
       </c>
       <c r="D25" t="n">
-        <v>23.105</v>
+        <v>25.722</v>
       </c>
     </row>
     <row r="26">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11.524</v>
+        <v>11.552</v>
       </c>
       <c r="C26" t="n">
-        <v>116.435</v>
+        <v>124.012</v>
       </c>
       <c r="D26" t="n">
-        <v>23.667</v>
+        <v>26.656</v>
       </c>
     </row>
     <row r="27">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.02</v>
+        <v>12.077</v>
       </c>
       <c r="C27" t="n">
-        <v>109.886</v>
+        <v>116.559</v>
       </c>
       <c r="D27" t="n">
-        <v>23.551</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="28">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12.417</v>
+        <v>12.38</v>
       </c>
       <c r="C28" t="n">
-        <v>116.022</v>
+        <v>123.708</v>
       </c>
       <c r="D28" t="n">
-        <v>24.024</v>
+        <v>26.638</v>
       </c>
     </row>
     <row r="29">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12.375</v>
+        <v>12.315</v>
       </c>
       <c r="C29" t="n">
-        <v>124.285</v>
+        <v>128.624</v>
       </c>
       <c r="D29" t="n">
-        <v>23.672</v>
+        <v>26.376</v>
       </c>
     </row>
     <row r="30">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10.926</v>
+        <v>10.863</v>
       </c>
       <c r="C30" t="n">
-        <v>132.606</v>
+        <v>137.4</v>
       </c>
       <c r="D30" t="n">
-        <v>22.593</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="31">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9.141</v>
+        <v>9.085000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>136.367</v>
+        <v>142.654</v>
       </c>
       <c r="D31" t="n">
-        <v>21.087</v>
+        <v>22.161</v>
       </c>
     </row>
     <row r="32">
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9.720000000000001</v>
+        <v>9.728999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>126.741</v>
+        <v>131.221</v>
       </c>
       <c r="D32" t="n">
-        <v>21.274</v>
+        <v>22.662</v>
       </c>
     </row>
     <row r="33">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>12.317</v>
+        <v>12.395</v>
       </c>
       <c r="C33" t="n">
-        <v>106.257</v>
+        <v>102.574</v>
       </c>
       <c r="D33" t="n">
-        <v>21.92</v>
+        <v>23.586</v>
       </c>
     </row>
     <row r="34">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12.174</v>
+        <v>12.288</v>
       </c>
       <c r="C34" t="n">
-        <v>107.657</v>
+        <v>103.962</v>
       </c>
       <c r="D34" t="n">
-        <v>21.885</v>
+        <v>24.97</v>
       </c>
     </row>
     <row r="35">
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11.314</v>
+        <v>11.34</v>
       </c>
       <c r="C35" t="n">
-        <v>121.091</v>
+        <v>113.384</v>
       </c>
       <c r="D35" t="n">
-        <v>21.464</v>
+        <v>23.718</v>
       </c>
     </row>
     <row r="36">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10.419</v>
+        <v>10.338</v>
       </c>
       <c r="C36" t="n">
-        <v>123.535</v>
+        <v>120.291</v>
       </c>
       <c r="D36" t="n">
-        <v>19.408</v>
+        <v>21.677</v>
       </c>
     </row>
     <row r="37">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10.689</v>
+        <v>10.595</v>
       </c>
       <c r="C37" t="n">
-        <v>106.037</v>
+        <v>106.443</v>
       </c>
       <c r="D37" t="n">
-        <v>16.566</v>
+        <v>17.275</v>
       </c>
     </row>
     <row r="38">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10.187</v>
+        <v>10.112</v>
       </c>
       <c r="C38" t="n">
-        <v>104.723</v>
+        <v>107.756</v>
       </c>
       <c r="D38" t="n">
-        <v>17.445</v>
+        <v>17.949</v>
       </c>
     </row>
     <row r="39">
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10.626</v>
+        <v>10.56</v>
       </c>
       <c r="C39" t="n">
-        <v>112.957</v>
+        <v>104.111</v>
       </c>
       <c r="D39" t="n">
-        <v>21.184</v>
+        <v>20.366</v>
       </c>
     </row>
     <row r="40">
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>11.292</v>
+        <v>11.115</v>
       </c>
       <c r="C40" t="n">
-        <v>109.426</v>
+        <v>101.733</v>
       </c>
       <c r="D40" t="n">
-        <v>21.724</v>
+        <v>20.933</v>
       </c>
     </row>
     <row r="41">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>11.746</v>
+        <v>11.601</v>
       </c>
       <c r="C41" t="n">
-        <v>93.15300000000001</v>
+        <v>95.905</v>
       </c>
       <c r="D41" t="n">
-        <v>18.825</v>
+        <v>17.936</v>
       </c>
     </row>
     <row r="42">
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10.542</v>
+        <v>10.503</v>
       </c>
       <c r="C42" t="n">
-        <v>98.85299999999999</v>
+        <v>103.49</v>
       </c>
       <c r="D42" t="n">
-        <v>17.775</v>
+        <v>17.624</v>
       </c>
     </row>
     <row r="43">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>8.316000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="C43" t="n">
-        <v>107.188</v>
+        <v>109.001</v>
       </c>
       <c r="D43" t="n">
-        <v>15.787</v>
+        <v>16.716</v>
       </c>
     </row>
     <row r="44">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7.319</v>
+        <v>7.441</v>
       </c>
       <c r="C44" t="n">
-        <v>113.899</v>
+        <v>111.629</v>
       </c>
       <c r="D44" t="n">
-        <v>15.516</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="45">
@@ -1133,13 +1133,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7.474</v>
+        <v>7.567</v>
       </c>
       <c r="C45" t="n">
-        <v>118.207</v>
+        <v>114.781</v>
       </c>
       <c r="D45" t="n">
-        <v>16.549</v>
+        <v>15.743</v>
       </c>
     </row>
     <row r="46">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6.908</v>
+        <v>6.949</v>
       </c>
       <c r="C46" t="n">
-        <v>125.857</v>
+        <v>120.574</v>
       </c>
       <c r="D46" t="n">
-        <v>16.794</v>
+        <v>15.466</v>
       </c>
     </row>
     <row r="47">
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>8.412000000000001</v>
+        <v>8.427</v>
       </c>
       <c r="C47" t="n">
-        <v>119.74</v>
+        <v>112.056</v>
       </c>
       <c r="D47" t="n">
-        <v>17.696</v>
+        <v>17.464</v>
       </c>
     </row>
     <row r="48">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>8.698</v>
+        <v>8.694000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>114.403</v>
+        <v>107.211</v>
       </c>
       <c r="D48" t="n">
-        <v>17.03</v>
+        <v>16.941</v>
       </c>
     </row>
     <row r="49">
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8.273</v>
+        <v>8.249000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>119.179</v>
+        <v>117.79</v>
       </c>
       <c r="D49" t="n">
-        <v>16.318</v>
+        <v>16.671</v>
       </c>
     </row>
     <row r="50">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8.238</v>
+        <v>8.170999999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>121.494</v>
+        <v>125.548</v>
       </c>
       <c r="D50" t="n">
-        <v>17.433</v>
+        <v>17.428</v>
       </c>
     </row>
     <row r="51">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>9.239000000000001</v>
+        <v>9.176</v>
       </c>
       <c r="C51" t="n">
-        <v>128.045</v>
+        <v>126.48</v>
       </c>
       <c r="D51" t="n">
-        <v>19.424</v>
+        <v>19.277</v>
       </c>
     </row>
     <row r="52">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>9.291</v>
+        <v>9.186</v>
       </c>
       <c r="C52" t="n">
-        <v>120.935</v>
+        <v>117.373</v>
       </c>
       <c r="D52" t="n">
-        <v>19.282</v>
+        <v>18.825</v>
       </c>
     </row>
     <row r="53">
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>9.493</v>
+        <v>9.427</v>
       </c>
       <c r="C53" t="n">
-        <v>111.333</v>
+        <v>108.419</v>
       </c>
       <c r="D53" t="n">
-        <v>18.119</v>
+        <v>17.365</v>
       </c>
     </row>
     <row r="54">
@@ -1277,13 +1277,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10.812</v>
+        <v>10.817</v>
       </c>
       <c r="C54" t="n">
-        <v>107.033</v>
+        <v>105.123</v>
       </c>
       <c r="D54" t="n">
-        <v>20.934</v>
+        <v>20.463</v>
       </c>
     </row>
     <row r="55">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10.766</v>
+        <v>10.811</v>
       </c>
       <c r="C55" t="n">
-        <v>109.56</v>
+        <v>107.915</v>
       </c>
       <c r="D55" t="n">
-        <v>20.33</v>
+        <v>19.809</v>
       </c>
     </row>
     <row r="56">
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10.501</v>
+        <v>10.498</v>
       </c>
       <c r="C56" t="n">
-        <v>109.307</v>
+        <v>107.373</v>
       </c>
       <c r="D56" t="n">
-        <v>20.101</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="57">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10.611</v>
+        <v>10.608</v>
       </c>
       <c r="C57" t="n">
-        <v>109.628</v>
+        <v>103.546</v>
       </c>
       <c r="D57" t="n">
-        <v>20.415</v>
+        <v>18.957</v>
       </c>
     </row>
     <row r="58">
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10.847</v>
+        <v>10.873</v>
       </c>
       <c r="C58" t="n">
-        <v>110.909</v>
+        <v>101.84</v>
       </c>
       <c r="D58" t="n">
-        <v>21.308</v>
+        <v>20.092</v>
       </c>
     </row>
     <row r="59">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10.786</v>
+        <v>10.813</v>
       </c>
       <c r="C59" t="n">
-        <v>110.944</v>
+        <v>102.426</v>
       </c>
       <c r="D59" t="n">
-        <v>21.126</v>
+        <v>19.878</v>
       </c>
     </row>
     <row r="60">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10.512</v>
+        <v>10.556</v>
       </c>
       <c r="C60" t="n">
-        <v>112.507</v>
+        <v>103.716</v>
       </c>
       <c r="D60" t="n">
-        <v>21.083</v>
+        <v>19.835</v>
       </c>
     </row>
     <row r="61">
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>11.239</v>
+        <v>11.259</v>
       </c>
       <c r="C61" t="n">
-        <v>107.694</v>
+        <v>98.956</v>
       </c>
       <c r="D61" t="n">
-        <v>21.112</v>
+        <v>19.581</v>
       </c>
     </row>
     <row r="62">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>12.687</v>
+        <v>12.704</v>
       </c>
       <c r="C62" t="n">
-        <v>98.651</v>
+        <v>95.241</v>
       </c>
       <c r="D62" t="n">
-        <v>20.732</v>
+        <v>20.006</v>
       </c>
     </row>
     <row r="63">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>13.601</v>
+        <v>13.624</v>
       </c>
       <c r="C63" t="n">
-        <v>92.977</v>
+        <v>91.17100000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>20.655</v>
+        <v>20.014</v>
       </c>
     </row>
     <row r="64">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>13.536</v>
+        <v>13.609</v>
       </c>
       <c r="C64" t="n">
-        <v>93.571</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="D64" t="n">
-        <v>20.469</v>
+        <v>20.303</v>
       </c>
     </row>
     <row r="65">
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>13.91</v>
+        <v>14.003</v>
       </c>
       <c r="C65" t="n">
-        <v>91.858</v>
+        <v>93.07299999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>20.635</v>
+        <v>20.534</v>
       </c>
     </row>
     <row r="66">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>12.847</v>
+        <v>12.916</v>
       </c>
       <c r="C66" t="n">
-        <v>95.946</v>
+        <v>96.86499999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>19.322</v>
+        <v>20.307</v>
       </c>
     </row>
     <row r="67">
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>11.147</v>
+        <v>11.124</v>
       </c>
       <c r="C67" t="n">
-        <v>105.174</v>
+        <v>109.899</v>
       </c>
       <c r="D67" t="n">
-        <v>18.686</v>
+        <v>19.913</v>
       </c>
     </row>
     <row r="68">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>10.157</v>
+        <v>10.056</v>
       </c>
       <c r="C68" t="n">
-        <v>111.933</v>
+        <v>116.088</v>
       </c>
       <c r="D68" t="n">
-        <v>18.496</v>
+        <v>19.596</v>
       </c>
     </row>
     <row r="69">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>10.725</v>
+        <v>10.594</v>
       </c>
       <c r="C69" t="n">
-        <v>111.034</v>
+        <v>112.206</v>
       </c>
       <c r="D69" t="n">
-        <v>19.12</v>
+        <v>19.621</v>
       </c>
     </row>
     <row r="70">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>10.749</v>
+        <v>10.629</v>
       </c>
       <c r="C70" t="n">
-        <v>112.184</v>
+        <v>101.692</v>
       </c>
       <c r="D70" t="n">
-        <v>19.142</v>
+        <v>19.058</v>
       </c>
     </row>
     <row r="71">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>10.224</v>
+        <v>10.143</v>
       </c>
       <c r="C71" t="n">
-        <v>107.597</v>
+        <v>108.748</v>
       </c>
       <c r="D71" t="n">
-        <v>18.062</v>
+        <v>18.724</v>
       </c>
     </row>
     <row r="72">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>9.548</v>
+        <v>9.494999999999999</v>
       </c>
       <c r="C72" t="n">
-        <v>102.173</v>
+        <v>116.786</v>
       </c>
       <c r="D72" t="n">
-        <v>16.609</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="73">
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>9.114000000000001</v>
+        <v>9.045999999999999</v>
       </c>
       <c r="C73" t="n">
-        <v>98.86799999999999</v>
+        <v>122.125</v>
       </c>
       <c r="D73" t="n">
-        <v>15.637</v>
+        <v>17.873</v>
       </c>
     </row>
     <row r="74">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>9.221</v>
+        <v>9.147</v>
       </c>
       <c r="C74" t="n">
-        <v>100.952</v>
+        <v>120.373</v>
       </c>
       <c r="D74" t="n">
-        <v>15.907</v>
+        <v>17.978</v>
       </c>
     </row>
     <row r="75">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>9.27</v>
+        <v>9.199</v>
       </c>
       <c r="C75" t="n">
-        <v>99.669</v>
+        <v>118.95</v>
       </c>
       <c r="D75" t="n">
-        <v>15.87</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="76">
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>9.103</v>
+        <v>9.052</v>
       </c>
       <c r="C76" t="n">
-        <v>104.757</v>
+        <v>121.932</v>
       </c>
       <c r="D76" t="n">
-        <v>16.066</v>
+        <v>18.026</v>
       </c>
     </row>
     <row r="77">
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>8.847</v>
+        <v>8.808</v>
       </c>
       <c r="C77" t="n">
-        <v>111.71</v>
+        <v>126.153</v>
       </c>
       <c r="D77" t="n">
-        <v>16.33</v>
+        <v>18.419</v>
       </c>
     </row>
     <row r="78">
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>8.65</v>
+        <v>8.622</v>
       </c>
       <c r="C78" t="n">
-        <v>116.676</v>
+        <v>129.223</v>
       </c>
       <c r="D78" t="n">
-        <v>16.442</v>
+        <v>18.781</v>
       </c>
     </row>
     <row r="79">
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>8.666</v>
+        <v>8.645</v>
       </c>
       <c r="C79" t="n">
-        <v>115.657</v>
+        <v>128.492</v>
       </c>
       <c r="D79" t="n">
-        <v>16.315</v>
+        <v>18.723</v>
       </c>
     </row>
     <row r="80">
@@ -1693,13 +1693,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>8.759</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="C80" t="n">
-        <v>113.921</v>
+        <v>126.332</v>
       </c>
       <c r="D80" t="n">
-        <v>16.031</v>
+        <v>18.616</v>
       </c>
     </row>
     <row r="81">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>8.253</v>
+        <v>8.252000000000001</v>
       </c>
       <c r="C81" t="n">
-        <v>121.288</v>
+        <v>135.613</v>
       </c>
       <c r="D81" t="n">
-        <v>16.935</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="82">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7.555</v>
+        <v>7.563</v>
       </c>
       <c r="C82" t="n">
-        <v>132.317</v>
+        <v>148.069</v>
       </c>
       <c r="D82" t="n">
-        <v>18.132</v>
+        <v>19.815</v>
       </c>
     </row>
     <row r="83">
@@ -1744,10 +1744,10 @@
         <v>7.153</v>
       </c>
       <c r="C83" t="n">
-        <v>139.709</v>
+        <v>156.183</v>
       </c>
       <c r="D83" t="n">
-        <v>18.962</v>
+        <v>20.123</v>
       </c>
     </row>
     <row r="84">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>7.298</v>
+        <v>7.287</v>
       </c>
       <c r="C84" t="n">
-        <v>138.594</v>
+        <v>153.96</v>
       </c>
       <c r="D84" t="n">
-        <v>18.713</v>
+        <v>19.843</v>
       </c>
     </row>
     <row r="85">
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6.9</v>
+        <v>6.876</v>
       </c>
       <c r="C85" t="n">
-        <v>142.807</v>
+        <v>159.575</v>
       </c>
       <c r="D85" t="n">
-        <v>18.588</v>
+        <v>19.677</v>
       </c>
     </row>
     <row r="86">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>8.265000000000001</v>
+        <v>8.343</v>
       </c>
       <c r="C86" t="n">
-        <v>128.84</v>
+        <v>138.955</v>
       </c>
       <c r="D86" t="n">
-        <v>18.999</v>
+        <v>20.424</v>
       </c>
     </row>
     <row r="87">
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>10.331</v>
+        <v>10.533</v>
       </c>
       <c r="C87" t="n">
-        <v>106.947</v>
+        <v>109.076</v>
       </c>
       <c r="D87" t="n">
-        <v>19.402</v>
+        <v>21.572</v>
       </c>
     </row>
     <row r="88">
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>11.759</v>
+        <v>12.046</v>
       </c>
       <c r="C88" t="n">
-        <v>92.53</v>
+        <v>89.434</v>
       </c>
       <c r="D88" t="n">
-        <v>19.857</v>
+        <v>22.687</v>
       </c>
     </row>
     <row r="89">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>11.399</v>
+        <v>11.663</v>
       </c>
       <c r="C89" t="n">
-        <v>96.352</v>
+        <v>95.245</v>
       </c>
       <c r="D89" t="n">
-        <v>19.779</v>
+        <v>22.635</v>
       </c>
     </row>
     <row r="90">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>11.574</v>
+        <v>11.853</v>
       </c>
       <c r="C90" t="n">
-        <v>95.82599999999999</v>
+        <v>93.53700000000001</v>
       </c>
       <c r="D90" t="n">
-        <v>19.996</v>
+        <v>22.439</v>
       </c>
     </row>
     <row r="91">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>10.845</v>
+        <v>11.094</v>
       </c>
       <c r="C91" t="n">
-        <v>97.996</v>
+        <v>96.437</v>
       </c>
       <c r="D91" t="n">
-        <v>19.047</v>
+        <v>21.419</v>
       </c>
     </row>
     <row r="92">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>9.805999999999999</v>
+        <v>10.002</v>
       </c>
       <c r="C92" t="n">
-        <v>102.085</v>
+        <v>101.61</v>
       </c>
       <c r="D92" t="n">
-        <v>17.973</v>
+        <v>20.524</v>
       </c>
     </row>
     <row r="93">
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>9.071999999999999</v>
+        <v>9.227</v>
       </c>
       <c r="C93" t="n">
-        <v>104.917</v>
+        <v>105.05</v>
       </c>
       <c r="D93" t="n">
-        <v>17.265</v>
+        <v>20.027</v>
       </c>
     </row>
     <row r="94">
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>9.273999999999999</v>
+        <v>9.433</v>
       </c>
       <c r="C94" t="n">
-        <v>103.653</v>
+        <v>104.308</v>
       </c>
       <c r="D94" t="n">
-        <v>17.333</v>
+        <v>20.033</v>
       </c>
     </row>
     <row r="95">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>8.789999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="C95" t="n">
-        <v>104.698</v>
+        <v>107.333</v>
       </c>
       <c r="D95" t="n">
-        <v>17.012</v>
+        <v>19.829</v>
       </c>
     </row>
     <row r="96">
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>10.923</v>
+        <v>11.021</v>
       </c>
       <c r="C96" t="n">
-        <v>98.59</v>
+        <v>101.31</v>
       </c>
       <c r="D96" t="n">
-        <v>18.061</v>
+        <v>19.958</v>
       </c>
     </row>
     <row r="97">
@@ -1965,13 +1965,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13.931</v>
+        <v>13.949</v>
       </c>
       <c r="C97" t="n">
-        <v>90.02500000000001</v>
+        <v>91.46899999999999</v>
       </c>
       <c r="D97" t="n">
-        <v>19.588</v>
+        <v>20.271</v>
       </c>
     </row>
     <row r="98">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>16.099</v>
+        <v>16.053</v>
       </c>
       <c r="C98" t="n">
-        <v>83.58</v>
+        <v>84.458</v>
       </c>
       <c r="D98" t="n">
-        <v>20.539</v>
+        <v>20.432</v>
       </c>
     </row>
     <row r="99">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>15.651</v>
+        <v>15.604</v>
       </c>
       <c r="C99" t="n">
-        <v>84.57599999999999</v>
+        <v>84.986</v>
       </c>
       <c r="D99" t="n">
-        <v>20.235</v>
+        <v>20.326</v>
       </c>
     </row>
     <row r="100">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>15.897</v>
+        <v>15.87</v>
       </c>
       <c r="C100" t="n">
-        <v>83.033</v>
+        <v>81.759</v>
       </c>
       <c r="D100" t="n">
-        <v>20.073</v>
+        <v>19.948</v>
       </c>
     </row>
     <row r="101">
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>14.947</v>
+        <v>14.913</v>
       </c>
       <c r="C101" t="n">
-        <v>88.494</v>
+        <v>88.545</v>
       </c>
       <c r="D101" t="n">
-        <v>20.88</v>
+        <v>21.351</v>
       </c>
     </row>
     <row r="102">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>13.62</v>
+        <v>13.566</v>
       </c>
       <c r="C102" t="n">
-        <v>96.634</v>
+        <v>99.294</v>
       </c>
       <c r="D102" t="n">
-        <v>22.041</v>
+        <v>23.431</v>
       </c>
     </row>
     <row r="103">
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>12.7</v>
+        <v>12.63</v>
       </c>
       <c r="C103" t="n">
-        <v>102.544</v>
+        <v>106.97</v>
       </c>
       <c r="D103" t="n">
-        <v>22.883</v>
+        <v>25.107</v>
       </c>
     </row>
     <row r="104">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>12.933</v>
+        <v>12.865</v>
       </c>
       <c r="C104" t="n">
-        <v>101.532</v>
+        <v>105.324</v>
       </c>
       <c r="D104" t="n">
-        <v>22.762</v>
+        <v>24.961</v>
       </c>
     </row>
     <row r="105">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>13.152</v>
+        <v>13.086</v>
       </c>
       <c r="C105" t="n">
-        <v>100.26</v>
+        <v>104.298</v>
       </c>
       <c r="D105" t="n">
-        <v>22.951</v>
+        <v>25.221</v>
       </c>
     </row>
     <row r="106">
@@ -2109,13 +2109,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>12.258</v>
+        <v>12.198</v>
       </c>
       <c r="C106" t="n">
-        <v>105.654</v>
+        <v>108.245</v>
       </c>
       <c r="D106" t="n">
-        <v>22.249</v>
+        <v>23.989</v>
       </c>
     </row>
     <row r="107">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>11</v>
+        <v>10.942</v>
       </c>
       <c r="C107" t="n">
-        <v>113.376</v>
+        <v>113.976</v>
       </c>
       <c r="D107" t="n">
-        <v>21.26</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="108">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>10.121</v>
+        <v>10.064</v>
       </c>
       <c r="C108" t="n">
-        <v>118.797</v>
+        <v>117.989</v>
       </c>
       <c r="D108" t="n">
-        <v>20.58</v>
+        <v>21.305</v>
       </c>
     </row>
     <row r="109">
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>10.356</v>
+        <v>10.299</v>
       </c>
       <c r="C109" t="n">
-        <v>117.299</v>
+        <v>116.97</v>
       </c>
       <c r="D109" t="n">
-        <v>20.751</v>
+        <v>21.591</v>
       </c>
     </row>
     <row r="110">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>10.199</v>
+        <v>10.153</v>
       </c>
       <c r="C110" t="n">
-        <v>119.305</v>
+        <v>118.551</v>
       </c>
       <c r="D110" t="n">
-        <v>20.908</v>
+        <v>21.648</v>
       </c>
     </row>
     <row r="111">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>10.81</v>
+        <v>10.719</v>
       </c>
       <c r="C111" t="n">
-        <v>111.372</v>
+        <v>112.222</v>
       </c>
       <c r="D111" t="n">
-        <v>20.34</v>
+        <v>21.433</v>
       </c>
     </row>
     <row r="112">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>11.686</v>
+        <v>11.537</v>
       </c>
       <c r="C112" t="n">
-        <v>100.116</v>
+        <v>103.793</v>
       </c>
       <c r="D112" t="n">
-        <v>19.532</v>
+        <v>21.279</v>
       </c>
     </row>
     <row r="113">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>12.317</v>
+        <v>12.151</v>
       </c>
       <c r="C113" t="n">
-        <v>91.84</v>
+        <v>97.693</v>
       </c>
       <c r="D113" t="n">
-        <v>18.931</v>
+        <v>21.201</v>
       </c>
     </row>
     <row r="114">
@@ -2237,13 +2237,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>12.215</v>
+        <v>12.089</v>
       </c>
       <c r="C114" t="n">
-        <v>93.705</v>
+        <v>99.29900000000001</v>
       </c>
       <c r="D114" t="n">
-        <v>19.063</v>
+        <v>21.345</v>
       </c>
     </row>
     <row r="115">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>12.405</v>
+        <v>12.265</v>
       </c>
       <c r="C115" t="n">
-        <v>92.416</v>
+        <v>97.697</v>
       </c>
       <c r="D115" t="n">
-        <v>19.058</v>
+        <v>21.397</v>
       </c>
     </row>
     <row r="116">
@@ -2269,13 +2269,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>11.879</v>
+        <v>11.861</v>
       </c>
       <c r="C116" t="n">
-        <v>95.54000000000001</v>
+        <v>102.47</v>
       </c>
       <c r="D116" t="n">
-        <v>18.929</v>
+        <v>21.199</v>
       </c>
     </row>
     <row r="117">
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>11.112</v>
+        <v>11.258</v>
       </c>
       <c r="C117" t="n">
-        <v>100.065</v>
+        <v>109.174</v>
       </c>
       <c r="D117" t="n">
-        <v>18.774</v>
+        <v>20.827</v>
       </c>
     </row>
     <row r="118">
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>10.374</v>
+        <v>10.601</v>
       </c>
       <c r="C118" t="n">
-        <v>103.742</v>
+        <v>114.263</v>
       </c>
       <c r="D118" t="n">
-        <v>18.366</v>
+        <v>20.367</v>
       </c>
     </row>
     <row r="119">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>10.383</v>
+        <v>10.556</v>
       </c>
       <c r="C119" t="n">
-        <v>103.098</v>
+        <v>113.277</v>
       </c>
       <c r="D119" t="n">
-        <v>18.234</v>
+        <v>20.362</v>
       </c>
     </row>
     <row r="120">
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>10.625</v>
+        <v>10.809</v>
       </c>
       <c r="C120" t="n">
-        <v>102.726</v>
+        <v>112.75</v>
       </c>
       <c r="D120" t="n">
-        <v>18.745</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="121">
@@ -2349,13 +2349,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>10.611</v>
+        <v>10.758</v>
       </c>
       <c r="C121" t="n">
-        <v>103.614</v>
+        <v>112.103</v>
       </c>
       <c r="D121" t="n">
-        <v>18.936</v>
+        <v>20.845</v>
       </c>
     </row>
     <row r="122">
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>10.238</v>
+        <v>10.31</v>
       </c>
       <c r="C122" t="n">
-        <v>105.178</v>
+        <v>111.751</v>
       </c>
       <c r="D122" t="n">
-        <v>18.518</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="123">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>9.845000000000001</v>
+        <v>9.874000000000001</v>
       </c>
       <c r="C123" t="n">
-        <v>106.587</v>
+        <v>112.34</v>
       </c>
       <c r="D123" t="n">
-        <v>18.012</v>
+        <v>20.648</v>
       </c>
     </row>
     <row r="124">
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>9.927</v>
+        <v>9.965999999999999</v>
       </c>
       <c r="C124" t="n">
-        <v>106.373</v>
+        <v>112.504</v>
       </c>
       <c r="D124" t="n">
-        <v>18.14</v>
+        <v>20.697</v>
       </c>
     </row>
     <row r="125">
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>9.888999999999999</v>
+        <v>9.952999999999999</v>
       </c>
       <c r="C125" t="n">
-        <v>105.268</v>
+        <v>111.518</v>
       </c>
       <c r="D125" t="n">
-        <v>18.01</v>
+        <v>20.731</v>
       </c>
     </row>
     <row r="126">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>10.369</v>
+        <v>10.395</v>
       </c>
       <c r="C126" t="n">
-        <v>109.174</v>
+        <v>115.594</v>
       </c>
       <c r="D126" t="n">
-        <v>18.817</v>
+        <v>20.961</v>
       </c>
     </row>
     <row r="127">
@@ -2445,13 +2445,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>10.946</v>
+        <v>10.901</v>
       </c>
       <c r="C127" t="n">
-        <v>114.896</v>
+        <v>121.856</v>
       </c>
       <c r="D127" t="n">
-        <v>19.863</v>
+        <v>21.229</v>
       </c>
     </row>
     <row r="128">
@@ -2461,13 +2461,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>11.255</v>
+        <v>11.182</v>
       </c>
       <c r="C128" t="n">
-        <v>119.112</v>
+        <v>126.14</v>
       </c>
       <c r="D128" t="n">
-        <v>20.523</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="129">
@@ -2477,13 +2477,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>11.134</v>
+        <v>11.081</v>
       </c>
       <c r="C129" t="n">
-        <v>117.974</v>
+        <v>125.05</v>
       </c>
       <c r="D129" t="n">
-        <v>20.307</v>
+        <v>21.295</v>
       </c>
     </row>
     <row r="130">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>11.05</v>
+        <v>10.967</v>
       </c>
       <c r="C130" t="n">
-        <v>119.569</v>
+        <v>127.238</v>
       </c>
       <c r="D130" t="n">
-        <v>20.319</v>
+        <v>21.375</v>
       </c>
     </row>
     <row r="131">
@@ -2509,13 +2509,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>11.521</v>
+        <v>11.492</v>
       </c>
       <c r="C131" t="n">
-        <v>112.694</v>
+        <v>118.294</v>
       </c>
       <c r="D131" t="n">
-        <v>20.457</v>
+        <v>21.297</v>
       </c>
     </row>
     <row r="132">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>12.155</v>
+        <v>12.242</v>
       </c>
       <c r="C132" t="n">
-        <v>103.097</v>
+        <v>105.539</v>
       </c>
       <c r="D132" t="n">
-        <v>20.605</v>
+        <v>21.103</v>
       </c>
     </row>
     <row r="133">
@@ -2541,13 +2541,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>12.537</v>
+        <v>12.707</v>
       </c>
       <c r="C133" t="n">
-        <v>96.169</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="D133" t="n">
-        <v>20.696</v>
+        <v>20.912</v>
       </c>
     </row>
     <row r="134">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>12.436</v>
+        <v>12.588</v>
       </c>
       <c r="C134" t="n">
-        <v>97.687</v>
+        <v>98.932</v>
       </c>
       <c r="D134" t="n">
-        <v>20.652</v>
+        <v>20.937</v>
       </c>
     </row>
     <row r="135">
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>12.429</v>
+        <v>12.604</v>
       </c>
       <c r="C135" t="n">
-        <v>97.291</v>
+        <v>99.331</v>
       </c>
       <c r="D135" t="n">
-        <v>20.626</v>
+        <v>20.897</v>
       </c>
     </row>
     <row r="136">
@@ -2589,13 +2589,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>12.548</v>
+        <v>12.66</v>
       </c>
       <c r="C136" t="n">
-        <v>98.67</v>
+        <v>98.116</v>
       </c>
       <c r="D136" t="n">
-        <v>21.07</v>
+        <v>21.107</v>
       </c>
     </row>
     <row r="137">
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>12.621</v>
+        <v>12.719</v>
       </c>
       <c r="C137" t="n">
-        <v>100.541</v>
+        <v>96.523</v>
       </c>
       <c r="D137" t="n">
-        <v>21.641</v>
+        <v>21.367</v>
       </c>
     </row>
     <row r="138">
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>12.649</v>
+        <v>12.772</v>
       </c>
       <c r="C138" t="n">
-        <v>102.582</v>
+        <v>95.316</v>
       </c>
       <c r="D138" t="n">
-        <v>21.9</v>
+        <v>21.849</v>
       </c>
     </row>
     <row r="139">
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>12.906</v>
+        <v>13.092</v>
       </c>
       <c r="C139" t="n">
-        <v>99.623</v>
+        <v>95.069</v>
       </c>
       <c r="D139" t="n">
-        <v>21.119</v>
+        <v>21.504</v>
       </c>
     </row>
     <row r="140">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>13.465</v>
+        <v>13.665</v>
       </c>
       <c r="C140" t="n">
-        <v>94.849</v>
+        <v>93.13800000000001</v>
       </c>
       <c r="D140" t="n">
-        <v>20.298</v>
+        <v>20.793</v>
       </c>
     </row>
     <row r="141">
@@ -2669,13 +2669,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>13.009</v>
+        <v>13.078</v>
       </c>
       <c r="C141" t="n">
-        <v>97.07599999999999</v>
+        <v>97.413</v>
       </c>
       <c r="D141" t="n">
-        <v>20.346</v>
+        <v>20.718</v>
       </c>
     </row>
     <row r="142">
@@ -2685,13 +2685,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>11.866</v>
+        <v>11.759</v>
       </c>
       <c r="C142" t="n">
-        <v>105.171</v>
+        <v>104.651</v>
       </c>
       <c r="D142" t="n">
-        <v>21.051</v>
+        <v>21.498</v>
       </c>
     </row>
     <row r="143">
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>11.081</v>
+        <v>10.851</v>
       </c>
       <c r="C143" t="n">
-        <v>110.299</v>
+        <v>109.487</v>
       </c>
       <c r="D143" t="n">
-        <v>21.426</v>
+        <v>21.963</v>
       </c>
     </row>
     <row r="144">
@@ -2717,13 +2717,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>11.299</v>
+        <v>11.082</v>
       </c>
       <c r="C144" t="n">
-        <v>108.869</v>
+        <v>108.083</v>
       </c>
       <c r="D144" t="n">
-        <v>21.341</v>
+        <v>21.844</v>
       </c>
     </row>
     <row r="145">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>11.668</v>
+        <v>11.403</v>
       </c>
       <c r="C145" t="n">
-        <v>106.97</v>
+        <v>106.101</v>
       </c>
       <c r="D145" t="n">
-        <v>21.631</v>
+        <v>22.07</v>
       </c>
     </row>
     <row r="146">
@@ -2749,13 +2749,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>10.612</v>
+        <v>10.418</v>
       </c>
       <c r="C146" t="n">
-        <v>112.106</v>
+        <v>113.044</v>
       </c>
       <c r="D146" t="n">
-        <v>20.571</v>
+        <v>21.132</v>
       </c>
     </row>
     <row r="147">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>9.074</v>
+        <v>9.015000000000001</v>
       </c>
       <c r="C147" t="n">
-        <v>116.21</v>
+        <v>122.489</v>
       </c>
       <c r="D147" t="n">
-        <v>18.831</v>
+        <v>19.677</v>
       </c>
     </row>
     <row r="148">
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>8.007</v>
+        <v>8.026</v>
       </c>
       <c r="C148" t="n">
-        <v>121.737</v>
+        <v>134.605</v>
       </c>
       <c r="D148" t="n">
-        <v>17.63</v>
+        <v>18.576</v>
       </c>
     </row>
     <row r="149">
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>8.332000000000001</v>
+        <v>8.327</v>
       </c>
       <c r="C149" t="n">
-        <v>122.577</v>
+        <v>138.958</v>
       </c>
       <c r="D149" t="n">
-        <v>18.021</v>
+        <v>18.743</v>
       </c>
     </row>
     <row r="150">
@@ -2813,13 +2813,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>8.367000000000001</v>
+        <v>8.353</v>
       </c>
       <c r="C150" t="n">
-        <v>124.541</v>
+        <v>132.184</v>
       </c>
       <c r="D150" t="n">
-        <v>18.139</v>
+        <v>18.417</v>
       </c>
     </row>
     <row r="151">
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>8.455</v>
+        <v>8.419</v>
       </c>
       <c r="C151" t="n">
-        <v>120.66</v>
+        <v>123.617</v>
       </c>
       <c r="D151" t="n">
-        <v>17.974</v>
+        <v>18.516</v>
       </c>
     </row>
     <row r="152">
@@ -2845,13 +2845,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>8.507999999999999</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="C152" t="n">
-        <v>119.097</v>
+        <v>123.382</v>
       </c>
       <c r="D152" t="n">
-        <v>17.976</v>
+        <v>18.958</v>
       </c>
     </row>
     <row r="153">
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>8.532999999999999</v>
+        <v>8.488</v>
       </c>
       <c r="C153" t="n">
-        <v>119.087</v>
+        <v>129.848</v>
       </c>
       <c r="D153" t="n">
-        <v>18.196</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="154">
@@ -2877,13 +2877,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>8.510999999999999</v>
+        <v>8.481999999999999</v>
       </c>
       <c r="C154" t="n">
-        <v>120.322</v>
+        <v>129.338</v>
       </c>
       <c r="D154" t="n">
-        <v>18.438</v>
+        <v>19.478</v>
       </c>
     </row>
     <row r="155">
@@ -2893,13 +2893,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>8.535</v>
+        <v>8.484999999999999</v>
       </c>
       <c r="C155" t="n">
-        <v>120.069</v>
+        <v>130.202</v>
       </c>
       <c r="D155" t="n">
-        <v>18.351</v>
+        <v>19.522</v>
       </c>
     </row>
     <row r="156">
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>8.429</v>
+        <v>8.371</v>
       </c>
       <c r="C156" t="n">
-        <v>119.74</v>
+        <v>125.154</v>
       </c>
       <c r="D156" t="n">
-        <v>18.054</v>
+        <v>18.983</v>
       </c>
     </row>
     <row r="157">
@@ -2925,13 +2925,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>8.359</v>
+        <v>8.292</v>
       </c>
       <c r="C157" t="n">
-        <v>118.786</v>
+        <v>118.069</v>
       </c>
       <c r="D157" t="n">
-        <v>17.705</v>
+        <v>18.274</v>
       </c>
     </row>
     <row r="158">
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>8.435</v>
+        <v>8.349</v>
       </c>
       <c r="C158" t="n">
-        <v>117.531</v>
+        <v>113.204</v>
       </c>
       <c r="D158" t="n">
-        <v>17.589</v>
+        <v>17.783</v>
       </c>
     </row>
     <row r="159">
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>8.500999999999999</v>
+        <v>8.375999999999999</v>
       </c>
       <c r="C159" t="n">
-        <v>118.93</v>
+        <v>114.806</v>
       </c>
       <c r="D159" t="n">
-        <v>17.723</v>
+        <v>17.932</v>
       </c>
     </row>
     <row r="160">
@@ -2973,13 +2973,13 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>8.429</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C160" t="n">
-        <v>119.86</v>
+        <v>113.86</v>
       </c>
       <c r="D160" t="n">
-        <v>17.734</v>
+        <v>17.857</v>
       </c>
     </row>
     <row r="161">
@@ -2989,13 +2989,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>8.263999999999999</v>
+        <v>8.164999999999999</v>
       </c>
       <c r="C161" t="n">
-        <v>121.956</v>
+        <v>120.826</v>
       </c>
       <c r="D161" t="n">
-        <v>17.727</v>
+        <v>18.231</v>
       </c>
     </row>
     <row r="162">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>8.157</v>
+        <v>8.090999999999999</v>
       </c>
       <c r="C162" t="n">
-        <v>122.103</v>
+        <v>129.461</v>
       </c>
       <c r="D162" t="n">
-        <v>17.394</v>
+        <v>18.503</v>
       </c>
     </row>
     <row r="163">
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>8.238</v>
+        <v>8.18</v>
       </c>
       <c r="C163" t="n">
-        <v>127.398</v>
+        <v>137.145</v>
       </c>
       <c r="D163" t="n">
-        <v>18.812</v>
+        <v>19.797</v>
       </c>
     </row>
     <row r="164">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>8.281000000000001</v>
+        <v>8.215999999999999</v>
       </c>
       <c r="C164" t="n">
-        <v>127.333</v>
+        <v>135.701</v>
       </c>
       <c r="D164" t="n">
-        <v>18.976</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="165">
@@ -3053,13 +3053,13 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>8.009</v>
+        <v>7.942</v>
       </c>
       <c r="C165" t="n">
-        <v>133.042</v>
+        <v>140.343</v>
       </c>
       <c r="D165" t="n">
-        <v>19.93</v>
+        <v>20.364</v>
       </c>
     </row>
     <row r="166">
@@ -3069,13 +3069,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>9.307</v>
+        <v>9.321</v>
       </c>
       <c r="C166" t="n">
-        <v>117.264</v>
+        <v>124.016</v>
       </c>
       <c r="D166" t="n">
-        <v>18.726</v>
+        <v>20.281</v>
       </c>
     </row>
     <row r="167">
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>10.872</v>
+        <v>11.012</v>
       </c>
       <c r="C167" t="n">
-        <v>99.46899999999999</v>
+        <v>102.674</v>
       </c>
       <c r="D167" t="n">
-        <v>18.277</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="168">
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>11.638</v>
+        <v>11.846</v>
       </c>
       <c r="C168" t="n">
-        <v>85.10899999999999</v>
+        <v>87.017</v>
       </c>
       <c r="D168" t="n">
-        <v>16.83</v>
+        <v>20.694</v>
       </c>
     </row>
     <row r="169">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>11.016</v>
+        <v>11.231</v>
       </c>
       <c r="C169" t="n">
-        <v>90.649</v>
+        <v>91.66</v>
       </c>
       <c r="D169" t="n">
-        <v>17.282</v>
+        <v>20.823</v>
       </c>
     </row>
     <row r="170">
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>10.943</v>
+        <v>11.174</v>
       </c>
       <c r="C170" t="n">
-        <v>88.881</v>
+        <v>90.619</v>
       </c>
       <c r="D170" t="n">
-        <v>16.643</v>
+        <v>20.539</v>
       </c>
     </row>
     <row r="171">
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>11.641</v>
+        <v>11.844</v>
       </c>
       <c r="C171" t="n">
-        <v>92.661</v>
+        <v>93.411</v>
       </c>
       <c r="D171" t="n">
-        <v>18.825</v>
+        <v>21.799</v>
       </c>
     </row>
     <row r="172">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>12.614</v>
+        <v>12.749</v>
       </c>
       <c r="C172" t="n">
-        <v>98.419</v>
+        <v>97.429</v>
       </c>
       <c r="D172" t="n">
-        <v>21.95</v>
+        <v>23.557</v>
       </c>
     </row>
     <row r="173">
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>13.285</v>
+        <v>13.371</v>
       </c>
       <c r="C173" t="n">
-        <v>102.622</v>
+        <v>100.454</v>
       </c>
       <c r="D173" t="n">
-        <v>24.171</v>
+        <v>24.786</v>
       </c>
     </row>
     <row r="174">
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>13.113</v>
+        <v>13.209</v>
       </c>
       <c r="C174" t="n">
-        <v>101.563</v>
+        <v>99.895</v>
       </c>
       <c r="D174" t="n">
-        <v>23.605</v>
+        <v>24.501</v>
       </c>
     </row>
     <row r="175">
@@ -3213,13 +3213,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>13.061</v>
+        <v>13.169</v>
       </c>
       <c r="C175" t="n">
-        <v>103.031</v>
+        <v>101.201</v>
       </c>
       <c r="D175" t="n">
-        <v>24.001</v>
+        <v>24.917</v>
       </c>
     </row>
     <row r="176">
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>13.316</v>
+        <v>13.395</v>
       </c>
       <c r="C176" t="n">
-        <v>97.89100000000001</v>
+        <v>96.593</v>
       </c>
       <c r="D176" t="n">
-        <v>22.494</v>
+        <v>23.325</v>
       </c>
     </row>
     <row r="177">
@@ -3245,13 +3245,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>13.645</v>
+        <v>13.666</v>
       </c>
       <c r="C177" t="n">
-        <v>90.52500000000001</v>
+        <v>90.319</v>
       </c>
       <c r="D177" t="n">
-        <v>20.289</v>
+        <v>21.075</v>
       </c>
     </row>
     <row r="178">
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>13.873</v>
+        <v>13.842</v>
       </c>
       <c r="C178" t="n">
-        <v>85.218</v>
+        <v>85.739</v>
       </c>
       <c r="D178" t="n">
-        <v>18.686</v>
+        <v>19.454</v>
       </c>
     </row>
     <row r="179">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>13.798</v>
+        <v>13.765</v>
       </c>
       <c r="C179" t="n">
-        <v>86.636</v>
+        <v>87.042</v>
       </c>
       <c r="D179" t="n">
-        <v>19.005</v>
+        <v>19.858</v>
       </c>
     </row>
     <row r="180">
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>13.91</v>
+        <v>13.871</v>
       </c>
       <c r="C180" t="n">
-        <v>85.28100000000001</v>
+        <v>86.023</v>
       </c>
       <c r="D180" t="n">
-        <v>18.722</v>
+        <v>19.547</v>
       </c>
     </row>
     <row r="181">
@@ -3309,13 +3309,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>13.446</v>
+        <v>13.416</v>
       </c>
       <c r="C181" t="n">
-        <v>90.145</v>
+        <v>91.614</v>
       </c>
       <c r="D181" t="n">
-        <v>19.706</v>
+        <v>20.978</v>
       </c>
     </row>
     <row r="182">
@@ -3325,13 +3325,13 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>12.805</v>
+        <v>12.78</v>
       </c>
       <c r="C182" t="n">
-        <v>97.148</v>
+        <v>99.22799999999999</v>
       </c>
       <c r="D182" t="n">
-        <v>21.109</v>
+        <v>22.898</v>
       </c>
     </row>
     <row r="183">
@@ -3341,13 +3341,13 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>12.362</v>
+        <v>12.346</v>
       </c>
       <c r="C183" t="n">
-        <v>102.077</v>
+        <v>104.667</v>
       </c>
       <c r="D183" t="n">
-        <v>22.116</v>
+        <v>24.325</v>
       </c>
     </row>
     <row r="184">
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>12.474</v>
+        <v>12.456</v>
       </c>
       <c r="C184" t="n">
-        <v>100.934</v>
+        <v>104.144</v>
       </c>
       <c r="D184" t="n">
-        <v>21.916</v>
+        <v>24.134</v>
       </c>
     </row>
     <row r="185">
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>12.829</v>
+        <v>12.823</v>
       </c>
       <c r="C185" t="n">
-        <v>99.65300000000001</v>
+        <v>102.756</v>
       </c>
       <c r="D185" t="n">
-        <v>22.387</v>
+        <v>24.849</v>
       </c>
     </row>
     <row r="186">
@@ -3389,13 +3389,13 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>11.609</v>
+        <v>11.585</v>
       </c>
       <c r="C186" t="n">
-        <v>105.548</v>
+        <v>107.489</v>
       </c>
       <c r="D186" t="n">
-        <v>20.99</v>
+        <v>22.957</v>
       </c>
     </row>
     <row r="187">
@@ -3405,13 +3405,13 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>9.826000000000001</v>
+        <v>9.766999999999999</v>
       </c>
       <c r="C187" t="n">
-        <v>113.855</v>
+        <v>113.48</v>
       </c>
       <c r="D187" t="n">
-        <v>18.917</v>
+        <v>20.152</v>
       </c>
     </row>
     <row r="188">
@@ -3421,13 +3421,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>8.516999999999999</v>
+        <v>8.420999999999999</v>
       </c>
       <c r="C188" t="n">
-        <v>120.061</v>
+        <v>125.44</v>
       </c>
       <c r="D188" t="n">
-        <v>17.43</v>
+        <v>18.214</v>
       </c>
     </row>
     <row r="189">
@@ -3437,13 +3437,13 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>8.785</v>
+        <v>8.673</v>
       </c>
       <c r="C189" t="n">
-        <v>118.939</v>
+        <v>125.537</v>
       </c>
       <c r="D189" t="n">
-        <v>17.783</v>
+        <v>18.723</v>
       </c>
     </row>
     <row r="190">
@@ -3453,13 +3453,13 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>8.879</v>
+        <v>8.750999999999999</v>
       </c>
       <c r="C190" t="n">
-        <v>117.582</v>
+        <v>128.001</v>
       </c>
       <c r="D190" t="n">
-        <v>17.706</v>
+        <v>18.758</v>
       </c>
     </row>
     <row r="191">
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>8.483000000000001</v>
+        <v>8.397</v>
       </c>
       <c r="C191" t="n">
-        <v>123.511</v>
+        <v>130.379</v>
       </c>
       <c r="D191" t="n">
-        <v>18.162</v>
+        <v>18.816</v>
       </c>
     </row>
     <row r="192">
@@ -3485,13 +3485,13 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>7.941</v>
+        <v>7.919</v>
       </c>
       <c r="C192" t="n">
-        <v>131.821</v>
+        <v>138.491</v>
       </c>
       <c r="D192" t="n">
-        <v>18.765</v>
+        <v>18.945</v>
       </c>
     </row>
     <row r="193">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>7.539</v>
+        <v>7.553</v>
       </c>
       <c r="C193" t="n">
-        <v>137.512</v>
+        <v>138.695</v>
       </c>
       <c r="D193" t="n">
-        <v>19.163</v>
+        <v>18.957</v>
       </c>
     </row>
     <row r="194">
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>7.648</v>
+        <v>7.651</v>
       </c>
       <c r="C194" t="n">
-        <v>135.834</v>
+        <v>138.159</v>
       </c>
       <c r="D194" t="n">
-        <v>19.067</v>
+        <v>18.954</v>
       </c>
     </row>
     <row r="195">
@@ -3533,13 +3533,13 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7.251</v>
+        <v>7.252</v>
       </c>
       <c r="C195" t="n">
-        <v>137.019</v>
+        <v>138.971</v>
       </c>
       <c r="D195" t="n">
-        <v>18.827</v>
+        <v>18.506</v>
       </c>
     </row>
     <row r="196">
@@ -3549,13 +3549,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>9.085000000000001</v>
+        <v>9.101000000000001</v>
       </c>
       <c r="C196" t="n">
-        <v>131.412</v>
+        <v>135.408</v>
       </c>
       <c r="D196" t="n">
-        <v>20.088</v>
+        <v>20.635</v>
       </c>
     </row>
     <row r="197">
@@ -3565,13 +3565,13 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>10.32</v>
+        <v>10.365</v>
       </c>
       <c r="C197" t="n">
-        <v>127.01</v>
+        <v>129.79</v>
       </c>
       <c r="D197" t="n">
-        <v>20.336</v>
+        <v>21.927</v>
       </c>
     </row>
     <row r="198">
@@ -3581,13 +3581,13 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>10.85</v>
+        <v>10.874</v>
       </c>
       <c r="C198" t="n">
-        <v>119.947</v>
+        <v>119.737</v>
       </c>
       <c r="D198" t="n">
-        <v>20.982</v>
+        <v>22.134</v>
       </c>
     </row>
     <row r="199">
@@ -3597,13 +3597,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>10.021</v>
+        <v>9.992000000000001</v>
       </c>
       <c r="C199" t="n">
-        <v>122.506</v>
+        <v>116.122</v>
       </c>
       <c r="D199" t="n">
-        <v>20.818</v>
+        <v>21.317</v>
       </c>
     </row>
     <row r="200">
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>11.577</v>
+        <v>11.615</v>
       </c>
       <c r="C200" t="n">
-        <v>119.468</v>
+        <v>111.205</v>
       </c>
       <c r="D200" t="n">
-        <v>22.086</v>
+        <v>22.877</v>
       </c>
     </row>
     <row r="201">
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>11.661</v>
+        <v>11.755</v>
       </c>
       <c r="C201" t="n">
-        <v>121.656</v>
+        <v>114.574</v>
       </c>
       <c r="D201" t="n">
-        <v>21.263</v>
+        <v>22.847</v>
       </c>
     </row>
     <row r="202">
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>10.463</v>
+        <v>10.534</v>
       </c>
       <c r="C202" t="n">
-        <v>124.964</v>
+        <v>116.205</v>
       </c>
       <c r="D202" t="n">
-        <v>20.23</v>
+        <v>20.485</v>
       </c>
     </row>
     <row r="203">
@@ -3661,13 +3661,13 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>9.106</v>
+        <v>9.073</v>
       </c>
       <c r="C203" t="n">
-        <v>134.51</v>
+        <v>129.253</v>
       </c>
       <c r="D203" t="n">
-        <v>19.349</v>
+        <v>19.929</v>
       </c>
     </row>
     <row r="204">
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>9.529999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="C204" t="n">
-        <v>130.784</v>
+        <v>131.277</v>
       </c>
       <c r="D204" t="n">
-        <v>20.502</v>
+        <v>21.408</v>
       </c>
     </row>
     <row r="205">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>10.335</v>
+        <v>10.287</v>
       </c>
       <c r="C205" t="n">
-        <v>125.044</v>
+        <v>133.53</v>
       </c>
       <c r="D205" t="n">
-        <v>20.807</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="206">
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>9.688000000000001</v>
+        <v>9.683</v>
       </c>
       <c r="C206" t="n">
-        <v>127.968</v>
+        <v>138.353</v>
       </c>
       <c r="D206" t="n">
-        <v>20.227</v>
+        <v>22.661</v>
       </c>
     </row>
     <row r="207">
@@ -3725,13 +3725,13 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>9.525</v>
+        <v>9.526</v>
       </c>
       <c r="C207" t="n">
-        <v>132.654</v>
+        <v>141.957</v>
       </c>
       <c r="D207" t="n">
-        <v>19.499</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="208">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>9.327999999999999</v>
+        <v>9.356</v>
       </c>
       <c r="C208" t="n">
-        <v>132.306</v>
+        <v>140.19</v>
       </c>
       <c r="D208" t="n">
-        <v>19.517</v>
+        <v>20.27</v>
       </c>
     </row>
     <row r="209">
@@ -3757,13 +3757,13 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>10.173</v>
+        <v>10.181</v>
       </c>
       <c r="C209" t="n">
-        <v>122.555</v>
+        <v>127.348</v>
       </c>
       <c r="D209" t="n">
-        <v>19.817</v>
+        <v>21.193</v>
       </c>
     </row>
     <row r="210">
@@ -3773,13 +3773,13 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>9.077</v>
+        <v>9.077999999999999</v>
       </c>
       <c r="C210" t="n">
-        <v>128.855</v>
+        <v>131.592</v>
       </c>
       <c r="D210" t="n">
-        <v>20.046</v>
+        <v>21.115</v>
       </c>
     </row>
     <row r="211">
@@ -3789,13 +3789,13 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>9.148</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="C211" t="n">
-        <v>131.578</v>
+        <v>132.453</v>
       </c>
       <c r="D211" t="n">
-        <v>19.878</v>
+        <v>22.103</v>
       </c>
     </row>
     <row r="212">
@@ -3805,13 +3805,13 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>9.771000000000001</v>
+        <v>9.831</v>
       </c>
       <c r="C212" t="n">
-        <v>125.08</v>
+        <v>127.122</v>
       </c>
       <c r="D212" t="n">
-        <v>18.755</v>
+        <v>22.208</v>
       </c>
     </row>
     <row r="213">
@@ -3821,13 +3821,13 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>10.605</v>
+        <v>10.692</v>
       </c>
       <c r="C213" t="n">
-        <v>114.568</v>
+        <v>115.107</v>
       </c>
       <c r="D213" t="n">
-        <v>18.25</v>
+        <v>22.956</v>
       </c>
     </row>
     <row r="214">
@@ -3837,13 +3837,13 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>10.216</v>
+        <v>10.245</v>
       </c>
       <c r="C214" t="n">
-        <v>124.355</v>
+        <v>125.463</v>
       </c>
       <c r="D214" t="n">
-        <v>19.848</v>
+        <v>22.721</v>
       </c>
     </row>
     <row r="215">
@@ -3853,13 +3853,13 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>9.682</v>
+        <v>9.74</v>
       </c>
       <c r="C215" t="n">
-        <v>134.03</v>
+        <v>137.571</v>
       </c>
       <c r="D215" t="n">
-        <v>20.512</v>
+        <v>23.492</v>
       </c>
     </row>
     <row r="216">
@@ -3869,13 +3869,13 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>10.792</v>
+        <v>10.825</v>
       </c>
       <c r="C216" t="n">
-        <v>118.175</v>
+        <v>139.816</v>
       </c>
       <c r="D216" t="n">
-        <v>20.508</v>
+        <v>24.071</v>
       </c>
     </row>
     <row r="217">
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>11.44</v>
+        <v>11.452</v>
       </c>
       <c r="C217" t="n">
-        <v>109.453</v>
+        <v>131.209</v>
       </c>
       <c r="D217" t="n">
-        <v>19.709</v>
+        <v>23.754</v>
       </c>
     </row>
     <row r="218">
@@ -3901,13 +3901,13 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>10.566</v>
+        <v>10.464</v>
       </c>
       <c r="C218" t="n">
-        <v>116.096</v>
+        <v>129.883</v>
       </c>
       <c r="D218" t="n">
-        <v>19.756</v>
+        <v>21.52</v>
       </c>
     </row>
     <row r="219">
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>10.136</v>
+        <v>10.042</v>
       </c>
       <c r="C219" t="n">
-        <v>126.101</v>
+        <v>126.065</v>
       </c>
       <c r="D219" t="n">
-        <v>20.236</v>
+        <v>21.689</v>
       </c>
     </row>
     <row r="220">
@@ -3933,13 +3933,13 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>10.708</v>
+        <v>10.649</v>
       </c>
       <c r="C220" t="n">
-        <v>123.513</v>
+        <v>124.122</v>
       </c>
       <c r="D220" t="n">
-        <v>21.235</v>
+        <v>22.788</v>
       </c>
     </row>
     <row r="221">
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>10.078</v>
+        <v>10.072</v>
       </c>
       <c r="C221" t="n">
-        <v>127.559</v>
+        <v>128.115</v>
       </c>
       <c r="D221" t="n">
-        <v>20.48</v>
+        <v>22.168</v>
       </c>
     </row>
     <row r="222">
@@ -3965,13 +3965,13 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>9.856</v>
+        <v>9.85</v>
       </c>
       <c r="C222" t="n">
-        <v>124.266</v>
+        <v>131.278</v>
       </c>
       <c r="D222" t="n">
-        <v>20.164</v>
+        <v>21.195</v>
       </c>
     </row>
     <row r="223">
@@ -3981,13 +3981,13 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>9.901</v>
+        <v>9.91</v>
       </c>
       <c r="C223" t="n">
-        <v>127.868</v>
+        <v>135.327</v>
       </c>
       <c r="D223" t="n">
-        <v>20.385</v>
+        <v>21.678</v>
       </c>
     </row>
     <row r="224">
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>10.802</v>
+        <v>10.876</v>
       </c>
       <c r="C224" t="n">
-        <v>123.366</v>
+        <v>124.43</v>
       </c>
       <c r="D224" t="n">
-        <v>20.427</v>
+        <v>21.805</v>
       </c>
     </row>
     <row r="225">
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>10.447</v>
+        <v>10.505</v>
       </c>
       <c r="C225" t="n">
-        <v>123.729</v>
+        <v>122.334</v>
       </c>
       <c r="D225" t="n">
-        <v>20.335</v>
+        <v>21.679</v>
       </c>
     </row>
     <row r="226">
@@ -4029,13 +4029,13 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>10.053</v>
+        <v>10.034</v>
       </c>
       <c r="C226" t="n">
-        <v>122.712</v>
+        <v>125.67</v>
       </c>
       <c r="D226" t="n">
-        <v>20.464</v>
+        <v>21.747</v>
       </c>
     </row>
     <row r="227">
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>10.498</v>
+        <v>10.548</v>
       </c>
       <c r="C227" t="n">
-        <v>120.363</v>
+        <v>117.459</v>
       </c>
       <c r="D227" t="n">
-        <v>21.11</v>
+        <v>21.971</v>
       </c>
     </row>
     <row r="228">
@@ -4061,13 +4061,13 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>11.206</v>
+        <v>11.295</v>
       </c>
       <c r="C228" t="n">
-        <v>113.777</v>
+        <v>107.745</v>
       </c>
       <c r="D228" t="n">
-        <v>21.223</v>
+        <v>22.108</v>
       </c>
     </row>
     <row r="229">
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>11.937</v>
+        <v>12.017</v>
       </c>
       <c r="C229" t="n">
-        <v>109.5</v>
+        <v>112.501</v>
       </c>
       <c r="D229" t="n">
-        <v>21.817</v>
+        <v>23.469</v>
       </c>
     </row>
     <row r="230">
@@ -4093,13 +4093,13 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>10.447</v>
+        <v>10.485</v>
       </c>
       <c r="C230" t="n">
-        <v>118.323</v>
+        <v>135.898</v>
       </c>
       <c r="D230" t="n">
-        <v>19.803</v>
+        <v>23.093</v>
       </c>
     </row>
     <row r="231">
@@ -4109,13 +4109,13 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>11.216</v>
+        <v>11.277</v>
       </c>
       <c r="C231" t="n">
-        <v>120.719</v>
+        <v>131.713</v>
       </c>
       <c r="D231" t="n">
-        <v>19.654</v>
+        <v>23.421</v>
       </c>
     </row>
     <row r="232">
@@ -4125,13 +4125,13 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>11.814</v>
+        <v>11.782</v>
       </c>
       <c r="C232" t="n">
-        <v>121.981</v>
+        <v>120.578</v>
       </c>
       <c r="D232" t="n">
-        <v>19.922</v>
+        <v>23.602</v>
       </c>
     </row>
     <row r="233">
@@ -4141,13 +4141,13 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>11.435</v>
+        <v>11.387</v>
       </c>
       <c r="C233" t="n">
-        <v>121.318</v>
+        <v>116.564</v>
       </c>
       <c r="D233" t="n">
-        <v>19.869</v>
+        <v>22.324</v>
       </c>
     </row>
     <row r="234">
@@ -4157,13 +4157,13 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>10.369</v>
+        <v>10.363</v>
       </c>
       <c r="C234" t="n">
-        <v>108.919</v>
+        <v>116.152</v>
       </c>
       <c r="D234" t="n">
-        <v>17.9</v>
+        <v>20.291</v>
       </c>
     </row>
     <row r="235">
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>10.814</v>
+        <v>10.841</v>
       </c>
       <c r="C235" t="n">
-        <v>107.884</v>
+        <v>114.134</v>
       </c>
       <c r="D235" t="n">
-        <v>18.783</v>
+        <v>20.81</v>
       </c>
     </row>
     <row r="236">
@@ -4189,13 +4189,13 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>10.901</v>
+        <v>10.939</v>
       </c>
       <c r="C236" t="n">
-        <v>118.528</v>
+        <v>128.621</v>
       </c>
       <c r="D236" t="n">
-        <v>19.578</v>
+        <v>23.076</v>
       </c>
     </row>
     <row r="237">
@@ -4205,13 +4205,13 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>11.375</v>
+        <v>11.381</v>
       </c>
       <c r="C237" t="n">
-        <v>124.24</v>
+        <v>129.233</v>
       </c>
       <c r="D237" t="n">
-        <v>22.574</v>
+        <v>25.465</v>
       </c>
     </row>
     <row r="238">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>11.087</v>
+        <v>11.111</v>
       </c>
       <c r="C238" t="n">
-        <v>125.877</v>
+        <v>133.125</v>
       </c>
       <c r="D238" t="n">
-        <v>23.517</v>
+        <v>25.622</v>
       </c>
     </row>
     <row r="239">
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>10.177</v>
+        <v>10.162</v>
       </c>
       <c r="C239" t="n">
-        <v>130.432</v>
+        <v>127.965</v>
       </c>
       <c r="D239" t="n">
-        <v>23.031</v>
+        <v>23.553</v>
       </c>
     </row>
     <row r="240">
@@ -4253,13 +4253,13 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>10.176</v>
+        <v>10.287</v>
       </c>
       <c r="C240" t="n">
-        <v>126.529</v>
+        <v>122.429</v>
       </c>
       <c r="D240" t="n">
-        <v>21.317</v>
+        <v>21.985</v>
       </c>
     </row>
     <row r="241">
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>9.971</v>
+        <v>10.072</v>
       </c>
       <c r="C241" t="n">
-        <v>120.549</v>
+        <v>111.697</v>
       </c>
       <c r="D241" t="n">
-        <v>20.093</v>
+        <v>20.766</v>
       </c>
     </row>
     <row r="242">
@@ -4285,13 +4285,13 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>11.015</v>
+        <v>11.073</v>
       </c>
       <c r="C242" t="n">
-        <v>109.802</v>
+        <v>107.258</v>
       </c>
       <c r="D242" t="n">
-        <v>19.077</v>
+        <v>20.582</v>
       </c>
     </row>
     <row r="243">
@@ -4301,13 +4301,13 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>11.951</v>
+        <v>11.88</v>
       </c>
       <c r="C243" t="n">
-        <v>101.714</v>
+        <v>101.164</v>
       </c>
       <c r="D243" t="n">
-        <v>19.259</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="244">
@@ -4317,13 +4317,13 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>12.657</v>
+        <v>12.649</v>
       </c>
       <c r="C244" t="n">
-        <v>97.146</v>
+        <v>100.779</v>
       </c>
       <c r="D244" t="n">
-        <v>20.484</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="245">
@@ -4333,13 +4333,13 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>9.731999999999999</v>
+        <v>9.737</v>
       </c>
       <c r="C245" t="n">
-        <v>114.187</v>
+        <v>114.031</v>
       </c>
       <c r="D245" t="n">
-        <v>19.504</v>
+        <v>20.31</v>
       </c>
     </row>
     <row r="246">
@@ -4349,13 +4349,13 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>9.532999999999999</v>
+        <v>9.545</v>
       </c>
       <c r="C246" t="n">
-        <v>115.523</v>
+        <v>114.975</v>
       </c>
       <c r="D246" t="n">
-        <v>18.798</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="247">
@@ -4365,13 +4365,13 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>11.521</v>
+        <v>11.529</v>
       </c>
       <c r="C247" t="n">
-        <v>113.308</v>
+        <v>109.799</v>
       </c>
       <c r="D247" t="n">
-        <v>20.172</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="248">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>11.656</v>
+        <v>11.698</v>
       </c>
       <c r="C248" t="n">
-        <v>116.145</v>
+        <v>119.504</v>
       </c>
       <c r="D248" t="n">
-        <v>21.37</v>
+        <v>23.139</v>
       </c>
     </row>
     <row r="249">
@@ -4397,13 +4397,13 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>11.105</v>
+        <v>11.112</v>
       </c>
       <c r="C249" t="n">
-        <v>116.778</v>
+        <v>118.926</v>
       </c>
       <c r="D249" t="n">
-        <v>21.041</v>
+        <v>23.202</v>
       </c>
     </row>
     <row r="250">
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>10.879</v>
+        <v>10.882</v>
       </c>
       <c r="C250" t="n">
-        <v>120.681</v>
+        <v>124.504</v>
       </c>
       <c r="D250" t="n">
-        <v>20.395</v>
+        <v>22.551</v>
       </c>
     </row>
     <row r="251">
@@ -4429,13 +4429,13 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>10.84</v>
+        <v>10.946</v>
       </c>
       <c r="C251" t="n">
-        <v>115.959</v>
+        <v>119.506</v>
       </c>
       <c r="D251" t="n">
-        <v>19.287</v>
+        <v>21.087</v>
       </c>
     </row>
     <row r="252">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>10.235</v>
+        <v>10.364</v>
       </c>
       <c r="C252" t="n">
-        <v>107.837</v>
+        <v>114.706</v>
       </c>
       <c r="D252" t="n">
-        <v>18.859</v>
+        <v>20.781</v>
       </c>
     </row>
     <row r="253">
@@ -4461,13 +4461,13 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>10.789</v>
+        <v>10.879</v>
       </c>
       <c r="C253" t="n">
-        <v>92.646</v>
+        <v>94.96899999999999</v>
       </c>
       <c r="D253" t="n">
-        <v>18.405</v>
+        <v>18.925</v>
       </c>
     </row>
     <row r="254">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>11.227</v>
+        <v>11.181</v>
       </c>
       <c r="C254" t="n">
-        <v>90.852</v>
+        <v>90.42400000000001</v>
       </c>
       <c r="D254" t="n">
-        <v>18.43</v>
+        <v>18.466</v>
       </c>
     </row>
     <row r="255">
@@ -4493,13 +4493,13 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>12.356</v>
+        <v>12.176</v>
       </c>
       <c r="C255" t="n">
-        <v>87.996</v>
+        <v>85.938</v>
       </c>
       <c r="D255" t="n">
-        <v>19.652</v>
+        <v>20.057</v>
       </c>
     </row>
     <row r="256">
@@ -4509,13 +4509,13 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>13.453</v>
+        <v>13.197</v>
       </c>
       <c r="C256" t="n">
-        <v>80.977</v>
+        <v>82.164</v>
       </c>
       <c r="D256" t="n">
-        <v>18.679</v>
+        <v>20.782</v>
       </c>
     </row>
     <row r="257">
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>13.71</v>
+        <v>13.445</v>
       </c>
       <c r="C257" t="n">
-        <v>76.977</v>
+        <v>79.30800000000001</v>
       </c>
       <c r="D257" t="n">
-        <v>18.006</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="258">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>14.871</v>
+        <v>14.62</v>
       </c>
       <c r="C258" t="n">
-        <v>79.499</v>
+        <v>79.755</v>
       </c>
       <c r="D258" t="n">
-        <v>19.729</v>
+        <v>19.823</v>
       </c>
     </row>
     <row r="259">
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>14.747</v>
+        <v>14.534</v>
       </c>
       <c r="C259" t="n">
-        <v>86.48699999999999</v>
+        <v>82.145</v>
       </c>
       <c r="D259" t="n">
-        <v>21.933</v>
+        <v>21.107</v>
       </c>
     </row>
     <row r="260">
@@ -4573,13 +4573,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>14.734</v>
+        <v>14.557</v>
       </c>
       <c r="C260" t="n">
-        <v>83.565</v>
+        <v>85.479</v>
       </c>
       <c r="D260" t="n">
-        <v>20.177</v>
+        <v>21.111</v>
       </c>
     </row>
     <row r="261">
@@ -4589,13 +4589,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>12.8</v>
+        <v>12.697</v>
       </c>
       <c r="C261" t="n">
-        <v>90.70099999999999</v>
+        <v>96.56100000000001</v>
       </c>
       <c r="D261" t="n">
-        <v>19.42</v>
+        <v>21.195</v>
       </c>
     </row>
     <row r="262">
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>13.154</v>
+        <v>13.017</v>
       </c>
       <c r="C262" t="n">
-        <v>94.129</v>
+        <v>99.324</v>
       </c>
       <c r="D262" t="n">
-        <v>20.967</v>
+        <v>22.234</v>
       </c>
     </row>
     <row r="263">
@@ -4621,13 +4621,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>12.109</v>
+        <v>12.086</v>
       </c>
       <c r="C263" t="n">
-        <v>90.536</v>
+        <v>90.997</v>
       </c>
       <c r="D263" t="n">
-        <v>20.041</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="264">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>13.09</v>
+        <v>13.004</v>
       </c>
       <c r="C264" t="n">
-        <v>81.863</v>
+        <v>81.842</v>
       </c>
       <c r="D264" t="n">
-        <v>19.258</v>
+        <v>19.593</v>
       </c>
     </row>
     <row r="265">
@@ -4653,13 +4653,13 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>12.781</v>
+        <v>12.668</v>
       </c>
       <c r="C265" t="n">
-        <v>86.10299999999999</v>
+        <v>83.49299999999999</v>
       </c>
       <c r="D265" t="n">
-        <v>19.726</v>
+        <v>19.645</v>
       </c>
     </row>
     <row r="266">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>15.001</v>
+        <v>14.859</v>
       </c>
       <c r="C266" t="n">
-        <v>81.438</v>
+        <v>80.56399999999999</v>
       </c>
       <c r="D266" t="n">
-        <v>20.534</v>
+        <v>19.684</v>
       </c>
     </row>
     <row r="267">
@@ -4685,13 +4685,13 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>15.604</v>
+        <v>15.399</v>
       </c>
       <c r="C267" t="n">
-        <v>90.26300000000001</v>
+        <v>90.81399999999999</v>
       </c>
       <c r="D267" t="n">
-        <v>21.85</v>
+        <v>21.121</v>
       </c>
     </row>
     <row r="268">
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>14.495</v>
+        <v>14.288</v>
       </c>
       <c r="C268" t="n">
-        <v>106.486</v>
+        <v>109.033</v>
       </c>
       <c r="D268" t="n">
-        <v>23.404</v>
+        <v>22.368</v>
       </c>
     </row>
     <row r="269">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>11.762</v>
+        <v>11.568</v>
       </c>
       <c r="C269" t="n">
-        <v>117.651</v>
+        <v>124.877</v>
       </c>
       <c r="D269" t="n">
-        <v>23.172</v>
+        <v>25.325</v>
       </c>
     </row>
     <row r="270">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>11.898</v>
+        <v>11.696</v>
       </c>
       <c r="C270" t="n">
-        <v>102.193</v>
+        <v>110.842</v>
       </c>
       <c r="D270" t="n">
-        <v>21.101</v>
+        <v>24.451</v>
       </c>
     </row>
     <row r="271">
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>14.282</v>
+        <v>13.998</v>
       </c>
       <c r="C271" t="n">
-        <v>86.26900000000001</v>
+        <v>93.297</v>
       </c>
       <c r="D271" t="n">
-        <v>20.324</v>
+        <v>23.055</v>
       </c>
     </row>
     <row r="272">
@@ -4765,13 +4765,13 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>14.784</v>
+        <v>14.569</v>
       </c>
       <c r="C272" t="n">
-        <v>79.383</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="D272" t="n">
-        <v>18.372</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="273">
@@ -4781,13 +4781,13 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>14.033</v>
+        <v>13.845</v>
       </c>
       <c r="C273" t="n">
-        <v>81.24299999999999</v>
+        <v>79.846</v>
       </c>
       <c r="D273" t="n">
-        <v>18.13</v>
+        <v>19.154</v>
       </c>
     </row>
     <row r="274">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>13.606</v>
+        <v>13.435</v>
       </c>
       <c r="C274" t="n">
-        <v>84.095</v>
+        <v>82.467</v>
       </c>
       <c r="D274" t="n">
-        <v>18.54</v>
+        <v>18.368</v>
       </c>
     </row>
     <row r="275">
@@ -4813,13 +4813,13 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>15.69</v>
+        <v>15.614</v>
       </c>
       <c r="C275" t="n">
-        <v>76.402</v>
+        <v>74.47499999999999</v>
       </c>
       <c r="D275" t="n">
-        <v>19.392</v>
+        <v>17.351</v>
       </c>
     </row>
     <row r="276">
@@ -4829,13 +4829,13 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>15.382</v>
+        <v>15.314</v>
       </c>
       <c r="C276" t="n">
-        <v>75.994</v>
+        <v>72.884</v>
       </c>
       <c r="D276" t="n">
-        <v>19.11</v>
+        <v>18.756</v>
       </c>
     </row>
     <row r="277">
@@ -4845,13 +4845,13 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>12.7</v>
+        <v>12.572</v>
       </c>
       <c r="C277" t="n">
-        <v>83.51900000000001</v>
+        <v>79.19499999999999</v>
       </c>
       <c r="D277" t="n">
-        <v>18.432</v>
+        <v>19.821</v>
       </c>
     </row>
     <row r="278">
@@ -4861,13 +4861,13 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>12.839</v>
+        <v>12.675</v>
       </c>
       <c r="C278" t="n">
-        <v>84.33799999999999</v>
+        <v>82.901</v>
       </c>
       <c r="D278" t="n">
-        <v>18.753</v>
+        <v>21.327</v>
       </c>
     </row>
     <row r="279">
@@ -4877,13 +4877,13 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>13.691</v>
+        <v>13.589</v>
       </c>
       <c r="C279" t="n">
-        <v>79.21899999999999</v>
+        <v>81.425</v>
       </c>
       <c r="D279" t="n">
-        <v>18.477</v>
+        <v>20.578</v>
       </c>
     </row>
     <row r="280">
@@ -4893,13 +4893,13 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>13.652</v>
+        <v>13.637</v>
       </c>
       <c r="C280" t="n">
-        <v>79.657</v>
+        <v>84.069</v>
       </c>
       <c r="D280" t="n">
-        <v>18.236</v>
+        <v>21.197</v>
       </c>
     </row>
     <row r="281">
@@ -4909,13 +4909,13 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>14.217</v>
+        <v>14.219</v>
       </c>
       <c r="C281" t="n">
-        <v>79.408</v>
+        <v>79.56699999999999</v>
       </c>
       <c r="D281" t="n">
-        <v>17.943</v>
+        <v>17.824</v>
       </c>
     </row>
     <row r="282">
@@ -4925,13 +4925,13 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>16.149</v>
+        <v>15.963</v>
       </c>
       <c r="C282" t="n">
-        <v>84.41800000000001</v>
+        <v>83.642</v>
       </c>
       <c r="D282" t="n">
-        <v>20.006</v>
+        <v>20.484</v>
       </c>
     </row>
     <row r="283">
@@ -4941,13 +4941,13 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>13.739</v>
+        <v>13.579</v>
       </c>
       <c r="C283" t="n">
-        <v>101.016</v>
+        <v>97.863</v>
       </c>
       <c r="D283" t="n">
-        <v>20.475</v>
+        <v>20.054</v>
       </c>
     </row>
     <row r="284">
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>12.576</v>
+        <v>12.545</v>
       </c>
       <c r="C284" t="n">
-        <v>102.058</v>
+        <v>100.914</v>
       </c>
       <c r="D284" t="n">
-        <v>19.943</v>
+        <v>19.401</v>
       </c>
     </row>
     <row r="285">
@@ -4976,10 +4976,10 @@
         <v>14.415</v>
       </c>
       <c r="C285" t="n">
-        <v>83.88</v>
+        <v>81.34699999999999</v>
       </c>
       <c r="D285" t="n">
-        <v>18.821</v>
+        <v>16.625</v>
       </c>
     </row>
     <row r="286">
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>14.472</v>
+        <v>14.353</v>
       </c>
       <c r="C286" t="n">
-        <v>79.703</v>
+        <v>82.77200000000001</v>
       </c>
       <c r="D286" t="n">
-        <v>18.39</v>
+        <v>19.654</v>
       </c>
     </row>
     <row r="287">
@@ -5005,13 +5005,13 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>13.386</v>
+        <v>13.269</v>
       </c>
       <c r="C287" t="n">
-        <v>80.813</v>
+        <v>80.675</v>
       </c>
       <c r="D287" t="n">
-        <v>17.759</v>
+        <v>18.87</v>
       </c>
     </row>
     <row r="288">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>14.481</v>
+        <v>14.393</v>
       </c>
       <c r="C288" t="n">
-        <v>81.642</v>
+        <v>79.63800000000001</v>
       </c>
       <c r="D288" t="n">
-        <v>19.9</v>
+        <v>19.788</v>
       </c>
     </row>
     <row r="289">
@@ -5037,13 +5037,13 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>16.181</v>
+        <v>16.136</v>
       </c>
       <c r="C289" t="n">
-        <v>80.312</v>
+        <v>77.256</v>
       </c>
       <c r="D289" t="n">
-        <v>21.358</v>
+        <v>21.361</v>
       </c>
     </row>
     <row r="290">
@@ -5053,13 +5053,13 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>16.896</v>
+        <v>16.849</v>
       </c>
       <c r="C290" t="n">
-        <v>81.214</v>
+        <v>79.697</v>
       </c>
       <c r="D290" t="n">
-        <v>21.897</v>
+        <v>22.431</v>
       </c>
     </row>
     <row r="291">
@@ -5069,13 +5069,13 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>14.73</v>
+        <v>14.785</v>
       </c>
       <c r="C291" t="n">
-        <v>87.45999999999999</v>
+        <v>88.26900000000001</v>
       </c>
       <c r="D291" t="n">
-        <v>19.734</v>
+        <v>21.317</v>
       </c>
     </row>
     <row r="292">
@@ -5085,13 +5085,13 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>14.629</v>
+        <v>14.607</v>
       </c>
       <c r="C292" t="n">
-        <v>84.75</v>
+        <v>85.03</v>
       </c>
       <c r="D292" t="n">
-        <v>19.235</v>
+        <v>19.569</v>
       </c>
     </row>
     <row r="293">
@@ -5101,13 +5101,13 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>14.658</v>
+        <v>14.516</v>
       </c>
       <c r="C293" t="n">
-        <v>80.764</v>
+        <v>83.611</v>
       </c>
       <c r="D293" t="n">
-        <v>18.988</v>
+        <v>19.275</v>
       </c>
     </row>
     <row r="294">
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>15.668</v>
+        <v>15.464</v>
       </c>
       <c r="C294" t="n">
-        <v>73.806</v>
+        <v>75.756</v>
       </c>
       <c r="D294" t="n">
-        <v>19.517</v>
+        <v>16.884</v>
       </c>
     </row>
     <row r="295">
@@ -5133,13 +5133,13 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>14.999</v>
+        <v>14.945</v>
       </c>
       <c r="C295" t="n">
-        <v>76.995</v>
+        <v>81.057</v>
       </c>
       <c r="D295" t="n">
-        <v>18.736</v>
+        <v>17.946</v>
       </c>
     </row>
     <row r="296">
@@ -5149,13 +5149,13 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>15.924</v>
+        <v>15.952</v>
       </c>
       <c r="C296" t="n">
-        <v>74.883</v>
+        <v>77.111</v>
       </c>
       <c r="D296" t="n">
-        <v>18.951</v>
+        <v>17.859</v>
       </c>
     </row>
     <row r="297">
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>15.086</v>
+        <v>15.052</v>
       </c>
       <c r="C297" t="n">
-        <v>77.646</v>
+        <v>85.264</v>
       </c>
       <c r="D297" t="n">
-        <v>18.329</v>
+        <v>18.989</v>
       </c>
     </row>
     <row r="298">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>12.337</v>
+        <v>12.234</v>
       </c>
       <c r="C298" t="n">
-        <v>94.194</v>
+        <v>93.874</v>
       </c>
       <c r="D298" t="n">
-        <v>20.508</v>
+        <v>17.782</v>
       </c>
     </row>
     <row r="299">
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>14.152</v>
+        <v>14.026</v>
       </c>
       <c r="C299" t="n">
-        <v>87.273</v>
+        <v>83.709</v>
       </c>
       <c r="D299" t="n">
-        <v>20.966</v>
+        <v>18.136</v>
       </c>
     </row>
     <row r="300">
@@ -5213,13 +5213,13 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>13.786</v>
+        <v>13.818</v>
       </c>
       <c r="C300" t="n">
-        <v>85.61</v>
+        <v>82.553</v>
       </c>
       <c r="D300" t="n">
-        <v>19.675</v>
+        <v>18.217</v>
       </c>
     </row>
     <row r="301">
@@ -5229,13 +5229,13 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>15.408</v>
+        <v>15.373</v>
       </c>
       <c r="C301" t="n">
-        <v>77.553</v>
+        <v>83.962</v>
       </c>
       <c r="D301" t="n">
-        <v>19.301</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="302">
@@ -5245,13 +5245,13 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>13.412</v>
+        <v>13.365</v>
       </c>
       <c r="C302" t="n">
-        <v>94.89</v>
+        <v>95.233</v>
       </c>
       <c r="D302" t="n">
-        <v>21.458</v>
+        <v>20.279</v>
       </c>
     </row>
     <row r="303">
@@ -5261,13 +5261,13 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>13.399</v>
+        <v>13.336</v>
       </c>
       <c r="C303" t="n">
-        <v>97.401</v>
+        <v>98.30500000000001</v>
       </c>
       <c r="D303" t="n">
-        <v>21.031</v>
+        <v>18.938</v>
       </c>
     </row>
     <row r="304">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>12.503</v>
+        <v>12.587</v>
       </c>
       <c r="C304" t="n">
-        <v>97.661</v>
+        <v>96.47499999999999</v>
       </c>
       <c r="D304" t="n">
-        <v>19.565</v>
+        <v>18.089</v>
       </c>
     </row>
     <row r="305">
@@ -5293,13 +5293,13 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>14.894</v>
+        <v>14.919</v>
       </c>
       <c r="C305" t="n">
-        <v>83.434</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="D305" t="n">
-        <v>19.157</v>
+        <v>19.414</v>
       </c>
     </row>
     <row r="306">
@@ -5309,13 +5309,13 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>15.202</v>
+        <v>15.077</v>
       </c>
       <c r="C306" t="n">
-        <v>77.616</v>
+        <v>77.678</v>
       </c>
       <c r="D306" t="n">
-        <v>19.215</v>
+        <v>19.086</v>
       </c>
     </row>
     <row r="307">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>13.197</v>
+        <v>12.921</v>
       </c>
       <c r="C307" t="n">
-        <v>78.392</v>
+        <v>85.428</v>
       </c>
       <c r="D307" t="n">
-        <v>17.771</v>
+        <v>20.014</v>
       </c>
     </row>
     <row r="308">
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>12.758</v>
+        <v>12.454</v>
       </c>
       <c r="C308" t="n">
-        <v>83.104</v>
+        <v>87.452</v>
       </c>
       <c r="D308" t="n">
-        <v>19.856</v>
+        <v>20.801</v>
       </c>
     </row>
     <row r="309">
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>13.722</v>
+        <v>13.476</v>
       </c>
       <c r="C309" t="n">
-        <v>79.998</v>
+        <v>82.10299999999999</v>
       </c>
       <c r="D309" t="n">
-        <v>19.854</v>
+        <v>20.381</v>
       </c>
     </row>
     <row r="310">
@@ -5373,13 +5373,13 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>16.003</v>
+        <v>15.903</v>
       </c>
       <c r="C310" t="n">
-        <v>72.53700000000001</v>
+        <v>70.486</v>
       </c>
       <c r="D310" t="n">
-        <v>19.064</v>
+        <v>18.82</v>
       </c>
     </row>
   </sheetData>

--- a/submission.xlsx
+++ b/submission.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.092</v>
+        <v>9.622999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>137.921</v>
+        <v>134.172</v>
       </c>
       <c r="D2" t="n">
-        <v>22.663</v>
+        <v>22.481</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.912000000000001</v>
+        <v>9.625</v>
       </c>
       <c r="C3" t="n">
-        <v>146.554</v>
+        <v>141.027</v>
       </c>
       <c r="D3" t="n">
-        <v>23.792</v>
+        <v>23.653</v>
       </c>
     </row>
     <row r="4">
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.917</v>
+        <v>9.782999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>148.977</v>
+        <v>143.271</v>
       </c>
       <c r="D4" t="n">
-        <v>24.627</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="5">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.494</v>
+        <v>10.436</v>
       </c>
       <c r="C5" t="n">
-        <v>149.976</v>
+        <v>146.131</v>
       </c>
       <c r="D5" t="n">
-        <v>26.414</v>
+        <v>26.149</v>
       </c>
     </row>
     <row r="6">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.219</v>
+        <v>10.355</v>
       </c>
       <c r="C6" t="n">
-        <v>136.847</v>
+        <v>135.038</v>
       </c>
       <c r="D6" t="n">
-        <v>25.633</v>
+        <v>25.098</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.8</v>
+        <v>11.052</v>
       </c>
       <c r="C7" t="n">
-        <v>127.452</v>
+        <v>126.913</v>
       </c>
       <c r="D7" t="n">
-        <v>25.477</v>
+        <v>24.984</v>
       </c>
     </row>
     <row r="8">
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.437</v>
+        <v>12.672</v>
       </c>
       <c r="C8" t="n">
-        <v>133.1</v>
+        <v>129.886</v>
       </c>
       <c r="D8" t="n">
-        <v>29.187</v>
+        <v>28.663</v>
       </c>
     </row>
     <row r="9">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.861</v>
+        <v>11.945</v>
       </c>
       <c r="C9" t="n">
-        <v>134.245</v>
+        <v>130.534</v>
       </c>
       <c r="D9" t="n">
-        <v>27.338</v>
+        <v>26.918</v>
       </c>
     </row>
     <row r="10">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.364000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="C10" t="n">
-        <v>136.366</v>
+        <v>134.506</v>
       </c>
       <c r="D10" t="n">
-        <v>22.608</v>
+        <v>22.364</v>
       </c>
     </row>
     <row r="11">
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.456</v>
+        <v>9.209</v>
       </c>
       <c r="C11" t="n">
-        <v>131.087</v>
+        <v>126.58</v>
       </c>
       <c r="D11" t="n">
-        <v>20.629</v>
+        <v>20.324</v>
       </c>
     </row>
     <row r="12">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.961</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>134.879</v>
+        <v>131.383</v>
       </c>
       <c r="D12" t="n">
-        <v>22.025</v>
+        <v>21.849</v>
       </c>
     </row>
     <row r="13">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9.933</v>
+        <v>9.936999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>117.115</v>
+        <v>117.954</v>
       </c>
       <c r="D13" t="n">
-        <v>21.118</v>
+        <v>21.269</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.709</v>
+        <v>8.632999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>103.651</v>
+        <v>108.599</v>
       </c>
       <c r="D14" t="n">
-        <v>18.364</v>
+        <v>18.479</v>
       </c>
     </row>
     <row r="15">
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.295999999999999</v>
+        <v>9.298999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>94.51000000000001</v>
+        <v>98.607</v>
       </c>
       <c r="D15" t="n">
-        <v>17.798</v>
+        <v>17.822</v>
       </c>
     </row>
     <row r="16">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9.771000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>114.233</v>
+        <v>117.407</v>
       </c>
       <c r="D16" t="n">
-        <v>21.483</v>
+        <v>21.198</v>
       </c>
     </row>
     <row r="17">
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11.709</v>
+        <v>11.575</v>
       </c>
       <c r="C17" t="n">
-        <v>119.858</v>
+        <v>118.525</v>
       </c>
       <c r="D17" t="n">
-        <v>25.026</v>
+        <v>24.981</v>
       </c>
     </row>
     <row r="18">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11.717</v>
+        <v>11.472</v>
       </c>
       <c r="C18" t="n">
-        <v>116.18</v>
+        <v>113.767</v>
       </c>
       <c r="D18" t="n">
-        <v>25.203</v>
+        <v>24.979</v>
       </c>
     </row>
     <row r="19">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.278</v>
+        <v>10.313</v>
       </c>
       <c r="C19" t="n">
-        <v>110.463</v>
+        <v>110.731</v>
       </c>
       <c r="D19" t="n">
-        <v>21.349</v>
+        <v>21.219</v>
       </c>
     </row>
     <row r="20">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.089</v>
+        <v>9.081</v>
       </c>
       <c r="C20" t="n">
-        <v>112.545</v>
+        <v>114.348</v>
       </c>
       <c r="D20" t="n">
-        <v>19.457</v>
+        <v>19.322</v>
       </c>
     </row>
     <row r="21">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.932</v>
+        <v>9.904</v>
       </c>
       <c r="C21" t="n">
-        <v>123.68</v>
+        <v>121.267</v>
       </c>
       <c r="D21" t="n">
-        <v>20.089</v>
+        <v>20.099</v>
       </c>
     </row>
     <row r="22">
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10.577</v>
+        <v>10.232</v>
       </c>
       <c r="C22" t="n">
-        <v>120.736</v>
+        <v>117.756</v>
       </c>
       <c r="D22" t="n">
-        <v>21.331</v>
+        <v>21.181</v>
       </c>
     </row>
     <row r="23">
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10.236</v>
+        <v>9.83</v>
       </c>
       <c r="C23" t="n">
-        <v>117.017</v>
+        <v>118.253</v>
       </c>
       <c r="D23" t="n">
-        <v>22.004</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="24">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10.093</v>
+        <v>9.669</v>
       </c>
       <c r="C24" t="n">
-        <v>119.764</v>
+        <v>122.427</v>
       </c>
       <c r="D24" t="n">
-        <v>23.934</v>
+        <v>23.95</v>
       </c>
     </row>
     <row r="25">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10.62</v>
+        <v>10.099</v>
       </c>
       <c r="C25" t="n">
-        <v>125.128</v>
+        <v>125.729</v>
       </c>
       <c r="D25" t="n">
-        <v>25.722</v>
+        <v>25.186</v>
       </c>
     </row>
     <row r="26">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11.552</v>
+        <v>10.768</v>
       </c>
       <c r="C26" t="n">
-        <v>124.012</v>
+        <v>122.096</v>
       </c>
       <c r="D26" t="n">
-        <v>26.656</v>
+        <v>25.644</v>
       </c>
     </row>
     <row r="27">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.077</v>
+        <v>11.461</v>
       </c>
       <c r="C27" t="n">
-        <v>116.559</v>
+        <v>113.653</v>
       </c>
       <c r="D27" t="n">
-        <v>25.9</v>
+        <v>25.007</v>
       </c>
     </row>
     <row r="28">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12.38</v>
+        <v>12.188</v>
       </c>
       <c r="C28" t="n">
-        <v>123.708</v>
+        <v>116.934</v>
       </c>
       <c r="D28" t="n">
-        <v>26.638</v>
+        <v>25.741</v>
       </c>
     </row>
     <row r="29">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12.315</v>
+        <v>12.13</v>
       </c>
       <c r="C29" t="n">
-        <v>128.624</v>
+        <v>119.742</v>
       </c>
       <c r="D29" t="n">
-        <v>26.376</v>
+        <v>25.513</v>
       </c>
     </row>
     <row r="30">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10.863</v>
+        <v>10.659</v>
       </c>
       <c r="C30" t="n">
-        <v>137.4</v>
+        <v>132.357</v>
       </c>
       <c r="D30" t="n">
-        <v>25.14</v>
+        <v>24.793</v>
       </c>
     </row>
     <row r="31">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9.085000000000001</v>
+        <v>8.817</v>
       </c>
       <c r="C31" t="n">
-        <v>142.654</v>
+        <v>141.809</v>
       </c>
       <c r="D31" t="n">
-        <v>22.161</v>
+        <v>22.154</v>
       </c>
     </row>
     <row r="32">
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9.728999999999999</v>
+        <v>9.696999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>131.221</v>
+        <v>132.202</v>
       </c>
       <c r="D32" t="n">
-        <v>22.662</v>
+        <v>22.647</v>
       </c>
     </row>
     <row r="33">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>12.395</v>
+        <v>12.611</v>
       </c>
       <c r="C33" t="n">
-        <v>102.574</v>
+        <v>101.801</v>
       </c>
       <c r="D33" t="n">
-        <v>23.586</v>
+        <v>23.306</v>
       </c>
     </row>
     <row r="34">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12.288</v>
+        <v>12.557</v>
       </c>
       <c r="C34" t="n">
-        <v>103.962</v>
+        <v>106.827</v>
       </c>
       <c r="D34" t="n">
-        <v>24.97</v>
+        <v>24.752</v>
       </c>
     </row>
     <row r="35">
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11.34</v>
+        <v>11.657</v>
       </c>
       <c r="C35" t="n">
-        <v>113.384</v>
+        <v>116.37</v>
       </c>
       <c r="D35" t="n">
-        <v>23.718</v>
+        <v>23.561</v>
       </c>
     </row>
     <row r="36">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10.338</v>
+        <v>10.53</v>
       </c>
       <c r="C36" t="n">
-        <v>120.291</v>
+        <v>121.491</v>
       </c>
       <c r="D36" t="n">
-        <v>21.677</v>
+        <v>21.775</v>
       </c>
     </row>
     <row r="37">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10.595</v>
+        <v>11.084</v>
       </c>
       <c r="C37" t="n">
-        <v>106.443</v>
+        <v>100.104</v>
       </c>
       <c r="D37" t="n">
-        <v>17.275</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="38">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10.112</v>
+        <v>10.362</v>
       </c>
       <c r="C38" t="n">
-        <v>107.756</v>
+        <v>104.342</v>
       </c>
       <c r="D38" t="n">
-        <v>17.949</v>
+        <v>18.133</v>
       </c>
     </row>
     <row r="39">
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10.56</v>
+        <v>10.544</v>
       </c>
       <c r="C39" t="n">
-        <v>104.111</v>
+        <v>102.614</v>
       </c>
       <c r="D39" t="n">
-        <v>20.366</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="40">
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>11.115</v>
+        <v>10.867</v>
       </c>
       <c r="C40" t="n">
-        <v>101.733</v>
+        <v>102.569</v>
       </c>
       <c r="D40" t="n">
-        <v>20.933</v>
+        <v>21.472</v>
       </c>
     </row>
     <row r="41">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>11.601</v>
+        <v>11.359</v>
       </c>
       <c r="C41" t="n">
-        <v>95.905</v>
+        <v>92.444</v>
       </c>
       <c r="D41" t="n">
-        <v>17.936</v>
+        <v>18.403</v>
       </c>
     </row>
     <row r="42">
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10.503</v>
+        <v>10.16</v>
       </c>
       <c r="C42" t="n">
-        <v>103.49</v>
+        <v>103.797</v>
       </c>
       <c r="D42" t="n">
-        <v>17.624</v>
+        <v>17.966</v>
       </c>
     </row>
     <row r="43">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>8.42</v>
+        <v>8.211</v>
       </c>
       <c r="C43" t="n">
-        <v>109.001</v>
+        <v>108.777</v>
       </c>
       <c r="D43" t="n">
-        <v>16.716</v>
+        <v>17.035</v>
       </c>
     </row>
     <row r="44">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7.441</v>
+        <v>7.292</v>
       </c>
       <c r="C44" t="n">
-        <v>111.629</v>
+        <v>109.658</v>
       </c>
       <c r="D44" t="n">
-        <v>15.72</v>
+        <v>15.498</v>
       </c>
     </row>
     <row r="45">
@@ -1133,13 +1133,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7.567</v>
+        <v>7.306</v>
       </c>
       <c r="C45" t="n">
-        <v>114.781</v>
+        <v>112.067</v>
       </c>
       <c r="D45" t="n">
-        <v>15.743</v>
+        <v>15.478</v>
       </c>
     </row>
     <row r="46">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6.949</v>
+        <v>6.62</v>
       </c>
       <c r="C46" t="n">
-        <v>120.574</v>
+        <v>118.468</v>
       </c>
       <c r="D46" t="n">
-        <v>15.466</v>
+        <v>15.271</v>
       </c>
     </row>
     <row r="47">
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>8.427</v>
+        <v>8.185</v>
       </c>
       <c r="C47" t="n">
-        <v>112.056</v>
+        <v>110.764</v>
       </c>
       <c r="D47" t="n">
-        <v>17.464</v>
+        <v>17.542</v>
       </c>
     </row>
     <row r="48">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>8.694000000000001</v>
+        <v>8.385999999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>107.211</v>
+        <v>103.193</v>
       </c>
       <c r="D48" t="n">
-        <v>16.941</v>
+        <v>16.387</v>
       </c>
     </row>
     <row r="49">
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8.249000000000001</v>
+        <v>8.199</v>
       </c>
       <c r="C49" t="n">
-        <v>117.79</v>
+        <v>115.225</v>
       </c>
       <c r="D49" t="n">
-        <v>16.671</v>
+        <v>16.338</v>
       </c>
     </row>
     <row r="50">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8.170999999999999</v>
+        <v>8.058</v>
       </c>
       <c r="C50" t="n">
-        <v>125.548</v>
+        <v>124.238</v>
       </c>
       <c r="D50" t="n">
-        <v>17.428</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="51">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>9.176</v>
+        <v>9.117000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>126.48</v>
+        <v>121.623</v>
       </c>
       <c r="D51" t="n">
-        <v>19.277</v>
+        <v>19.662</v>
       </c>
     </row>
     <row r="52">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>9.186</v>
+        <v>9.161</v>
       </c>
       <c r="C52" t="n">
-        <v>117.373</v>
+        <v>110.928</v>
       </c>
       <c r="D52" t="n">
-        <v>18.825</v>
+        <v>19.064</v>
       </c>
     </row>
     <row r="53">
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>9.427</v>
+        <v>9.923999999999999</v>
       </c>
       <c r="C53" t="n">
-        <v>108.419</v>
+        <v>103.574</v>
       </c>
       <c r="D53" t="n">
-        <v>17.365</v>
+        <v>17.786</v>
       </c>
     </row>
     <row r="54">
@@ -1277,13 +1277,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10.817</v>
+        <v>11.036</v>
       </c>
       <c r="C54" t="n">
-        <v>105.123</v>
+        <v>107.841</v>
       </c>
       <c r="D54" t="n">
-        <v>20.463</v>
+        <v>21.262</v>
       </c>
     </row>
     <row r="55">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10.811</v>
+        <v>11.501</v>
       </c>
       <c r="C55" t="n">
-        <v>107.915</v>
+        <v>108.187</v>
       </c>
       <c r="D55" t="n">
-        <v>19.809</v>
+        <v>20.611</v>
       </c>
     </row>
     <row r="56">
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10.498</v>
+        <v>11.011</v>
       </c>
       <c r="C56" t="n">
-        <v>107.373</v>
+        <v>108.082</v>
       </c>
       <c r="D56" t="n">
-        <v>19.33</v>
+        <v>19.671</v>
       </c>
     </row>
     <row r="57">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10.608</v>
+        <v>10.845</v>
       </c>
       <c r="C57" t="n">
-        <v>103.546</v>
+        <v>104.803</v>
       </c>
       <c r="D57" t="n">
-        <v>18.957</v>
+        <v>18.612</v>
       </c>
     </row>
     <row r="58">
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10.873</v>
+        <v>10.408</v>
       </c>
       <c r="C58" t="n">
-        <v>101.84</v>
+        <v>105.482</v>
       </c>
       <c r="D58" t="n">
-        <v>20.092</v>
+        <v>19.511</v>
       </c>
     </row>
     <row r="59">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10.813</v>
+        <v>10.528</v>
       </c>
       <c r="C59" t="n">
-        <v>102.426</v>
+        <v>105.449</v>
       </c>
       <c r="D59" t="n">
-        <v>19.878</v>
+        <v>19.386</v>
       </c>
     </row>
     <row r="60">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10.556</v>
+        <v>10.28</v>
       </c>
       <c r="C60" t="n">
-        <v>103.716</v>
+        <v>106.886</v>
       </c>
       <c r="D60" t="n">
-        <v>19.835</v>
+        <v>19.387</v>
       </c>
     </row>
     <row r="61">
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>11.259</v>
+        <v>10.991</v>
       </c>
       <c r="C61" t="n">
-        <v>98.956</v>
+        <v>101.772</v>
       </c>
       <c r="D61" t="n">
-        <v>19.581</v>
+        <v>19.305</v>
       </c>
     </row>
     <row r="62">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>12.704</v>
+        <v>12.459</v>
       </c>
       <c r="C62" t="n">
-        <v>95.241</v>
+        <v>94.55800000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>20.006</v>
+        <v>19.832</v>
       </c>
     </row>
     <row r="63">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>13.624</v>
+        <v>13.356</v>
       </c>
       <c r="C63" t="n">
-        <v>91.17100000000001</v>
+        <v>89.157</v>
       </c>
       <c r="D63" t="n">
-        <v>20.014</v>
+        <v>19.929</v>
       </c>
     </row>
     <row r="64">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>13.609</v>
+        <v>13.318</v>
       </c>
       <c r="C64" t="n">
-        <v>93.48999999999999</v>
+        <v>90.411</v>
       </c>
       <c r="D64" t="n">
-        <v>20.303</v>
+        <v>20.166</v>
       </c>
     </row>
     <row r="65">
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>14.003</v>
+        <v>13.675</v>
       </c>
       <c r="C65" t="n">
-        <v>93.07299999999999</v>
+        <v>89.261</v>
       </c>
       <c r="D65" t="n">
-        <v>20.534</v>
+        <v>20.346</v>
       </c>
     </row>
     <row r="66">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>12.916</v>
+        <v>12.615</v>
       </c>
       <c r="C66" t="n">
-        <v>96.86499999999999</v>
+        <v>92.45399999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>20.307</v>
+        <v>20.209</v>
       </c>
     </row>
     <row r="67">
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>11.124</v>
+        <v>10.773</v>
       </c>
       <c r="C67" t="n">
-        <v>109.899</v>
+        <v>108.792</v>
       </c>
       <c r="D67" t="n">
-        <v>19.913</v>
+        <v>20.102</v>
       </c>
     </row>
     <row r="68">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>10.056</v>
+        <v>9.683999999999999</v>
       </c>
       <c r="C68" t="n">
-        <v>116.088</v>
+        <v>115.856</v>
       </c>
       <c r="D68" t="n">
-        <v>19.596</v>
+        <v>19.944</v>
       </c>
     </row>
     <row r="69">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>10.594</v>
+        <v>10.235</v>
       </c>
       <c r="C69" t="n">
-        <v>112.206</v>
+        <v>110.165</v>
       </c>
       <c r="D69" t="n">
-        <v>19.621</v>
+        <v>19.917</v>
       </c>
     </row>
     <row r="70">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>10.629</v>
+        <v>10.273</v>
       </c>
       <c r="C70" t="n">
-        <v>101.692</v>
+        <v>98.99299999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>19.058</v>
+        <v>19.417</v>
       </c>
     </row>
     <row r="71">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>10.143</v>
+        <v>9.996</v>
       </c>
       <c r="C71" t="n">
-        <v>108.748</v>
+        <v>105.897</v>
       </c>
       <c r="D71" t="n">
-        <v>18.724</v>
+        <v>18.953</v>
       </c>
     </row>
     <row r="72">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>9.494999999999999</v>
+        <v>9.628</v>
       </c>
       <c r="C72" t="n">
-        <v>116.786</v>
+        <v>112.777</v>
       </c>
       <c r="D72" t="n">
-        <v>18.22</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="73">
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>9.045999999999999</v>
+        <v>9.391999999999999</v>
       </c>
       <c r="C73" t="n">
-        <v>122.125</v>
+        <v>116.773</v>
       </c>
       <c r="D73" t="n">
-        <v>17.873</v>
+        <v>17.567</v>
       </c>
     </row>
     <row r="74">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>9.147</v>
+        <v>9.438000000000001</v>
       </c>
       <c r="C74" t="n">
-        <v>120.373</v>
+        <v>114.89</v>
       </c>
       <c r="D74" t="n">
-        <v>17.978</v>
+        <v>17.705</v>
       </c>
     </row>
     <row r="75">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>9.199</v>
+        <v>9.496</v>
       </c>
       <c r="C75" t="n">
-        <v>118.95</v>
+        <v>113.048</v>
       </c>
       <c r="D75" t="n">
-        <v>17.81</v>
+        <v>17.505</v>
       </c>
     </row>
     <row r="76">
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>9.052</v>
+        <v>9.311999999999999</v>
       </c>
       <c r="C76" t="n">
-        <v>121.932</v>
+        <v>117.332</v>
       </c>
       <c r="D76" t="n">
-        <v>18.026</v>
+        <v>17.782</v>
       </c>
     </row>
     <row r="77">
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>8.808</v>
+        <v>9.007999999999999</v>
       </c>
       <c r="C77" t="n">
-        <v>126.153</v>
+        <v>123.568</v>
       </c>
       <c r="D77" t="n">
-        <v>18.419</v>
+        <v>18.256</v>
       </c>
     </row>
     <row r="78">
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>8.622</v>
+        <v>8.797000000000001</v>
       </c>
       <c r="C78" t="n">
-        <v>129.223</v>
+        <v>128.184</v>
       </c>
       <c r="D78" t="n">
-        <v>18.781</v>
+        <v>18.682</v>
       </c>
     </row>
     <row r="79">
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>8.645</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="C79" t="n">
-        <v>128.492</v>
+        <v>127.177</v>
       </c>
       <c r="D79" t="n">
-        <v>18.723</v>
+        <v>18.594</v>
       </c>
     </row>
     <row r="80">
@@ -1693,13 +1693,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>8.744999999999999</v>
+        <v>9</v>
       </c>
       <c r="C80" t="n">
-        <v>126.332</v>
+        <v>124.442</v>
       </c>
       <c r="D80" t="n">
-        <v>18.616</v>
+        <v>18.407</v>
       </c>
     </row>
     <row r="81">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>8.252000000000001</v>
+        <v>8.345000000000001</v>
       </c>
       <c r="C81" t="n">
-        <v>135.613</v>
+        <v>136.021</v>
       </c>
       <c r="D81" t="n">
-        <v>19.21</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="82">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7.563</v>
+        <v>7.428</v>
       </c>
       <c r="C82" t="n">
-        <v>148.069</v>
+        <v>151.246</v>
       </c>
       <c r="D82" t="n">
-        <v>19.815</v>
+        <v>20.128</v>
       </c>
     </row>
     <row r="83">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>7.153</v>
+        <v>6.92</v>
       </c>
       <c r="C83" t="n">
-        <v>156.183</v>
+        <v>160.244</v>
       </c>
       <c r="D83" t="n">
-        <v>20.123</v>
+        <v>20.693</v>
       </c>
     </row>
     <row r="84">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>7.287</v>
+        <v>7.142</v>
       </c>
       <c r="C84" t="n">
-        <v>153.96</v>
+        <v>156.291</v>
       </c>
       <c r="D84" t="n">
-        <v>19.843</v>
+        <v>20.381</v>
       </c>
     </row>
     <row r="85">
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6.876</v>
+        <v>6.666</v>
       </c>
       <c r="C85" t="n">
-        <v>159.575</v>
+        <v>162.581</v>
       </c>
       <c r="D85" t="n">
-        <v>19.677</v>
+        <v>20.137</v>
       </c>
     </row>
     <row r="86">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>8.343</v>
+        <v>8.192</v>
       </c>
       <c r="C86" t="n">
-        <v>138.955</v>
+        <v>142.091</v>
       </c>
       <c r="D86" t="n">
-        <v>20.424</v>
+        <v>20.917</v>
       </c>
     </row>
     <row r="87">
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>10.533</v>
+        <v>10.584</v>
       </c>
       <c r="C87" t="n">
-        <v>109.076</v>
+        <v>110.778</v>
       </c>
       <c r="D87" t="n">
-        <v>21.572</v>
+        <v>22.074</v>
       </c>
     </row>
     <row r="88">
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>12.046</v>
+        <v>12.251</v>
       </c>
       <c r="C88" t="n">
-        <v>89.434</v>
+        <v>89.708</v>
       </c>
       <c r="D88" t="n">
-        <v>22.687</v>
+        <v>23.062</v>
       </c>
     </row>
     <row r="89">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>11.663</v>
+        <v>11.823</v>
       </c>
       <c r="C89" t="n">
-        <v>95.245</v>
+        <v>95.619</v>
       </c>
       <c r="D89" t="n">
-        <v>22.635</v>
+        <v>22.931</v>
       </c>
     </row>
     <row r="90">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>11.853</v>
+        <v>12.017</v>
       </c>
       <c r="C90" t="n">
-        <v>93.53700000000001</v>
+        <v>93.453</v>
       </c>
       <c r="D90" t="n">
-        <v>22.439</v>
+        <v>22.695</v>
       </c>
     </row>
     <row r="91">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>11.094</v>
+        <v>11.184</v>
       </c>
       <c r="C91" t="n">
-        <v>96.437</v>
+        <v>95.502</v>
       </c>
       <c r="D91" t="n">
-        <v>21.419</v>
+        <v>21.304</v>
       </c>
     </row>
     <row r="92">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>10.002</v>
+        <v>9.983000000000001</v>
       </c>
       <c r="C92" t="n">
-        <v>101.61</v>
+        <v>100.007</v>
       </c>
       <c r="D92" t="n">
-        <v>20.524</v>
+        <v>19.915</v>
       </c>
     </row>
     <row r="93">
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>9.227</v>
+        <v>9.147</v>
       </c>
       <c r="C93" t="n">
-        <v>105.05</v>
+        <v>103.132</v>
       </c>
       <c r="D93" t="n">
-        <v>20.027</v>
+        <v>19.285</v>
       </c>
     </row>
     <row r="94">
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>9.433</v>
+        <v>9.363</v>
       </c>
       <c r="C94" t="n">
-        <v>104.308</v>
+        <v>102.252</v>
       </c>
       <c r="D94" t="n">
-        <v>20.033</v>
+        <v>19.366</v>
       </c>
     </row>
     <row r="95">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>8.94</v>
+        <v>8.829000000000001</v>
       </c>
       <c r="C95" t="n">
-        <v>107.333</v>
+        <v>106.027</v>
       </c>
       <c r="D95" t="n">
-        <v>19.829</v>
+        <v>19.103</v>
       </c>
     </row>
     <row r="96">
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>11.021</v>
+        <v>10.932</v>
       </c>
       <c r="C96" t="n">
-        <v>101.31</v>
+        <v>97.72199999999999</v>
       </c>
       <c r="D96" t="n">
-        <v>19.958</v>
+        <v>19.248</v>
       </c>
     </row>
     <row r="97">
@@ -1965,13 +1965,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13.949</v>
+        <v>13.914</v>
       </c>
       <c r="C97" t="n">
-        <v>91.46899999999999</v>
+        <v>84.002</v>
       </c>
       <c r="D97" t="n">
-        <v>20.271</v>
+        <v>19.649</v>
       </c>
     </row>
     <row r="98">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>16.053</v>
+        <v>16.026</v>
       </c>
       <c r="C98" t="n">
-        <v>84.458</v>
+        <v>74.405</v>
       </c>
       <c r="D98" t="n">
-        <v>20.432</v>
+        <v>19.874</v>
       </c>
     </row>
     <row r="99">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>15.604</v>
+        <v>15.498</v>
       </c>
       <c r="C99" t="n">
-        <v>84.986</v>
+        <v>75.636</v>
       </c>
       <c r="D99" t="n">
-        <v>20.326</v>
+        <v>19.769</v>
       </c>
     </row>
     <row r="100">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>15.87</v>
+        <v>15.756</v>
       </c>
       <c r="C100" t="n">
-        <v>81.759</v>
+        <v>72.318</v>
       </c>
       <c r="D100" t="n">
-        <v>19.948</v>
+        <v>19.372</v>
       </c>
     </row>
     <row r="101">
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>14.913</v>
+        <v>14.816</v>
       </c>
       <c r="C101" t="n">
-        <v>88.545</v>
+        <v>80.173</v>
       </c>
       <c r="D101" t="n">
-        <v>21.351</v>
+        <v>20.897</v>
       </c>
     </row>
     <row r="102">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>13.566</v>
+        <v>13.482</v>
       </c>
       <c r="C102" t="n">
-        <v>99.294</v>
+        <v>92.99299999999999</v>
       </c>
       <c r="D102" t="n">
-        <v>23.431</v>
+        <v>23.181</v>
       </c>
     </row>
     <row r="103">
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>12.63</v>
+        <v>12.533</v>
       </c>
       <c r="C103" t="n">
-        <v>106.97</v>
+        <v>102.076</v>
       </c>
       <c r="D103" t="n">
-        <v>25.107</v>
+        <v>24.988</v>
       </c>
     </row>
     <row r="104">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>12.865</v>
+        <v>12.781</v>
       </c>
       <c r="C104" t="n">
-        <v>105.324</v>
+        <v>99.94499999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>24.961</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="105">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>13.086</v>
+        <v>13.069</v>
       </c>
       <c r="C105" t="n">
-        <v>104.298</v>
+        <v>97.33799999999999</v>
       </c>
       <c r="D105" t="n">
-        <v>25.221</v>
+        <v>24.961</v>
       </c>
     </row>
     <row r="106">
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>12.198</v>
+        <v>11.914</v>
       </c>
       <c r="C106" t="n">
-        <v>108.245</v>
+        <v>106.685</v>
       </c>
       <c r="D106" t="n">
         <v>23.989</v>
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>10.942</v>
+        <v>10.283</v>
       </c>
       <c r="C107" t="n">
-        <v>113.976</v>
+        <v>120.036</v>
       </c>
       <c r="D107" t="n">
-        <v>22.39</v>
+        <v>22.736</v>
       </c>
     </row>
     <row r="108">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>10.064</v>
+        <v>9.128</v>
       </c>
       <c r="C108" t="n">
-        <v>117.989</v>
+        <v>129.367</v>
       </c>
       <c r="D108" t="n">
-        <v>21.305</v>
+        <v>21.871</v>
       </c>
     </row>
     <row r="109">
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>10.299</v>
+        <v>9.411</v>
       </c>
       <c r="C109" t="n">
-        <v>116.97</v>
+        <v>127.054</v>
       </c>
       <c r="D109" t="n">
-        <v>21.591</v>
+        <v>22.084</v>
       </c>
     </row>
     <row r="110">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>10.153</v>
+        <v>9.228999999999999</v>
       </c>
       <c r="C110" t="n">
-        <v>118.551</v>
+        <v>129.676</v>
       </c>
       <c r="D110" t="n">
-        <v>21.648</v>
+        <v>22.216</v>
       </c>
     </row>
     <row r="111">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>10.719</v>
+        <v>9.956</v>
       </c>
       <c r="C111" t="n">
-        <v>112.222</v>
+        <v>119.01</v>
       </c>
       <c r="D111" t="n">
-        <v>21.433</v>
+        <v>21.668</v>
       </c>
     </row>
     <row r="112">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>11.537</v>
+        <v>10.985</v>
       </c>
       <c r="C112" t="n">
-        <v>103.793</v>
+        <v>104.407</v>
       </c>
       <c r="D112" t="n">
-        <v>21.279</v>
+        <v>21.026</v>
       </c>
     </row>
     <row r="113">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>12.151</v>
+        <v>11.711</v>
       </c>
       <c r="C113" t="n">
-        <v>97.693</v>
+        <v>94.435</v>
       </c>
       <c r="D113" t="n">
-        <v>21.201</v>
+        <v>20.645</v>
       </c>
     </row>
     <row r="114">
@@ -2237,13 +2237,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>12.089</v>
+        <v>11.627</v>
       </c>
       <c r="C114" t="n">
-        <v>99.29900000000001</v>
+        <v>97.217</v>
       </c>
       <c r="D114" t="n">
-        <v>21.345</v>
+        <v>20.901</v>
       </c>
     </row>
     <row r="115">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>12.265</v>
+        <v>11.863</v>
       </c>
       <c r="C115" t="n">
-        <v>97.697</v>
+        <v>94.94199999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>21.397</v>
+        <v>20.911</v>
       </c>
     </row>
     <row r="116">
@@ -2269,13 +2269,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>11.861</v>
+        <v>11.47</v>
       </c>
       <c r="C116" t="n">
-        <v>102.47</v>
+        <v>100.398</v>
       </c>
       <c r="D116" t="n">
-        <v>21.199</v>
+        <v>20.715</v>
       </c>
     </row>
     <row r="117">
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>11.258</v>
+        <v>10.755</v>
       </c>
       <c r="C117" t="n">
-        <v>109.174</v>
+        <v>109.056</v>
       </c>
       <c r="D117" t="n">
-        <v>20.827</v>
+        <v>20.447</v>
       </c>
     </row>
     <row r="118">
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>10.601</v>
+        <v>10.127</v>
       </c>
       <c r="C118" t="n">
-        <v>114.263</v>
+        <v>115.46</v>
       </c>
       <c r="D118" t="n">
-        <v>20.367</v>
+        <v>20.028</v>
       </c>
     </row>
     <row r="119">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>10.556</v>
+        <v>10.154</v>
       </c>
       <c r="C119" t="n">
-        <v>113.277</v>
+        <v>114.323</v>
       </c>
       <c r="D119" t="n">
-        <v>20.362</v>
+        <v>19.985</v>
       </c>
     </row>
     <row r="120">
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>10.809</v>
+        <v>10.379</v>
       </c>
       <c r="C120" t="n">
-        <v>112.75</v>
+        <v>113.698</v>
       </c>
       <c r="D120" t="n">
-        <v>20.61</v>
+        <v>20.194</v>
       </c>
     </row>
     <row r="121">
@@ -2349,13 +2349,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>10.758</v>
+        <v>10.284</v>
       </c>
       <c r="C121" t="n">
-        <v>112.103</v>
+        <v>114.803</v>
       </c>
       <c r="D121" t="n">
-        <v>20.845</v>
+        <v>20.553</v>
       </c>
     </row>
     <row r="122">
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>10.31</v>
+        <v>9.898999999999999</v>
       </c>
       <c r="C122" t="n">
-        <v>111.751</v>
+        <v>116.539</v>
       </c>
       <c r="D122" t="n">
-        <v>20.77</v>
+        <v>20.601</v>
       </c>
     </row>
     <row r="123">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>9.874000000000001</v>
+        <v>9.529</v>
       </c>
       <c r="C123" t="n">
-        <v>112.34</v>
+        <v>118.265</v>
       </c>
       <c r="D123" t="n">
-        <v>20.648</v>
+        <v>20.548</v>
       </c>
     </row>
     <row r="124">
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>9.965999999999999</v>
+        <v>9.587</v>
       </c>
       <c r="C124" t="n">
-        <v>112.504</v>
+        <v>118.028</v>
       </c>
       <c r="D124" t="n">
-        <v>20.697</v>
+        <v>20.554</v>
       </c>
     </row>
     <row r="125">
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>9.952999999999999</v>
+        <v>9.536</v>
       </c>
       <c r="C125" t="n">
-        <v>111.518</v>
+        <v>117.589</v>
       </c>
       <c r="D125" t="n">
-        <v>20.731</v>
+        <v>20.691</v>
       </c>
     </row>
     <row r="126">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>10.395</v>
+        <v>10.051</v>
       </c>
       <c r="C126" t="n">
-        <v>115.594</v>
+        <v>118.308</v>
       </c>
       <c r="D126" t="n">
-        <v>20.961</v>
+        <v>20.825</v>
       </c>
     </row>
     <row r="127">
@@ -2445,13 +2445,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>10.901</v>
+        <v>10.704</v>
       </c>
       <c r="C127" t="n">
-        <v>121.856</v>
+        <v>119.623</v>
       </c>
       <c r="D127" t="n">
-        <v>21.229</v>
+        <v>20.821</v>
       </c>
     </row>
     <row r="128">
@@ -2461,13 +2461,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>11.182</v>
+        <v>11.069</v>
       </c>
       <c r="C128" t="n">
-        <v>126.14</v>
+        <v>120.91</v>
       </c>
       <c r="D128" t="n">
-        <v>21.36</v>
+        <v>20.722</v>
       </c>
     </row>
     <row r="129">
@@ -2477,13 +2477,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>11.081</v>
+        <v>10.929</v>
       </c>
       <c r="C129" t="n">
-        <v>125.05</v>
+        <v>120.82</v>
       </c>
       <c r="D129" t="n">
-        <v>21.295</v>
+        <v>20.728</v>
       </c>
     </row>
     <row r="130">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>10.967</v>
+        <v>10.822</v>
       </c>
       <c r="C130" t="n">
-        <v>127.238</v>
+        <v>123.032</v>
       </c>
       <c r="D130" t="n">
-        <v>21.375</v>
+        <v>20.856</v>
       </c>
     </row>
     <row r="131">
@@ -2509,13 +2509,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>11.492</v>
+        <v>11.243</v>
       </c>
       <c r="C131" t="n">
-        <v>118.294</v>
+        <v>115.412</v>
       </c>
       <c r="D131" t="n">
-        <v>21.297</v>
+        <v>20.944</v>
       </c>
     </row>
     <row r="132">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>12.242</v>
+        <v>11.865</v>
       </c>
       <c r="C132" t="n">
-        <v>105.539</v>
+        <v>104.023</v>
       </c>
       <c r="D132" t="n">
-        <v>21.103</v>
+        <v>20.929</v>
       </c>
     </row>
     <row r="133">
@@ -2541,13 +2541,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>12.707</v>
+        <v>12.179</v>
       </c>
       <c r="C133" t="n">
-        <v>96.81999999999999</v>
+        <v>96.443</v>
       </c>
       <c r="D133" t="n">
-        <v>20.912</v>
+        <v>20.856</v>
       </c>
     </row>
     <row r="134">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>12.588</v>
+        <v>12.083</v>
       </c>
       <c r="C134" t="n">
-        <v>98.932</v>
+        <v>98.274</v>
       </c>
       <c r="D134" t="n">
-        <v>20.937</v>
+        <v>20.848</v>
       </c>
     </row>
     <row r="135">
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>12.604</v>
+        <v>12.123</v>
       </c>
       <c r="C135" t="n">
-        <v>99.331</v>
+        <v>98.199</v>
       </c>
       <c r="D135" t="n">
-        <v>20.897</v>
+        <v>20.826</v>
       </c>
     </row>
     <row r="136">
@@ -2589,13 +2589,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>12.66</v>
+        <v>12.158</v>
       </c>
       <c r="C136" t="n">
-        <v>98.116</v>
+        <v>97.932</v>
       </c>
       <c r="D136" t="n">
-        <v>21.107</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="137">
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>12.719</v>
+        <v>12.131</v>
       </c>
       <c r="C137" t="n">
-        <v>96.523</v>
+        <v>98.104</v>
       </c>
       <c r="D137" t="n">
-        <v>21.367</v>
+        <v>21.355</v>
       </c>
     </row>
     <row r="138">
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>12.772</v>
+        <v>12.2</v>
       </c>
       <c r="C138" t="n">
-        <v>95.316</v>
+        <v>98.376</v>
       </c>
       <c r="D138" t="n">
-        <v>21.849</v>
+        <v>21.855</v>
       </c>
     </row>
     <row r="139">
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>13.092</v>
+        <v>12.594</v>
       </c>
       <c r="C139" t="n">
-        <v>95.069</v>
+        <v>95.999</v>
       </c>
       <c r="D139" t="n">
-        <v>21.504</v>
+        <v>21.374</v>
       </c>
     </row>
     <row r="140">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>13.665</v>
+        <v>13.22</v>
       </c>
       <c r="C140" t="n">
-        <v>93.13800000000001</v>
+        <v>91.315</v>
       </c>
       <c r="D140" t="n">
-        <v>20.793</v>
+        <v>20.501</v>
       </c>
     </row>
     <row r="141">
@@ -2669,13 +2669,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>13.078</v>
+        <v>12.495</v>
       </c>
       <c r="C141" t="n">
-        <v>97.413</v>
+        <v>96.056</v>
       </c>
       <c r="D141" t="n">
-        <v>20.718</v>
+        <v>20.348</v>
       </c>
     </row>
     <row r="142">
@@ -2685,13 +2685,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>11.759</v>
+        <v>10.987</v>
       </c>
       <c r="C142" t="n">
-        <v>104.651</v>
+        <v>106.71</v>
       </c>
       <c r="D142" t="n">
-        <v>21.498</v>
+        <v>21.271</v>
       </c>
     </row>
     <row r="143">
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>10.851</v>
+        <v>9.942</v>
       </c>
       <c r="C143" t="n">
-        <v>109.487</v>
+        <v>113.799</v>
       </c>
       <c r="D143" t="n">
-        <v>21.963</v>
+        <v>21.803</v>
       </c>
     </row>
     <row r="144">
@@ -2717,13 +2717,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>11.082</v>
+        <v>10.227</v>
       </c>
       <c r="C144" t="n">
-        <v>108.083</v>
+        <v>111.785</v>
       </c>
       <c r="D144" t="n">
-        <v>21.844</v>
+        <v>21.664</v>
       </c>
     </row>
     <row r="145">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>11.403</v>
+        <v>10.512</v>
       </c>
       <c r="C145" t="n">
-        <v>106.101</v>
+        <v>110.118</v>
       </c>
       <c r="D145" t="n">
-        <v>22.07</v>
+        <v>21.907</v>
       </c>
     </row>
     <row r="146">
@@ -2749,13 +2749,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>10.418</v>
+        <v>9.821</v>
       </c>
       <c r="C146" t="n">
-        <v>113.044</v>
+        <v>113.954</v>
       </c>
       <c r="D146" t="n">
-        <v>21.132</v>
+        <v>20.889</v>
       </c>
     </row>
     <row r="147">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>9.015000000000001</v>
+        <v>8.691000000000001</v>
       </c>
       <c r="C147" t="n">
-        <v>122.489</v>
+        <v>120.362</v>
       </c>
       <c r="D147" t="n">
-        <v>19.677</v>
+        <v>19.445</v>
       </c>
     </row>
     <row r="148">
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>8.026</v>
+        <v>7.897</v>
       </c>
       <c r="C148" t="n">
-        <v>134.605</v>
+        <v>131.623</v>
       </c>
       <c r="D148" t="n">
-        <v>18.576</v>
+        <v>18.527</v>
       </c>
     </row>
     <row r="149">
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>8.327</v>
+        <v>8.151</v>
       </c>
       <c r="C149" t="n">
-        <v>138.958</v>
+        <v>136.999</v>
       </c>
       <c r="D149" t="n">
-        <v>18.743</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="150">
@@ -2813,13 +2813,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>8.353</v>
+        <v>8.256</v>
       </c>
       <c r="C150" t="n">
-        <v>132.184</v>
+        <v>128.268</v>
       </c>
       <c r="D150" t="n">
-        <v>18.417</v>
+        <v>18.509</v>
       </c>
     </row>
     <row r="151">
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>8.419</v>
+        <v>8.314</v>
       </c>
       <c r="C151" t="n">
-        <v>123.617</v>
+        <v>120.025</v>
       </c>
       <c r="D151" t="n">
-        <v>18.516</v>
+        <v>18.486</v>
       </c>
     </row>
     <row r="152">
@@ -2845,13 +2845,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>8.454000000000001</v>
+        <v>8.324</v>
       </c>
       <c r="C152" t="n">
-        <v>123.382</v>
+        <v>122.182</v>
       </c>
       <c r="D152" t="n">
-        <v>18.958</v>
+        <v>18.967</v>
       </c>
     </row>
     <row r="153">
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>8.488</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="C153" t="n">
-        <v>129.848</v>
+        <v>130.344</v>
       </c>
       <c r="D153" t="n">
-        <v>19.53</v>
+        <v>19.619</v>
       </c>
     </row>
     <row r="154">
@@ -2877,13 +2877,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>8.481999999999999</v>
+        <v>8.307</v>
       </c>
       <c r="C154" t="n">
-        <v>129.338</v>
+        <v>129.002</v>
       </c>
       <c r="D154" t="n">
-        <v>19.478</v>
+        <v>19.586</v>
       </c>
     </row>
     <row r="155">
@@ -2893,13 +2893,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>8.484999999999999</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="C155" t="n">
-        <v>130.202</v>
+        <v>130.411</v>
       </c>
       <c r="D155" t="n">
-        <v>19.522</v>
+        <v>19.672</v>
       </c>
     </row>
     <row r="156">
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>8.371</v>
+        <v>8.255000000000001</v>
       </c>
       <c r="C156" t="n">
-        <v>125.154</v>
+        <v>124.391</v>
       </c>
       <c r="D156" t="n">
-        <v>18.983</v>
+        <v>18.924</v>
       </c>
     </row>
     <row r="157">
@@ -2925,13 +2925,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>8.292</v>
+        <v>8.278</v>
       </c>
       <c r="C157" t="n">
-        <v>118.069</v>
+        <v>114.992</v>
       </c>
       <c r="D157" t="n">
-        <v>18.274</v>
+        <v>17.881</v>
       </c>
     </row>
     <row r="158">
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>8.349</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="C158" t="n">
-        <v>113.204</v>
+        <v>107.402</v>
       </c>
       <c r="D158" t="n">
-        <v>17.783</v>
+        <v>17.184</v>
       </c>
     </row>
     <row r="159">
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>8.375999999999999</v>
+        <v>8.494999999999999</v>
       </c>
       <c r="C159" t="n">
-        <v>114.806</v>
+        <v>109.084</v>
       </c>
       <c r="D159" t="n">
-        <v>17.932</v>
+        <v>17.379</v>
       </c>
     </row>
     <row r="160">
@@ -2973,13 +2973,13 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>8.300000000000001</v>
+        <v>8.374000000000001</v>
       </c>
       <c r="C160" t="n">
-        <v>113.86</v>
+        <v>108.072</v>
       </c>
       <c r="D160" t="n">
-        <v>17.857</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="161">
@@ -2989,13 +2989,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>8.164999999999999</v>
+        <v>8.226000000000001</v>
       </c>
       <c r="C161" t="n">
-        <v>120.826</v>
+        <v>116.698</v>
       </c>
       <c r="D161" t="n">
-        <v>18.231</v>
+        <v>17.823</v>
       </c>
     </row>
     <row r="162">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>8.090999999999999</v>
+        <v>8.162000000000001</v>
       </c>
       <c r="C162" t="n">
-        <v>129.461</v>
+        <v>127.413</v>
       </c>
       <c r="D162" t="n">
-        <v>18.503</v>
+        <v>18.358</v>
       </c>
     </row>
     <row r="163">
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>8.18</v>
+        <v>8.323</v>
       </c>
       <c r="C163" t="n">
-        <v>137.145</v>
+        <v>136.953</v>
       </c>
       <c r="D163" t="n">
-        <v>19.797</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="164">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>8.215999999999999</v>
+        <v>8.372</v>
       </c>
       <c r="C164" t="n">
-        <v>135.701</v>
+        <v>134.995</v>
       </c>
       <c r="D164" t="n">
-        <v>19.85</v>
+        <v>19.924</v>
       </c>
     </row>
     <row r="165">
@@ -3053,13 +3053,13 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>7.942</v>
+        <v>8.129</v>
       </c>
       <c r="C165" t="n">
-        <v>140.343</v>
+        <v>139.855</v>
       </c>
       <c r="D165" t="n">
-        <v>20.364</v>
+        <v>20.492</v>
       </c>
     </row>
     <row r="166">
@@ -3069,13 +3069,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>9.321</v>
+        <v>9.603999999999999</v>
       </c>
       <c r="C166" t="n">
-        <v>124.016</v>
+        <v>122.461</v>
       </c>
       <c r="D166" t="n">
-        <v>20.281</v>
+        <v>20.198</v>
       </c>
     </row>
     <row r="167">
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>11.012</v>
+        <v>11.259</v>
       </c>
       <c r="C167" t="n">
-        <v>102.674</v>
+        <v>101.011</v>
       </c>
       <c r="D167" t="n">
-        <v>20.98</v>
+        <v>20.718</v>
       </c>
     </row>
     <row r="168">
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>11.846</v>
+        <v>11.875</v>
       </c>
       <c r="C168" t="n">
-        <v>87.017</v>
+        <v>85.878</v>
       </c>
       <c r="D168" t="n">
-        <v>20.694</v>
+        <v>20.268</v>
       </c>
     </row>
     <row r="169">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>11.231</v>
+        <v>11.059</v>
       </c>
       <c r="C169" t="n">
-        <v>91.66</v>
+        <v>91.771</v>
       </c>
       <c r="D169" t="n">
-        <v>20.823</v>
+        <v>20.474</v>
       </c>
     </row>
     <row r="170">
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>11.174</v>
+        <v>10.992</v>
       </c>
       <c r="C170" t="n">
-        <v>90.619</v>
+        <v>91.02800000000001</v>
       </c>
       <c r="D170" t="n">
-        <v>20.539</v>
+        <v>20.152</v>
       </c>
     </row>
     <row r="171">
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>11.844</v>
+        <v>11.692</v>
       </c>
       <c r="C171" t="n">
-        <v>93.411</v>
+        <v>92.428</v>
       </c>
       <c r="D171" t="n">
-        <v>21.799</v>
+        <v>21.467</v>
       </c>
     </row>
     <row r="172">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>12.749</v>
+        <v>12.692</v>
       </c>
       <c r="C172" t="n">
-        <v>97.429</v>
+        <v>94.495</v>
       </c>
       <c r="D172" t="n">
-        <v>23.557</v>
+        <v>23.328</v>
       </c>
     </row>
     <row r="173">
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>13.371</v>
+        <v>13.365</v>
       </c>
       <c r="C173" t="n">
-        <v>100.454</v>
+        <v>95.94499999999999</v>
       </c>
       <c r="D173" t="n">
-        <v>24.786</v>
+        <v>24.616</v>
       </c>
     </row>
     <row r="174">
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>13.209</v>
+        <v>13.179</v>
       </c>
       <c r="C174" t="n">
-        <v>99.895</v>
+        <v>95.58199999999999</v>
       </c>
       <c r="D174" t="n">
-        <v>24.501</v>
+        <v>24.298</v>
       </c>
     </row>
     <row r="175">
@@ -3213,13 +3213,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>13.169</v>
+        <v>13.132</v>
       </c>
       <c r="C175" t="n">
-        <v>101.201</v>
+        <v>96.714</v>
       </c>
       <c r="D175" t="n">
-        <v>24.917</v>
+        <v>24.727</v>
       </c>
     </row>
     <row r="176">
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>13.395</v>
+        <v>13.432</v>
       </c>
       <c r="C176" t="n">
-        <v>96.593</v>
+        <v>91.681</v>
       </c>
       <c r="D176" t="n">
-        <v>23.325</v>
+        <v>23.058</v>
       </c>
     </row>
     <row r="177">
@@ -3245,13 +3245,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>13.666</v>
+        <v>13.79</v>
       </c>
       <c r="C177" t="n">
-        <v>90.319</v>
+        <v>84.90600000000001</v>
       </c>
       <c r="D177" t="n">
-        <v>21.075</v>
+        <v>20.737</v>
       </c>
     </row>
     <row r="178">
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>13.842</v>
+        <v>14.048</v>
       </c>
       <c r="C178" t="n">
-        <v>85.739</v>
+        <v>80.002</v>
       </c>
       <c r="D178" t="n">
-        <v>19.454</v>
+        <v>19.06</v>
       </c>
     </row>
     <row r="179">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>13.765</v>
+        <v>13.986</v>
       </c>
       <c r="C179" t="n">
-        <v>87.042</v>
+        <v>81.126</v>
       </c>
       <c r="D179" t="n">
-        <v>19.858</v>
+        <v>19.467</v>
       </c>
     </row>
     <row r="180">
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>13.871</v>
+        <v>14.119</v>
       </c>
       <c r="C180" t="n">
-        <v>86.023</v>
+        <v>79.465</v>
       </c>
       <c r="D180" t="n">
-        <v>19.547</v>
+        <v>19.12</v>
       </c>
     </row>
     <row r="181">
@@ -3309,13 +3309,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>13.416</v>
+        <v>13.528</v>
       </c>
       <c r="C181" t="n">
-        <v>91.614</v>
+        <v>87.232</v>
       </c>
       <c r="D181" t="n">
-        <v>20.978</v>
+        <v>20.492</v>
       </c>
     </row>
     <row r="182">
@@ -3325,13 +3325,13 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>12.78</v>
+        <v>12.716</v>
       </c>
       <c r="C182" t="n">
-        <v>99.22799999999999</v>
+        <v>97.81</v>
       </c>
       <c r="D182" t="n">
-        <v>22.898</v>
+        <v>22.34</v>
       </c>
     </row>
     <row r="183">
@@ -3341,13 +3341,13 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>12.346</v>
+        <v>12.152</v>
       </c>
       <c r="C183" t="n">
-        <v>104.667</v>
+        <v>105.089</v>
       </c>
       <c r="D183" t="n">
-        <v>24.325</v>
+        <v>23.682</v>
       </c>
     </row>
     <row r="184">
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>12.456</v>
+        <v>12.301</v>
       </c>
       <c r="C184" t="n">
-        <v>104.144</v>
+        <v>103.661</v>
       </c>
       <c r="D184" t="n">
-        <v>24.134</v>
+        <v>23.47</v>
       </c>
     </row>
     <row r="185">
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>12.823</v>
+        <v>12.624</v>
       </c>
       <c r="C185" t="n">
-        <v>102.756</v>
+        <v>102.478</v>
       </c>
       <c r="D185" t="n">
-        <v>24.849</v>
+        <v>24.104</v>
       </c>
     </row>
     <row r="186">
@@ -3389,13 +3389,13 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>11.585</v>
+        <v>11.354</v>
       </c>
       <c r="C186" t="n">
-        <v>107.489</v>
+        <v>107.686</v>
       </c>
       <c r="D186" t="n">
-        <v>22.957</v>
+        <v>22.446</v>
       </c>
     </row>
     <row r="187">
@@ -3405,13 +3405,13 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>9.766999999999999</v>
+        <v>9.506</v>
       </c>
       <c r="C187" t="n">
-        <v>113.48</v>
+        <v>114.021</v>
       </c>
       <c r="D187" t="n">
-        <v>20.152</v>
+        <v>19.942</v>
       </c>
     </row>
     <row r="188">
@@ -3421,13 +3421,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>8.420999999999999</v>
+        <v>8.186999999999999</v>
       </c>
       <c r="C188" t="n">
-        <v>125.44</v>
+        <v>126.51</v>
       </c>
       <c r="D188" t="n">
-        <v>18.214</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="189">
@@ -3437,13 +3437,13 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>8.673</v>
+        <v>8.420999999999999</v>
       </c>
       <c r="C189" t="n">
-        <v>125.537</v>
+        <v>126.722</v>
       </c>
       <c r="D189" t="n">
-        <v>18.723</v>
+        <v>18.553</v>
       </c>
     </row>
     <row r="190">
@@ -3453,13 +3453,13 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>8.750999999999999</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="C190" t="n">
-        <v>128.001</v>
+        <v>129.969</v>
       </c>
       <c r="D190" t="n">
-        <v>18.758</v>
+        <v>18.552</v>
       </c>
     </row>
     <row r="191">
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>8.397</v>
+        <v>8.176</v>
       </c>
       <c r="C191" t="n">
-        <v>130.379</v>
+        <v>130.865</v>
       </c>
       <c r="D191" t="n">
-        <v>18.816</v>
+        <v>18.591</v>
       </c>
     </row>
     <row r="192">
@@ -3485,13 +3485,13 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>7.919</v>
+        <v>7.808</v>
       </c>
       <c r="C192" t="n">
-        <v>138.491</v>
+        <v>137.432</v>
       </c>
       <c r="D192" t="n">
-        <v>18.945</v>
+        <v>18.725</v>
       </c>
     </row>
     <row r="193">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>7.553</v>
+        <v>7.515</v>
       </c>
       <c r="C193" t="n">
-        <v>138.695</v>
+        <v>136.177</v>
       </c>
       <c r="D193" t="n">
-        <v>18.957</v>
+        <v>18.702</v>
       </c>
     </row>
     <row r="194">
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>7.651</v>
+        <v>7.591</v>
       </c>
       <c r="C194" t="n">
-        <v>138.159</v>
+        <v>136.078</v>
       </c>
       <c r="D194" t="n">
-        <v>18.954</v>
+        <v>18.714</v>
       </c>
     </row>
     <row r="195">
@@ -3533,13 +3533,13 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7.252</v>
+        <v>7.249</v>
       </c>
       <c r="C195" t="n">
-        <v>138.971</v>
+        <v>137.13</v>
       </c>
       <c r="D195" t="n">
-        <v>18.506</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="196">
@@ -3549,13 +3549,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>9.101000000000001</v>
+        <v>8.795</v>
       </c>
       <c r="C196" t="n">
-        <v>135.408</v>
+        <v>132.193</v>
       </c>
       <c r="D196" t="n">
-        <v>20.635</v>
+        <v>20.425</v>
       </c>
     </row>
     <row r="197">
@@ -3565,13 +3565,13 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>10.365</v>
+        <v>10.014</v>
       </c>
       <c r="C197" t="n">
-        <v>129.79</v>
+        <v>126.352</v>
       </c>
       <c r="D197" t="n">
-        <v>21.927</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="198">
@@ -3581,13 +3581,13 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>10.874</v>
+        <v>10.702</v>
       </c>
       <c r="C198" t="n">
-        <v>119.737</v>
+        <v>116.936</v>
       </c>
       <c r="D198" t="n">
-        <v>22.134</v>
+        <v>21.994</v>
       </c>
     </row>
     <row r="199">
@@ -3597,13 +3597,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>9.992000000000001</v>
+        <v>10.043</v>
       </c>
       <c r="C199" t="n">
-        <v>116.122</v>
+        <v>113.868</v>
       </c>
       <c r="D199" t="n">
-        <v>21.317</v>
+        <v>21.363</v>
       </c>
     </row>
     <row r="200">
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>11.615</v>
+        <v>11.536</v>
       </c>
       <c r="C200" t="n">
-        <v>111.205</v>
+        <v>108.979</v>
       </c>
       <c r="D200" t="n">
-        <v>22.877</v>
+        <v>22.975</v>
       </c>
     </row>
     <row r="201">
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>11.755</v>
+        <v>11.77</v>
       </c>
       <c r="C201" t="n">
-        <v>114.574</v>
+        <v>111.662</v>
       </c>
       <c r="D201" t="n">
-        <v>22.847</v>
+        <v>22.678</v>
       </c>
     </row>
     <row r="202">
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>10.534</v>
+        <v>10.593</v>
       </c>
       <c r="C202" t="n">
-        <v>116.205</v>
+        <v>113.053</v>
       </c>
       <c r="D202" t="n">
-        <v>20.485</v>
+        <v>20.187</v>
       </c>
     </row>
     <row r="203">
@@ -3661,13 +3661,13 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>9.073</v>
+        <v>9.225</v>
       </c>
       <c r="C203" t="n">
-        <v>129.253</v>
+        <v>126.322</v>
       </c>
       <c r="D203" t="n">
-        <v>19.929</v>
+        <v>19.936</v>
       </c>
     </row>
     <row r="204">
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>9.470000000000001</v>
+        <v>9.378</v>
       </c>
       <c r="C204" t="n">
-        <v>131.277</v>
+        <v>130.506</v>
       </c>
       <c r="D204" t="n">
-        <v>21.408</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="205">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>10.287</v>
+        <v>10.169</v>
       </c>
       <c r="C205" t="n">
-        <v>133.53</v>
+        <v>133.379</v>
       </c>
       <c r="D205" t="n">
-        <v>23.49</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="206">
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>9.683</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C206" t="n">
-        <v>138.353</v>
+        <v>138.49</v>
       </c>
       <c r="D206" t="n">
-        <v>22.661</v>
+        <v>22.812</v>
       </c>
     </row>
     <row r="207">
@@ -3725,13 +3725,13 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>9.526</v>
+        <v>9.494</v>
       </c>
       <c r="C207" t="n">
-        <v>141.957</v>
+        <v>139.565</v>
       </c>
       <c r="D207" t="n">
-        <v>21.43</v>
+        <v>21.711</v>
       </c>
     </row>
     <row r="208">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>9.356</v>
+        <v>9.278</v>
       </c>
       <c r="C208" t="n">
-        <v>140.19</v>
+        <v>135.585</v>
       </c>
       <c r="D208" t="n">
-        <v>20.27</v>
+        <v>20.444</v>
       </c>
     </row>
     <row r="209">
@@ -3757,13 +3757,13 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>10.181</v>
+        <v>9.964</v>
       </c>
       <c r="C209" t="n">
-        <v>127.348</v>
+        <v>124.492</v>
       </c>
       <c r="D209" t="n">
-        <v>21.193</v>
+        <v>21.242</v>
       </c>
     </row>
     <row r="210">
@@ -3773,13 +3773,13 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>9.077999999999999</v>
+        <v>8.647</v>
       </c>
       <c r="C210" t="n">
-        <v>131.592</v>
+        <v>134.951</v>
       </c>
       <c r="D210" t="n">
-        <v>21.115</v>
+        <v>21.091</v>
       </c>
     </row>
     <row r="211">
@@ -3789,13 +3789,13 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>9.132999999999999</v>
+        <v>8.692</v>
       </c>
       <c r="C211" t="n">
-        <v>132.453</v>
+        <v>138.427</v>
       </c>
       <c r="D211" t="n">
-        <v>22.103</v>
+        <v>22.133</v>
       </c>
     </row>
     <row r="212">
@@ -3805,13 +3805,13 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>9.831</v>
+        <v>9.586</v>
       </c>
       <c r="C212" t="n">
-        <v>127.122</v>
+        <v>129.577</v>
       </c>
       <c r="D212" t="n">
-        <v>22.208</v>
+        <v>22.238</v>
       </c>
     </row>
     <row r="213">
@@ -3821,13 +3821,13 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>10.692</v>
+        <v>10.604</v>
       </c>
       <c r="C213" t="n">
-        <v>115.107</v>
+        <v>115.379</v>
       </c>
       <c r="D213" t="n">
-        <v>22.956</v>
+        <v>23.115</v>
       </c>
     </row>
     <row r="214">
@@ -3837,13 +3837,13 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>10.245</v>
+        <v>10.077</v>
       </c>
       <c r="C214" t="n">
-        <v>125.463</v>
+        <v>124.083</v>
       </c>
       <c r="D214" t="n">
-        <v>22.721</v>
+        <v>22.909</v>
       </c>
     </row>
     <row r="215">
@@ -3853,13 +3853,13 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>9.74</v>
+        <v>9.554</v>
       </c>
       <c r="C215" t="n">
-        <v>137.571</v>
+        <v>136.591</v>
       </c>
       <c r="D215" t="n">
-        <v>23.492</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="216">
@@ -3869,13 +3869,13 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>10.825</v>
+        <v>10.413</v>
       </c>
       <c r="C216" t="n">
-        <v>139.816</v>
+        <v>137.339</v>
       </c>
       <c r="D216" t="n">
-        <v>24.071</v>
+        <v>23.582</v>
       </c>
     </row>
     <row r="217">
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>11.452</v>
+        <v>11.24</v>
       </c>
       <c r="C217" t="n">
-        <v>131.209</v>
+        <v>126.892</v>
       </c>
       <c r="D217" t="n">
-        <v>23.754</v>
+        <v>23.464</v>
       </c>
     </row>
     <row r="218">
@@ -3901,13 +3901,13 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>10.464</v>
+        <v>10.396</v>
       </c>
       <c r="C218" t="n">
-        <v>129.883</v>
+        <v>125.64</v>
       </c>
       <c r="D218" t="n">
-        <v>21.52</v>
+        <v>21.615</v>
       </c>
     </row>
     <row r="219">
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>10.042</v>
+        <v>10.247</v>
       </c>
       <c r="C219" t="n">
-        <v>126.065</v>
+        <v>123.416</v>
       </c>
       <c r="D219" t="n">
-        <v>21.689</v>
+        <v>21.719</v>
       </c>
     </row>
     <row r="220">
@@ -3933,13 +3933,13 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>10.649</v>
+        <v>10.641</v>
       </c>
       <c r="C220" t="n">
-        <v>124.122</v>
+        <v>123.876</v>
       </c>
       <c r="D220" t="n">
-        <v>22.788</v>
+        <v>22.747</v>
       </c>
     </row>
     <row r="221">
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>10.072</v>
+        <v>10.111</v>
       </c>
       <c r="C221" t="n">
-        <v>128.115</v>
+        <v>126.995</v>
       </c>
       <c r="D221" t="n">
-        <v>22.168</v>
+        <v>22.093</v>
       </c>
     </row>
     <row r="222">
@@ -3965,13 +3965,13 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>9.85</v>
+        <v>9.69</v>
       </c>
       <c r="C222" t="n">
-        <v>131.278</v>
+        <v>129.732</v>
       </c>
       <c r="D222" t="n">
-        <v>21.195</v>
+        <v>21.136</v>
       </c>
     </row>
     <row r="223">
@@ -3981,13 +3981,13 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>9.91</v>
+        <v>9.669</v>
       </c>
       <c r="C223" t="n">
-        <v>135.327</v>
+        <v>133.315</v>
       </c>
       <c r="D223" t="n">
-        <v>21.678</v>
+        <v>21.58</v>
       </c>
     </row>
     <row r="224">
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>10.876</v>
+        <v>10.411</v>
       </c>
       <c r="C224" t="n">
-        <v>124.43</v>
+        <v>121.288</v>
       </c>
       <c r="D224" t="n">
-        <v>21.805</v>
+        <v>21.544</v>
       </c>
     </row>
     <row r="225">
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>10.505</v>
+        <v>10.033</v>
       </c>
       <c r="C225" t="n">
-        <v>122.334</v>
+        <v>119.439</v>
       </c>
       <c r="D225" t="n">
-        <v>21.679</v>
+        <v>21.406</v>
       </c>
     </row>
     <row r="226">
@@ -4029,13 +4029,13 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>10.034</v>
+        <v>9.641</v>
       </c>
       <c r="C226" t="n">
-        <v>125.67</v>
+        <v>121.602</v>
       </c>
       <c r="D226" t="n">
-        <v>21.747</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="227">
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>10.548</v>
+        <v>10.33</v>
       </c>
       <c r="C227" t="n">
-        <v>117.459</v>
+        <v>115.822</v>
       </c>
       <c r="D227" t="n">
-        <v>21.971</v>
+        <v>21.734</v>
       </c>
     </row>
     <row r="228">
@@ -4061,13 +4061,13 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>11.295</v>
+        <v>11.263</v>
       </c>
       <c r="C228" t="n">
-        <v>107.745</v>
+        <v>107.716</v>
       </c>
       <c r="D228" t="n">
-        <v>22.108</v>
+        <v>22.163</v>
       </c>
     </row>
     <row r="229">
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>12.017</v>
+        <v>11.914</v>
       </c>
       <c r="C229" t="n">
-        <v>112.501</v>
+        <v>112.372</v>
       </c>
       <c r="D229" t="n">
-        <v>23.469</v>
+        <v>23.812</v>
       </c>
     </row>
     <row r="230">
@@ -4093,13 +4093,13 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>10.485</v>
+        <v>10.058</v>
       </c>
       <c r="C230" t="n">
-        <v>135.898</v>
+        <v>137.202</v>
       </c>
       <c r="D230" t="n">
-        <v>23.093</v>
+        <v>23.24</v>
       </c>
     </row>
     <row r="231">
@@ -4109,13 +4109,13 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>11.277</v>
+        <v>10.75</v>
       </c>
       <c r="C231" t="n">
-        <v>131.713</v>
+        <v>132.377</v>
       </c>
       <c r="D231" t="n">
-        <v>23.421</v>
+        <v>23.638</v>
       </c>
     </row>
     <row r="232">
@@ -4125,13 +4125,13 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>11.782</v>
+        <v>11.647</v>
       </c>
       <c r="C232" t="n">
-        <v>120.578</v>
+        <v>117.528</v>
       </c>
       <c r="D232" t="n">
-        <v>23.602</v>
+        <v>23.839</v>
       </c>
     </row>
     <row r="233">
@@ -4141,13 +4141,13 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>11.387</v>
+        <v>11.494</v>
       </c>
       <c r="C233" t="n">
-        <v>116.564</v>
+        <v>110.219</v>
       </c>
       <c r="D233" t="n">
-        <v>22.324</v>
+        <v>22.462</v>
       </c>
     </row>
     <row r="234">
@@ -4157,13 +4157,13 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>10.363</v>
+        <v>10.056</v>
       </c>
       <c r="C234" t="n">
-        <v>116.152</v>
+        <v>111.608</v>
       </c>
       <c r="D234" t="n">
-        <v>20.291</v>
+        <v>19.81</v>
       </c>
     </row>
     <row r="235">
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>10.841</v>
+        <v>10.363</v>
       </c>
       <c r="C235" t="n">
-        <v>114.134</v>
+        <v>110.144</v>
       </c>
       <c r="D235" t="n">
-        <v>20.81</v>
+        <v>20.292</v>
       </c>
     </row>
     <row r="236">
@@ -4189,13 +4189,13 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>10.939</v>
+        <v>10.535</v>
       </c>
       <c r="C236" t="n">
-        <v>128.621</v>
+        <v>123.668</v>
       </c>
       <c r="D236" t="n">
-        <v>23.076</v>
+        <v>22.925</v>
       </c>
     </row>
     <row r="237">
@@ -4205,13 +4205,13 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>11.381</v>
+        <v>11.222</v>
       </c>
       <c r="C237" t="n">
-        <v>129.233</v>
+        <v>127.767</v>
       </c>
       <c r="D237" t="n">
-        <v>25.465</v>
+        <v>26.004</v>
       </c>
     </row>
     <row r="238">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>11.111</v>
+        <v>10.97</v>
       </c>
       <c r="C238" t="n">
-        <v>133.125</v>
+        <v>132.795</v>
       </c>
       <c r="D238" t="n">
-        <v>25.622</v>
+        <v>26.168</v>
       </c>
     </row>
     <row r="239">
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>10.162</v>
+        <v>9.964</v>
       </c>
       <c r="C239" t="n">
-        <v>127.965</v>
+        <v>126.793</v>
       </c>
       <c r="D239" t="n">
-        <v>23.553</v>
+        <v>23.65</v>
       </c>
     </row>
     <row r="240">
@@ -4253,13 +4253,13 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>10.287</v>
+        <v>10.039</v>
       </c>
       <c r="C240" t="n">
-        <v>122.429</v>
+        <v>119.692</v>
       </c>
       <c r="D240" t="n">
-        <v>21.985</v>
+        <v>21.569</v>
       </c>
     </row>
     <row r="241">
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>10.072</v>
+        <v>9.991</v>
       </c>
       <c r="C241" t="n">
-        <v>111.697</v>
+        <v>110.349</v>
       </c>
       <c r="D241" t="n">
-        <v>20.766</v>
+        <v>20.608</v>
       </c>
     </row>
     <row r="242">
@@ -4285,13 +4285,13 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>11.073</v>
+        <v>10.793</v>
       </c>
       <c r="C242" t="n">
-        <v>107.258</v>
+        <v>106.048</v>
       </c>
       <c r="D242" t="n">
-        <v>20.582</v>
+        <v>20.431</v>
       </c>
     </row>
     <row r="243">
@@ -4301,13 +4301,13 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>11.88</v>
+        <v>11.492</v>
       </c>
       <c r="C243" t="n">
-        <v>101.164</v>
+        <v>98.95699999999999</v>
       </c>
       <c r="D243" t="n">
-        <v>21.03</v>
+        <v>20.904</v>
       </c>
     </row>
     <row r="244">
@@ -4317,13 +4317,13 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>12.649</v>
+        <v>12.456</v>
       </c>
       <c r="C244" t="n">
-        <v>100.779</v>
+        <v>98.39</v>
       </c>
       <c r="D244" t="n">
-        <v>22.08</v>
+        <v>21.893</v>
       </c>
     </row>
     <row r="245">
@@ -4333,13 +4333,13 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>9.737</v>
+        <v>9.711</v>
       </c>
       <c r="C245" t="n">
-        <v>114.031</v>
+        <v>112.81</v>
       </c>
       <c r="D245" t="n">
-        <v>20.31</v>
+        <v>20.068</v>
       </c>
     </row>
     <row r="246">
@@ -4349,13 +4349,13 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>9.545</v>
+        <v>9.555999999999999</v>
       </c>
       <c r="C246" t="n">
-        <v>114.975</v>
+        <v>111.105</v>
       </c>
       <c r="D246" t="n">
-        <v>19.73</v>
+        <v>19.188</v>
       </c>
     </row>
     <row r="247">
@@ -4365,13 +4365,13 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>11.529</v>
+        <v>11.633</v>
       </c>
       <c r="C247" t="n">
-        <v>109.799</v>
+        <v>101.465</v>
       </c>
       <c r="D247" t="n">
-        <v>21.4</v>
+        <v>21.049</v>
       </c>
     </row>
     <row r="248">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>11.698</v>
+        <v>11.734</v>
       </c>
       <c r="C248" t="n">
-        <v>119.504</v>
+        <v>114.027</v>
       </c>
       <c r="D248" t="n">
-        <v>23.139</v>
+        <v>22.965</v>
       </c>
     </row>
     <row r="249">
@@ -4397,13 +4397,13 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>11.112</v>
+        <v>10.889</v>
       </c>
       <c r="C249" t="n">
-        <v>118.926</v>
+        <v>116.675</v>
       </c>
       <c r="D249" t="n">
-        <v>23.202</v>
+        <v>22.907</v>
       </c>
     </row>
     <row r="250">
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>10.882</v>
+        <v>10.789</v>
       </c>
       <c r="C250" t="n">
-        <v>124.504</v>
+        <v>121.171</v>
       </c>
       <c r="D250" t="n">
-        <v>22.551</v>
+        <v>22.276</v>
       </c>
     </row>
     <row r="251">
@@ -4429,13 +4429,13 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>10.946</v>
+        <v>10.738</v>
       </c>
       <c r="C251" t="n">
-        <v>119.506</v>
+        <v>114.014</v>
       </c>
       <c r="D251" t="n">
-        <v>21.087</v>
+        <v>20.707</v>
       </c>
     </row>
     <row r="252">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>10.364</v>
+        <v>10.05</v>
       </c>
       <c r="C252" t="n">
-        <v>114.706</v>
+        <v>113.62</v>
       </c>
       <c r="D252" t="n">
-        <v>20.781</v>
+        <v>20.35</v>
       </c>
     </row>
     <row r="253">
@@ -4461,13 +4461,13 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>10.879</v>
+        <v>10.445</v>
       </c>
       <c r="C253" t="n">
-        <v>94.96899999999999</v>
+        <v>96.41500000000001</v>
       </c>
       <c r="D253" t="n">
-        <v>18.925</v>
+        <v>18.278</v>
       </c>
     </row>
     <row r="254">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>11.181</v>
+        <v>11.048</v>
       </c>
       <c r="C254" t="n">
-        <v>90.42400000000001</v>
+        <v>90.47199999999999</v>
       </c>
       <c r="D254" t="n">
-        <v>18.466</v>
+        <v>17.797</v>
       </c>
     </row>
     <row r="255">
@@ -4493,13 +4493,13 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>12.176</v>
+        <v>12.536</v>
       </c>
       <c r="C255" t="n">
-        <v>85.938</v>
+        <v>82.55</v>
       </c>
       <c r="D255" t="n">
-        <v>20.057</v>
+        <v>19.192</v>
       </c>
     </row>
     <row r="256">
@@ -4509,13 +4509,13 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>13.197</v>
+        <v>14.05</v>
       </c>
       <c r="C256" t="n">
-        <v>82.164</v>
+        <v>75.857</v>
       </c>
       <c r="D256" t="n">
-        <v>20.782</v>
+        <v>20.114</v>
       </c>
     </row>
     <row r="257">
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>13.445</v>
+        <v>14.29</v>
       </c>
       <c r="C257" t="n">
-        <v>79.30800000000001</v>
+        <v>73.681</v>
       </c>
       <c r="D257" t="n">
-        <v>19.77</v>
+        <v>19.537</v>
       </c>
     </row>
     <row r="258">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>14.62</v>
+        <v>14.983</v>
       </c>
       <c r="C258" t="n">
-        <v>79.755</v>
+        <v>74.035</v>
       </c>
       <c r="D258" t="n">
-        <v>19.823</v>
+        <v>19.641</v>
       </c>
     </row>
     <row r="259">
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>14.534</v>
+        <v>14.677</v>
       </c>
       <c r="C259" t="n">
-        <v>82.145</v>
+        <v>80.512</v>
       </c>
       <c r="D259" t="n">
-        <v>21.107</v>
+        <v>20.949</v>
       </c>
     </row>
     <row r="260">
@@ -4573,13 +4573,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>14.557</v>
+        <v>14.857</v>
       </c>
       <c r="C260" t="n">
-        <v>85.479</v>
+        <v>81.54600000000001</v>
       </c>
       <c r="D260" t="n">
-        <v>21.111</v>
+        <v>20.747</v>
       </c>
     </row>
     <row r="261">
@@ -4589,13 +4589,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>12.697</v>
+        <v>12.909</v>
       </c>
       <c r="C261" t="n">
-        <v>96.56100000000001</v>
+        <v>95.788</v>
       </c>
       <c r="D261" t="n">
-        <v>21.195</v>
+        <v>21.019</v>
       </c>
     </row>
     <row r="262">
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>13.017</v>
+        <v>13.325</v>
       </c>
       <c r="C262" t="n">
-        <v>99.324</v>
+        <v>94.934</v>
       </c>
       <c r="D262" t="n">
-        <v>22.234</v>
+        <v>21.582</v>
       </c>
     </row>
     <row r="263">
@@ -4621,13 +4621,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>12.086</v>
+        <v>12.076</v>
       </c>
       <c r="C263" t="n">
-        <v>90.997</v>
+        <v>90.04600000000001</v>
       </c>
       <c r="D263" t="n">
-        <v>21.19</v>
+        <v>20.762</v>
       </c>
     </row>
     <row r="264">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>13.004</v>
+        <v>13.191</v>
       </c>
       <c r="C264" t="n">
-        <v>81.842</v>
+        <v>78.468</v>
       </c>
       <c r="D264" t="n">
-        <v>19.593</v>
+        <v>19.223</v>
       </c>
     </row>
     <row r="265">
@@ -4653,13 +4653,13 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>12.668</v>
+        <v>12.958</v>
       </c>
       <c r="C265" t="n">
-        <v>83.49299999999999</v>
+        <v>83.148</v>
       </c>
       <c r="D265" t="n">
-        <v>19.645</v>
+        <v>19.691</v>
       </c>
     </row>
     <row r="266">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>14.859</v>
+        <v>15.299</v>
       </c>
       <c r="C266" t="n">
-        <v>80.56399999999999</v>
+        <v>77.05</v>
       </c>
       <c r="D266" t="n">
-        <v>19.684</v>
+        <v>19.405</v>
       </c>
     </row>
     <row r="267">
@@ -4685,13 +4685,13 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>15.399</v>
+        <v>15.744</v>
       </c>
       <c r="C267" t="n">
-        <v>90.81399999999999</v>
+        <v>84.254</v>
       </c>
       <c r="D267" t="n">
-        <v>21.121</v>
+        <v>21.036</v>
       </c>
     </row>
     <row r="268">
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>14.288</v>
+        <v>14.385</v>
       </c>
       <c r="C268" t="n">
-        <v>109.033</v>
+        <v>103.489</v>
       </c>
       <c r="D268" t="n">
-        <v>22.368</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="269">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>11.568</v>
+        <v>11.749</v>
       </c>
       <c r="C269" t="n">
-        <v>124.877</v>
+        <v>118.706</v>
       </c>
       <c r="D269" t="n">
-        <v>25.325</v>
+        <v>24.923</v>
       </c>
     </row>
     <row r="270">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>11.696</v>
+        <v>11.965</v>
       </c>
       <c r="C270" t="n">
-        <v>110.842</v>
+        <v>105.029</v>
       </c>
       <c r="D270" t="n">
-        <v>24.451</v>
+        <v>23.593</v>
       </c>
     </row>
     <row r="271">
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>13.998</v>
+        <v>14.36</v>
       </c>
       <c r="C271" t="n">
-        <v>93.297</v>
+        <v>86.251</v>
       </c>
       <c r="D271" t="n">
-        <v>23.055</v>
+        <v>22.378</v>
       </c>
     </row>
     <row r="272">
@@ -4765,13 +4765,13 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>14.569</v>
+        <v>14.872</v>
       </c>
       <c r="C272" t="n">
-        <v>82.18000000000001</v>
+        <v>78.001</v>
       </c>
       <c r="D272" t="n">
-        <v>20.3</v>
+        <v>20.037</v>
       </c>
     </row>
     <row r="273">
@@ -4781,13 +4781,13 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>13.845</v>
+        <v>14.239</v>
       </c>
       <c r="C273" t="n">
-        <v>79.846</v>
+        <v>75.476</v>
       </c>
       <c r="D273" t="n">
-        <v>19.154</v>
+        <v>19.097</v>
       </c>
     </row>
     <row r="274">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>13.435</v>
+        <v>14.119</v>
       </c>
       <c r="C274" t="n">
-        <v>82.467</v>
+        <v>75.443</v>
       </c>
       <c r="D274" t="n">
-        <v>18.368</v>
+        <v>18.091</v>
       </c>
     </row>
     <row r="275">
@@ -4813,13 +4813,13 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>15.614</v>
+        <v>15.813</v>
       </c>
       <c r="C275" t="n">
-        <v>74.47499999999999</v>
+        <v>67.77200000000001</v>
       </c>
       <c r="D275" t="n">
-        <v>17.351</v>
+        <v>16.737</v>
       </c>
     </row>
     <row r="276">
@@ -4829,13 +4829,13 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>15.314</v>
+        <v>15.389</v>
       </c>
       <c r="C276" t="n">
-        <v>72.884</v>
+        <v>67.185</v>
       </c>
       <c r="D276" t="n">
-        <v>18.756</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="277">
@@ -4845,13 +4845,13 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>12.572</v>
+        <v>12.688</v>
       </c>
       <c r="C277" t="n">
-        <v>79.19499999999999</v>
+        <v>78.09399999999999</v>
       </c>
       <c r="D277" t="n">
-        <v>19.821</v>
+        <v>19.132</v>
       </c>
     </row>
     <row r="278">
@@ -4861,13 +4861,13 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>12.675</v>
+        <v>12.725</v>
       </c>
       <c r="C278" t="n">
-        <v>82.901</v>
+        <v>82.809</v>
       </c>
       <c r="D278" t="n">
-        <v>21.327</v>
+        <v>20.881</v>
       </c>
     </row>
     <row r="279">
@@ -4877,13 +4877,13 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>13.589</v>
+        <v>13.258</v>
       </c>
       <c r="C279" t="n">
-        <v>81.425</v>
+        <v>82.133</v>
       </c>
       <c r="D279" t="n">
-        <v>20.578</v>
+        <v>20.141</v>
       </c>
     </row>
     <row r="280">
@@ -4893,13 +4893,13 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>13.637</v>
+        <v>13.707</v>
       </c>
       <c r="C280" t="n">
-        <v>84.069</v>
+        <v>82.518</v>
       </c>
       <c r="D280" t="n">
-        <v>21.197</v>
+        <v>20.813</v>
       </c>
     </row>
     <row r="281">
@@ -4909,13 +4909,13 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>14.219</v>
+        <v>14.315</v>
       </c>
       <c r="C281" t="n">
-        <v>79.56699999999999</v>
+        <v>76.34399999999999</v>
       </c>
       <c r="D281" t="n">
-        <v>17.824</v>
+        <v>17.268</v>
       </c>
     </row>
     <row r="282">
@@ -4925,13 +4925,13 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>15.963</v>
+        <v>16.094</v>
       </c>
       <c r="C282" t="n">
-        <v>83.642</v>
+        <v>75.387</v>
       </c>
       <c r="D282" t="n">
-        <v>20.484</v>
+        <v>19.926</v>
       </c>
     </row>
     <row r="283">
@@ -4941,13 +4941,13 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>13.579</v>
+        <v>13.437</v>
       </c>
       <c r="C283" t="n">
-        <v>97.863</v>
+        <v>87.163</v>
       </c>
       <c r="D283" t="n">
-        <v>20.054</v>
+        <v>19.417</v>
       </c>
     </row>
     <row r="284">
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>12.545</v>
+        <v>12.333</v>
       </c>
       <c r="C284" t="n">
-        <v>100.914</v>
+        <v>91.44499999999999</v>
       </c>
       <c r="D284" t="n">
-        <v>19.401</v>
+        <v>19.073</v>
       </c>
     </row>
     <row r="285">
@@ -4973,13 +4973,13 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>14.415</v>
+        <v>14.233</v>
       </c>
       <c r="C285" t="n">
-        <v>81.34699999999999</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="D285" t="n">
-        <v>16.625</v>
+        <v>16.081</v>
       </c>
     </row>
     <row r="286">
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>14.353</v>
+        <v>14.733</v>
       </c>
       <c r="C286" t="n">
-        <v>82.77200000000001</v>
+        <v>74.452</v>
       </c>
       <c r="D286" t="n">
-        <v>19.654</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="287">
@@ -5005,13 +5005,13 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>13.269</v>
+        <v>13.511</v>
       </c>
       <c r="C287" t="n">
-        <v>80.675</v>
+        <v>75.36499999999999</v>
       </c>
       <c r="D287" t="n">
-        <v>18.87</v>
+        <v>17.932</v>
       </c>
     </row>
     <row r="288">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>14.393</v>
+        <v>14.307</v>
       </c>
       <c r="C288" t="n">
-        <v>79.63800000000001</v>
+        <v>77.044</v>
       </c>
       <c r="D288" t="n">
-        <v>19.788</v>
+        <v>19.398</v>
       </c>
     </row>
     <row r="289">
@@ -5037,13 +5037,13 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>16.136</v>
+        <v>15.981</v>
       </c>
       <c r="C289" t="n">
-        <v>77.256</v>
+        <v>73.209</v>
       </c>
       <c r="D289" t="n">
-        <v>21.361</v>
+        <v>21.197</v>
       </c>
     </row>
     <row r="290">
@@ -5053,13 +5053,13 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>16.849</v>
+        <v>16.724</v>
       </c>
       <c r="C290" t="n">
-        <v>79.697</v>
+        <v>72.785</v>
       </c>
       <c r="D290" t="n">
-        <v>22.431</v>
+        <v>22.421</v>
       </c>
     </row>
     <row r="291">
@@ -5069,13 +5069,13 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>14.785</v>
+        <v>14.417</v>
       </c>
       <c r="C291" t="n">
-        <v>88.26900000000001</v>
+        <v>81.828</v>
       </c>
       <c r="D291" t="n">
-        <v>21.317</v>
+        <v>21.104</v>
       </c>
     </row>
     <row r="292">
@@ -5085,13 +5085,13 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>14.607</v>
+        <v>14.261</v>
       </c>
       <c r="C292" t="n">
-        <v>85.03</v>
+        <v>81.67400000000001</v>
       </c>
       <c r="D292" t="n">
-        <v>19.569</v>
+        <v>19.221</v>
       </c>
     </row>
     <row r="293">
@@ -5101,13 +5101,13 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>14.516</v>
+        <v>14.452</v>
       </c>
       <c r="C293" t="n">
-        <v>83.611</v>
+        <v>79.286</v>
       </c>
       <c r="D293" t="n">
-        <v>19.275</v>
+        <v>18.845</v>
       </c>
     </row>
     <row r="294">
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>15.464</v>
+        <v>15.768</v>
       </c>
       <c r="C294" t="n">
-        <v>75.756</v>
+        <v>66.11</v>
       </c>
       <c r="D294" t="n">
-        <v>16.884</v>
+        <v>16.417</v>
       </c>
     </row>
     <row r="295">
@@ -5133,13 +5133,13 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>14.945</v>
+        <v>15.217</v>
       </c>
       <c r="C295" t="n">
-        <v>81.057</v>
+        <v>69.777</v>
       </c>
       <c r="D295" t="n">
-        <v>17.946</v>
+        <v>17.442</v>
       </c>
     </row>
     <row r="296">
@@ -5149,13 +5149,13 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>15.952</v>
+        <v>15.88</v>
       </c>
       <c r="C296" t="n">
-        <v>77.111</v>
+        <v>67.34699999999999</v>
       </c>
       <c r="D296" t="n">
-        <v>17.859</v>
+        <v>17.223</v>
       </c>
     </row>
     <row r="297">
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>15.052</v>
+        <v>14.887</v>
       </c>
       <c r="C297" t="n">
-        <v>85.264</v>
+        <v>74.64700000000001</v>
       </c>
       <c r="D297" t="n">
-        <v>18.989</v>
+        <v>18.443</v>
       </c>
     </row>
     <row r="298">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>12.234</v>
+        <v>12.52</v>
       </c>
       <c r="C298" t="n">
-        <v>93.874</v>
+        <v>82.12</v>
       </c>
       <c r="D298" t="n">
-        <v>17.782</v>
+        <v>17.231</v>
       </c>
     </row>
     <row r="299">
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>14.026</v>
+        <v>14.147</v>
       </c>
       <c r="C299" t="n">
-        <v>83.709</v>
+        <v>75.548</v>
       </c>
       <c r="D299" t="n">
-        <v>18.136</v>
+        <v>17.624</v>
       </c>
     </row>
     <row r="300">
@@ -5213,13 +5213,13 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>13.818</v>
+        <v>13.657</v>
       </c>
       <c r="C300" t="n">
-        <v>82.553</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="D300" t="n">
-        <v>18.217</v>
+        <v>17.645</v>
       </c>
     </row>
     <row r="301">
@@ -5229,13 +5229,13 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>15.373</v>
+        <v>14.681</v>
       </c>
       <c r="C301" t="n">
-        <v>83.962</v>
+        <v>80.503</v>
       </c>
       <c r="D301" t="n">
-        <v>21.22</v>
+        <v>20.704</v>
       </c>
     </row>
     <row r="302">
@@ -5245,13 +5245,13 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>13.365</v>
+        <v>12.728</v>
       </c>
       <c r="C302" t="n">
-        <v>95.233</v>
+        <v>88.479</v>
       </c>
       <c r="D302" t="n">
-        <v>20.279</v>
+        <v>19.831</v>
       </c>
     </row>
     <row r="303">
@@ -5261,13 +5261,13 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>13.336</v>
+        <v>12.938</v>
       </c>
       <c r="C303" t="n">
-        <v>98.30500000000001</v>
+        <v>87.428</v>
       </c>
       <c r="D303" t="n">
-        <v>18.938</v>
+        <v>18.529</v>
       </c>
     </row>
     <row r="304">
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>12.587</v>
+        <v>12.455</v>
       </c>
       <c r="C304" t="n">
-        <v>96.47499999999999</v>
+        <v>88.252</v>
       </c>
       <c r="D304" t="n">
-        <v>18.089</v>
+        <v>17.722</v>
       </c>
     </row>
     <row r="305">
@@ -5293,13 +5293,13 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>14.919</v>
+        <v>15.038</v>
       </c>
       <c r="C305" t="n">
-        <v>84.73999999999999</v>
+        <v>78.205</v>
       </c>
       <c r="D305" t="n">
-        <v>19.414</v>
+        <v>18.972</v>
       </c>
     </row>
     <row r="306">
@@ -5309,13 +5309,13 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>15.077</v>
+        <v>15.549</v>
       </c>
       <c r="C306" t="n">
-        <v>77.678</v>
+        <v>73.788</v>
       </c>
       <c r="D306" t="n">
-        <v>19.086</v>
+        <v>18.77</v>
       </c>
     </row>
     <row r="307">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>12.921</v>
+        <v>13.59</v>
       </c>
       <c r="C307" t="n">
-        <v>85.428</v>
+        <v>83.94799999999999</v>
       </c>
       <c r="D307" t="n">
-        <v>20.014</v>
+        <v>19.665</v>
       </c>
     </row>
     <row r="308">
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>12.454</v>
+        <v>13.045</v>
       </c>
       <c r="C308" t="n">
-        <v>87.452</v>
+        <v>86.36799999999999</v>
       </c>
       <c r="D308" t="n">
-        <v>20.801</v>
+        <v>20.383</v>
       </c>
     </row>
     <row r="309">
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>13.476</v>
+        <v>13.589</v>
       </c>
       <c r="C309" t="n">
-        <v>82.10299999999999</v>
+        <v>81.24299999999999</v>
       </c>
       <c r="D309" t="n">
-        <v>20.381</v>
+        <v>20.228</v>
       </c>
     </row>
     <row r="310">
@@ -5373,13 +5373,13 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>15.903</v>
+        <v>15.233</v>
       </c>
       <c r="C310" t="n">
-        <v>70.486</v>
+        <v>68.566</v>
       </c>
       <c r="D310" t="n">
-        <v>18.82</v>
+        <v>19.107</v>
       </c>
     </row>
   </sheetData>
